--- a/banks/CLEARBANK FINANCIALS.xlsx
+++ b/banks/CLEARBANK FINANCIALS.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,18 +197,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>ClearBank Limited — Cash Flow Summary by Year</a:t>
+              <a:t>ClearBank Limited — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -235,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -259,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -283,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -295,30 +300,6 @@
           <val>
             <numRef>
               <f>'Overview'!$J$8:$N$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'Overview'!I9</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Overview'!$J$9:$N$9</f>
             </numRef>
           </val>
         </ser>
@@ -350,8 +331,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -390,13 +371,583 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ClearBank Limited — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$11:$V$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$11:$V$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$11:$V$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ClearBank Limited — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y18</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$17:$AD$17</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$17:$AD$17</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$17:$AD$17</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$17:$AD$17</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$21:$AD$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ClearBank Limited — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$24:$AL$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$24:$AL$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$24:$AL$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG28</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$24:$AL$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$28:$AL$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -428,30 +979,30 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -461,30 +1012,30 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q7</f>
+              <f>'Overview'!AO7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$7:$V$7</f>
+              <f>'Overview'!$AP$7:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -494,30 +1045,30 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q8</f>
+              <f>'Overview'!AO8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$8:$V$8</f>
+              <f>'Overview'!$AP$8:$AT$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -549,8 +1100,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -589,12 +1140,12 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -604,9 +1155,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -616,19 +1167,85 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>82</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>104</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>126</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -926,7 +1543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:AT36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -949,6 +1566,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -961,14 +1602,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary (£'000)</t>
+          <t>Balance Sheet Summary (£'000)</t>
         </is>
       </c>
     </row>
@@ -1028,27 +1669,27 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1057,376 +1698,988 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net cash from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>7017191</v>
+        <v>18068355</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>4690772</v>
+        <v>11064063</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>3142548</v>
+        <v>6366850</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>413627</v>
+        <v>3204409</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1683715</v>
+        <v>2772608</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net cash from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1683715</v>
+        <v>2772608</v>
       </c>
       <c r="K6" t="n">
-        <v>413627</v>
+        <v>3204409</v>
       </c>
       <c r="L6" t="n">
-        <v>3142548</v>
+        <v>6366850</v>
       </c>
       <c r="M6" t="n">
-        <v>4690772</v>
+        <v>11064063</v>
       </c>
       <c r="N6" t="n">
-        <v>7017191</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>18068355</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="AP6" t="n">
         <v>139.7</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AQ6" t="n">
         <v>87.66</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AR6" t="n">
         <v>77.45</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AS6" t="n">
         <v>67.02</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AT6" t="n">
         <v>49.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
+          <t>Customer deposits</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-15684</v>
+        <v>17826803</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-24096</v>
+        <v>10818568</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-21778</v>
+        <v>6147363</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-8144</v>
+        <v>2982259</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-8624</v>
+        <v>2644756</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
+          <t>Customer deposits</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-8624</v>
+        <v>2644756</v>
       </c>
       <c r="K7" t="n">
-        <v>-8144</v>
+        <v>2982259</v>
       </c>
       <c r="L7" t="n">
-        <v>-21778</v>
+        <v>6147363</v>
       </c>
       <c r="M7" t="n">
-        <v>-24096</v>
+        <v>10818568</v>
       </c>
       <c r="N7" t="n">
-        <v>-15684</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>17826803</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="AP7" t="n">
         <v>38.79</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AQ7" t="n">
         <v>13.87</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AR7" t="n">
         <v>43.51</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AS7" t="n">
         <v>26.07</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AT7" t="n">
         <v>20.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>212839</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>222291</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>129526</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>87312</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>72217</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>72217</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87312</v>
+      </c>
+      <c r="L8" t="n">
+        <v>129526</v>
+      </c>
+      <c r="M8" t="n">
+        <v>222291</v>
+      </c>
+      <c r="N8" t="n">
+        <v>212839</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>LCR</t>
+        </is>
+      </c>
+      <c r="AP8" t="n">
+        <v>185.94</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>297.05</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>445.36</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>381.88</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>396.85</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Profit &amp; Loss Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>132684</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>112086</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>111347</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>58284</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>21394</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>21394</v>
+      </c>
+      <c r="S12" t="n">
+        <v>58284</v>
+      </c>
+      <c r="T12" t="n">
+        <v>111347</v>
+      </c>
+      <c r="U12" t="n">
+        <v>112086</v>
+      </c>
+      <c r="V12" t="n">
+        <v>132684</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>-148934</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-122035</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-105783</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-77638</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-52439</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>-52439</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-77638</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-105783</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-122035</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-148934</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year after taxation</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-15765</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-10318</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>22396</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>6818</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-28200</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year after taxation</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-28200</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6818</v>
+      </c>
+      <c r="T14" t="n">
+        <v>22396</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-10318</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-15765</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>222291</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>196497</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>87312</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>72217</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>58247</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>58247</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>72217</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>87312</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>196497</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>222291</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>-13977</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-11085</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>22396</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>6819</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-28201</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>-28201</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>6819</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>22396</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-11085</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-13977</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>4525</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>36879</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>19818</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>8276</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>42171</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>42171</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>8276</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>19818</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>36879</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>212839</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>222291</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>129526</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>87312</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>72217</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>72217</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>87312</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>129526</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>222291</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>212839</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from operating activities</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>7017191</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>4690772</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3142548</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>413627</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>1683715</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Net cash from operating activities</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>1683715</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>413627</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>3142548</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>4690772</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>7017191</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-15684</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-24096</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-21778</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-8144</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-8624</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>-8624</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>-8144</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>-21778</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>-24096</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-15684</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>Net cash from/(used in) financing activities</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B27" s="5" t="n">
         <v>-1603</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C27" s="5" t="n">
         <v>33433</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D27" s="5" t="n">
         <v>9537</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E27" s="5" t="n">
         <v>-384</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F27" s="5" t="n">
         <v>32492</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>Net cash from/(used in) financing activities</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="AH27" t="n">
         <v>32492</v>
       </c>
-      <c r="K8" t="n">
+      <c r="AI27" t="n">
         <v>-384</v>
       </c>
-      <c r="L8" t="n">
+      <c r="AJ27" t="n">
         <v>9537</v>
       </c>
-      <c r="M8" t="n">
+      <c r="AK27" t="n">
         <v>33433</v>
       </c>
-      <c r="N8" t="n">
+      <c r="AL27" t="n">
         <v>-1603</v>
       </c>
-      <c r="Q8" t="inlineStr">
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>17956976</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>10961293</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>6256126</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>3125862</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>2720797</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>2720797</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>3125862</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>6256126</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>10961293</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>17956976</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Pillar 3 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>CET1 Ratio</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>49.75%</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>67.02%</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>77.45%</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>87.66%</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>139.70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Leverage Ratio</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>20.05%</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>26.07%</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>43.51%</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>13.87%</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>38.79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="R8" t="n">
-        <v>185.94</v>
-      </c>
-      <c r="S8" t="n">
-        <v>297.05</v>
-      </c>
-      <c r="T8" t="n">
-        <v>445.36</v>
-      </c>
-      <c r="U8" t="n">
-        <v>381.88</v>
-      </c>
-      <c r="V8" t="n">
-        <v>396.85</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents at end of year</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>17956976</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>10961293</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>6256126</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>3125862</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>2720797</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents at end of year</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>2720797</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3125862</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6256126</v>
-      </c>
-      <c r="M9" t="n">
-        <v>10961293</v>
-      </c>
-      <c r="N9" t="n">
-        <v>17956976</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Pillar 3 Key Metrics</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>CET1 Ratio</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>49.75%</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>67.02%</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>77.45%</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>87.66%</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>139.70%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Leverage Ratio</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>20.05%</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>26.07%</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>43.51%</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>13.87%</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>38.79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>LCR</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>396.85%</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>381.88%</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>445.36%</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>297.05%</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>185.94%</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. NSFR omitted from this chart (values in the thousands of percent would flatten every other series) - see the NSFR sheet directly.</t>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Statement of Changes in Equity Summary: FY2024's Opening equity is a new ultimate parent entity's own balance (ClearBank Group Holdings Limited, inserted above ClearBank Limited during FY2024), not a continuation of FY2023's Closing equity - see the Statement of Changes in Equity sheet for the full entity-change note. NSFR omitted from this chart (values in the thousands of percent would flatten every other series) - see the NSFR sheet directly.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A36:F36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1439,7 +2692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1453,14 +2706,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — Leverage Ratio</t>
+          <t>ClearBank Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -1499,44 +2752,37 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Leverage ratio excluding claims on central banks</t>
+          <t>Tier 1 ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>20.05%</t>
+          <t>49.75%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>26.07%</t>
+          <t>67.02%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>43.51%</t>
+          <t>77.45%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>13.87%</t>
+          <t>87.66%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>38.79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is on the "UK leverage ratio" basis (39% as originally disclosed in ClearBank's own FY2021 Pillar 3 document), consistent with the "excluding claims on central banks" basis used FY2022 onward - see the LEVERAGE RATIO BASIS NOTE in this sheet's source citation for the very different "CRD leverage ratio" (1%) also disclosed for FY2021 on a different exposure-measure definition.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="190" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>139.70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="190" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
@@ -1548,9 +2794,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1576,14 +2821,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — LCR</t>
+          <t>ClearBank Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m (= CET1 capital; no Tier 2 instruments)</t>
         </is>
       </c>
     </row>
@@ -1622,33 +2867,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Liquidity Coverage Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>396.85%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>381.88%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>445.36%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>297.05%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>185.94%</t>
-        </is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>36.7</v>
       </c>
     </row>
     <row r="6" ht="190" customHeight="1">
@@ -1672,6 +2907,389 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank Limited — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>% of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>49.75%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>67.02%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>77.45%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>87.66%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>139.70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="190" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
+FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>266</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>211</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>163</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="190" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
+FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000 (source tables are in £m; converted x1000 for unit consistency with other sheets). See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>RWA by risk category</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (excluding CCR), standardised approach</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>34000</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk, basic indicator approach</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>221000</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>178000</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>127000</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Total RWAs</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>266000</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>212000</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>163000</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>38000</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="9" ht="340" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank Group Pillar 3 "Overview of RWA"/"Overview of risk weighted exposure amounts" table:
+FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.18 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2023: ClearBank Pillar 3 Disclosure 2023, p.11 (ClearBank Group column) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
+FY2022: ClearBank Pillar 3 disclosure 2022, p.15 (own originally-published figures, not FY2023's restated comparative - see note below) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf
+FY2021: ClearBank Pillar 3 disclosure 2022, p.15 (FY2021 comparative column) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf
+Only two risk categories are disclosed in any year: Credit risk (excluding CCR, Standardised Approach) and Operational risk (Basic Indicator Approach) - no market risk, CCR, or CVA charge in any year (consistent with a clearing/embedded-banking bank with no trading book).
+FY2024's Total here (£212m = £34m + £178m) is £1m higher than the FY2024 figure on this workbook's own Total RWAs sheet (£211m) - an immaterial rounding artifact in ClearBank's own Pillar 3 table, reproduced as disclosed rather than force-matched.
+RESTATEMENT NOTE: ClearBank's own FY2022 Pillar 3 disclosure (2022 edition) states Operational risk RWA of £22m (Total £38m), matching this workbook's existing Total RWAs sheet. The FY2023 Pillar 3 disclosure's own FY2022 comparative column instead shows Operational risk RWA of £55m (Total £71m) - a large restatement between Pillar 3 vintages with no explanation given. Per project convention, FY2022's own originally-published figures (£16m credit / £22m operational / £38m total) are used here, not the later restated comparative.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1691,7 +3309,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — NSFR</t>
+          <t>ClearBank Limited — Leverage Ratio</t>
         </is>
       </c>
     </row>
@@ -1737,39 +3355,39 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Net Stable Funding Ratio</t>
+          <t>Leverage ratio excluding claims on central banks</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>20366.50%</t>
+          <t>20.05%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>15959.22%</t>
+          <t>26.07%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>10153.88%</t>
+          <t>43.51%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>5429.15%</t>
+          <t>13.87%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>11701.32%</t>
+          <t>38.79%</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Extreme values (5,000%-20,000%+) are genuine, not a transcription error - ClearBank's clearing-bank business model holds very large customer deposit balances relative to a small lending book, so required stable funding is tiny relative to available stable funding.</t>
+          <t>Note: FY2021 figure is on the "UK leverage ratio" basis (39% as originally disclosed in ClearBank's own FY2021 Pillar 3 document), consistent with the "excluding claims on central banks" basis used FY2022 onward - see the LEVERAGE RATIO BASIS NOTE in this sheet's source citation for the very different "CRD leverage ratio" (1%) also disclosed for FY2021 on a different exposure-measure definition.</t>
         </is>
       </c>
     </row>
@@ -1794,7 +3412,245 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank Limited — LCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>396.85%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>381.88%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>445.36%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>297.05%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>185.94%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="190" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
+FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank Limited — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20366.50%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>15959.22%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>10153.88%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>5429.15%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>11701.32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Extreme values (5,000%-20,000%+) are genuine, not a transcription error - ClearBank's clearing-bank business model holds very large customer deposit balances relative to a small lending book, so required stable funding is tiny relative to available stable funding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="190" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
+FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1919,6 +3775,1972 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank — Consolidated Statement of Financial Position</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000. FY2023 is Company-only (no Consolidated statements published that year). See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>17956976</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>10961293</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>6256126</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>3125862</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>2720797</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n">
+        <v>19525</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>9156</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>5962</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Collateral placed</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>509</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1368</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1352</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>433</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>17296</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>10408</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>9768</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>6212</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>4478</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Current tax asset / due from UK tax authorities</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1563</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>753</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>3542</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Right-of-use asset</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>549</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>2111</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>952</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>2677</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>566</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>51683</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>52670</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>41806</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>29184</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>27479</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax asset</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>39779</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>35426</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>33682</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>25956</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>12525</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>18068355</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>11064063</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>6366850</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>3204409</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>2772608</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Customer deposits</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>17826803</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>10818568</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>6147363</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>2982259</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>2644756</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Other payables</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>27067</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>20708</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>82372</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>109307</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>9897</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Lease obligations</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1256</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>2219</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1003</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>2789</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Deferred income</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>390</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>277</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>6444</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>22742</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>45229</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Current tax liability</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n">
+        <v>142</v>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>17855516</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>10841772</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>6237324</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>3117097</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>2700391</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Called up share capital</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Share premium</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>224403</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>224403</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>203445</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>192349</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>191816</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Treasury shares</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n">
+        <v>-204</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-204</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Capital contribution reserve</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>11942</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>9188</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>26805</v>
+      </c>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payment reserve</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n">
+        <v>24933</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>17190</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Retained earnings/(losses)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>-24512</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>-10518</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>-100724</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>-129650</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>-136468</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Translation reserve</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>1004</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>-784</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n">
+        <v>-116</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>-117</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>212839</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>222291</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>129526</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>87312</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>72217</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>18068355</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>11064063</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>6366850</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>3204409</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>2772608</v>
+      </c>
+    </row>
+    <row r="33" ht="380" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank's own Statement of Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, transcribed from each year's own report:
+FY2025/FY2024: Consolidated statements, ClearBank Group Holdings Limited Annual Report and Accounts 2025, pp.68-70 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2025.pdf
+FY2023: Company statements (no Consolidated statements published that year), ClearBank Annual Report and Accounts 2023, pp.69-72 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts-2023.pdf
+FY2022: Consolidated statements, own originally-published figures (not FY2023's restated comparative - see Note 32 of the FY2023 report), ClearBank Annual Report and Accounts 2022, pp.80-83 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts_2022.pdf
+FY2021: Consolidated statements, ClearBank Limited Annual Report and Accounts 2021, pp.60-63 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2021.pdf
+ENTITY-CHANGE NOTE (corrected on follow-up review against ClearBank Group Holdings Limited's own FY2023 Companies House filing, company 14254435): FY2021-FY2023 figures are ClearBank Limited's own statements (Companies House 09736376). FY2024/FY2025 figures are instead from the Annual Report and Accounts 2025, whose auditor's report and Statement of Financial Position are addressed to "ClearBank Group Holdings Limited" - a NEW intermediate holding entity (incorporated 25 July 2022) inserted above ClearBank Limited DURING FY2023, not between FY2023 and FY2024 as an earlier pass of this workbook stated. Per that entity's own first Group accounts (period ended 31 December 2023, filed at Companies House 18 May 2024 - https://find-and-update.company-information.service.gov.uk/company/14254435/filing-history/MzQyMTUzMzg4NGFkaXF6a2N4/document?format=pdf&amp;download=0), its inaugural subsidiary ClearBank Europe N.V. was incorporated 6 March 2023; it acquired 100% of ClearBank Limited on 8 December 2023 as a Business Combination Under Common Control, with ClearBank Limited's results consolidated from 1 May 2023 (the day after common control was established, 30 April 2023). "CB Growth Holdings Limited" (named in AR2023's own equity note 3, and confirmed in ClearBank Group Holdings Limited's own Note 1.4 as "its parent") is a GENUINELY SEPARATE, higher entity in the group chain - not an earlier name for ClearBank Group Holdings Limited (no Companies House previous-names record exists for company 14254435, and its own filing history shows no rename). The corrected chain, top to bottom, is: CB Growth Holdings Limited -&gt; ClearBank Group Holdings Limited (14254435) -&gt; ClearBank Limited. This is a genuine change of reporting entity, not a presentation choice: the Statement of Changes in Equity's FY2024 opening balance (£196,497k) does not equal FY2023's own closing balance (£129,526k) below, and the two entities' equity bases are not directly comparable, so no plug/bridging row is used across that boundary in this sheet. However, a genuine bridge DOES exist and is now cited for traceability: ClearBank Group Holdings Limited's own stub-period Consolidated statement of changes in equity (in the filing above) runs from £(812)k total equity at 1 March 2023 (its own first reporting date) to exactly £196,497k at 31 December 2023 - i.e. this workbook's existing FY2024 opening figure is that entity's own closing balance for its first, ~10-month accounting period, built mostly from a £179,405k share capital issuance (the mechanism for the ClearBank Limited acquisition) rather than organic trading profit. This bridging period is not added as its own column here since it doesn't align with this workbook's FY-year grid, but the £196,497k figure is now independently verified against its true source rather than only appearing as an unexplained opening balance. Balance Sheet and P&amp;L totals for each year are still internally consistent (assets = liabilities + equity; income - expenses = profit/loss) since each is a same-entity, same-year snapshot - only the cross-year equity roll-forward is affected. FY2023's own Statement of Financial Position/Comprehensive Income are Company-only (ClearBank Limited did not publish Consolidated statements that year - see the Company vs Consolidated presentation note below); FY2021/FY2022/FY2024/FY2025 are Consolidated. Per project convention, each year's own originally-published figures are used throughout (FY2022's own AR2022 Consolidated figures, not AR2023's restated comparative - see CASH_FLOW_SOURCES' existing ENTITY_NOTE for the same convention applied to Cash Flow).
+PRESENTATION NOTE: FY2021's own Statement of Comprehensive Income discloses only Net interest income and Net fee income (no separate Interest income/expense or Fee income/expense split) - per AR2022's own footnote, "In 2021, only net interest income and net fee income were presented without splitting for gross amounts." FY2023's own Statement of Comprehensive Income additionally has an "Expenses recharged" line (income, not cost) not present in any other year, resulting in a positive "Operating profit" that year rather than the "Operating loss" label used elsewhere - both reproduced as reported. Balance Sheet: "Loans and advances to banks" (an interbank placement, not a customer loan) appears as its own line FY2021-FY2023 only - dropped from FY2024/FY2025's presentation (folded into Cash and cash equivalents per the Group's own accounting policy note). "Due from UK tax authorities" (FY2022/FY2023) and "Current tax asset" (FY2024/FY2025) are the same concept under different labels; FY2021 has neither line. Equity: "Share-based payment reserve" (FY2021/FY2022) was replaced by "Capital contribution reserve" from FY2023 onward (see the entity-change note above); "Treasury shares" and "Translation reserve" are absent from FY2023's Company-only presentation, present in every other year's Consolidated presentation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A33:F33"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank — Consolidated Statement of Comprehensive Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000. FY2023 is Company-only (no Consolidated statements published that year). See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>625779</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>425289</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>243956</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>43774</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-554816</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-358179</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-162042</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-9911</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>70963</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>67110</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>81914</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>33863</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fee income</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>66183</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>47141</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>31390</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>25455</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Fee expenses</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-5268</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-2952</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-2620</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-1047</v>
+      </c>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net fee income</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>60915</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>44189</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>28770</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>24408</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>18614</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>806</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>787</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>663</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>132684</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>112086</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>111347</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>58284</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>21394</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Staff costs</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>-78740</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-67335</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-55318</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-40095</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-27719</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>-2265</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>-1693</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-2212</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-1334</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-2145</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Amortisation of intangibles</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>-15706</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>-11643</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>-8869</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-7824</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-5791</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Impairment</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>-936</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>-1584</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-268</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-675</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-337</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Other operating expenses</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>-51287</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>-39780</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>-39116</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-27710</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-16447</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>-148934</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-122035</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-105783</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-77638</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-52439</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Expenses recharged</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n">
+        <v>13054</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>8587</v>
+      </c>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Operating profit/(loss)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-16250</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-9949</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>18618</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-10767</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-31045</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Other gains/(losses)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>-354</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>-165</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>-111</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>-181</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Finance costs</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>-106</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>-130</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-78</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>-55</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-34</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year before taxation</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-16710</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-10244</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>18429</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-11003</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-31074</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Taxation</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>945</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-74</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>3967</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>17821</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year after taxation</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-15765</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-10318</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>22396</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>6818</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-28200</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Foreign currency translation differences</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>1788</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>-767</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>-13977</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>-11085</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>22396</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>6819</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-28201</v>
+      </c>
+    </row>
+    <row r="31" ht="380" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank's own Statement of Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, transcribed from each year's own report:
+FY2025/FY2024: Consolidated statements, ClearBank Group Holdings Limited Annual Report and Accounts 2025, pp.68-70 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2025.pdf
+FY2023: Company statements (no Consolidated statements published that year), ClearBank Annual Report and Accounts 2023, pp.69-72 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts-2023.pdf
+FY2022: Consolidated statements, own originally-published figures (not FY2023's restated comparative - see Note 32 of the FY2023 report), ClearBank Annual Report and Accounts 2022, pp.80-83 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts_2022.pdf
+FY2021: Consolidated statements, ClearBank Limited Annual Report and Accounts 2021, pp.60-63 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2021.pdf
+ENTITY-CHANGE NOTE (corrected on follow-up review against ClearBank Group Holdings Limited's own FY2023 Companies House filing, company 14254435): FY2021-FY2023 figures are ClearBank Limited's own statements (Companies House 09736376). FY2024/FY2025 figures are instead from the Annual Report and Accounts 2025, whose auditor's report and Statement of Financial Position are addressed to "ClearBank Group Holdings Limited" - a NEW intermediate holding entity (incorporated 25 July 2022) inserted above ClearBank Limited DURING FY2023, not between FY2023 and FY2024 as an earlier pass of this workbook stated. Per that entity's own first Group accounts (period ended 31 December 2023, filed at Companies House 18 May 2024 - https://find-and-update.company-information.service.gov.uk/company/14254435/filing-history/MzQyMTUzMzg4NGFkaXF6a2N4/document?format=pdf&amp;download=0), its inaugural subsidiary ClearBank Europe N.V. was incorporated 6 March 2023; it acquired 100% of ClearBank Limited on 8 December 2023 as a Business Combination Under Common Control, with ClearBank Limited's results consolidated from 1 May 2023 (the day after common control was established, 30 April 2023). "CB Growth Holdings Limited" (named in AR2023's own equity note 3, and confirmed in ClearBank Group Holdings Limited's own Note 1.4 as "its parent") is a GENUINELY SEPARATE, higher entity in the group chain - not an earlier name for ClearBank Group Holdings Limited (no Companies House previous-names record exists for company 14254435, and its own filing history shows no rename). The corrected chain, top to bottom, is: CB Growth Holdings Limited -&gt; ClearBank Group Holdings Limited (14254435) -&gt; ClearBank Limited. This is a genuine change of reporting entity, not a presentation choice: the Statement of Changes in Equity's FY2024 opening balance (£196,497k) does not equal FY2023's own closing balance (£129,526k) below, and the two entities' equity bases are not directly comparable, so no plug/bridging row is used across that boundary in this sheet. However, a genuine bridge DOES exist and is now cited for traceability: ClearBank Group Holdings Limited's own stub-period Consolidated statement of changes in equity (in the filing above) runs from £(812)k total equity at 1 March 2023 (its own first reporting date) to exactly £196,497k at 31 December 2023 - i.e. this workbook's existing FY2024 opening figure is that entity's own closing balance for its first, ~10-month accounting period, built mostly from a £179,405k share capital issuance (the mechanism for the ClearBank Limited acquisition) rather than organic trading profit. This bridging period is not added as its own column here since it doesn't align with this workbook's FY-year grid, but the £196,497k figure is now independently verified against its true source rather than only appearing as an unexplained opening balance. Balance Sheet and P&amp;L totals for each year are still internally consistent (assets = liabilities + equity; income - expenses = profit/loss) since each is a same-entity, same-year snapshot - only the cross-year equity roll-forward is affected. FY2023's own Statement of Financial Position/Comprehensive Income are Company-only (ClearBank Limited did not publish Consolidated statements that year - see the Company vs Consolidated presentation note below); FY2021/FY2022/FY2024/FY2025 are Consolidated. Per project convention, each year's own originally-published figures are used throughout (FY2022's own AR2022 Consolidated figures, not AR2023's restated comparative - see CASH_FLOW_SOURCES' existing ENTITY_NOTE for the same convention applied to Cash Flow).
+PRESENTATION NOTE: FY2021's own Statement of Comprehensive Income discloses only Net interest income and Net fee income (no separate Interest income/expense or Fee income/expense split) - per AR2022's own footnote, "In 2021, only net interest income and net fee income were presented without splitting for gross amounts." FY2023's own Statement of Comprehensive Income additionally has an "Expenses recharged" line (income, not cost) not present in any other year, resulting in a positive "Operating profit" that year rather than the "Operating loss" label used elsewhere - both reproduced as reported. Balance Sheet: "Loans and advances to banks" (an interbank placement, not a customer loan) appears as its own line FY2021-FY2023 only - dropped from FY2024/FY2025's presentation (folded into Cash and cash equivalents per the Group's own accounting policy note). "Due from UK tax authorities" (FY2022/FY2023) and "Current tax asset" (FY2024/FY2025) are the same concept under different labels; FY2021 has neither line. Equity: "Share-based payment reserve" (FY2021/FY2022) was replaced by "Capital contribution reserve" from FY2023 onward (see the entity-change note above); "Treasury shares" and "Translation reserve" are absent from FY2023's Company-only presentation, present in every other year's Consolidated presentation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A31:F31"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank — Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000, chronological. Contains a genuine entity-basis break at FY2023/FY2024 - see the notes rows and source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Share premium</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Treasury shares</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Share-based payment reserve</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Capital contribution reserve</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings/(losses)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Translation reserve</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>At 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n">
+        <v>157316</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-204</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>9519</v>
+      </c>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n">
+        <v>-108268</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>58247</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year (FY2021)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n">
+        <v>-28200</v>
+      </c>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n">
+        <v>-28200</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss (FY2021)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Issue of share capital (FY2021)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n">
+        <v>34500</v>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n">
+        <v>34500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payments (FY2021)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n">
+        <v>7671</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n">
+        <v>7671</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n">
+        <v>191816</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-204</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>17190</v>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n">
+        <v>-136468</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>72217</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year (FY2022)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n">
+        <v>6818</v>
+      </c>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n">
+        <v>6818</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (FY2022)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Issue of share capital (FY2022)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n">
+        <v>533</v>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payments (FY2022)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n">
+        <v>7743</v>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n">
+        <v>7743</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n">
+        <v>192349</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-204</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>24933</v>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n">
+        <v>-129650</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>87312</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Note: FY2023's own report is Company-only - Treasury shares/Translation reserve columns are not disclosed that year (see Presentation Note); the FY2022 closing balance it re-presents (£87,312k Total) matches the Consolidated total above exactly.</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year (FY2023)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n">
+        <v>22396</v>
+      </c>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n">
+        <v>22396</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Issue of share capital (FY2023)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n">
+        <v>11300</v>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n">
+        <v>11300</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payments and reserve transfer (FY2023)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n">
+        <v>-21408</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>26805</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1332</v>
+      </c>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n">
+        <v>6729</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Tax on share-based payments (FY2023)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n">
+        <v>1789</v>
+      </c>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n">
+        <v>203445</v>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n">
+        <v>26805</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>-100724</v>
+      </c>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n">
+        <v>129526</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>ENTITY-CHANGE NOTE: a new intermediate parent, ClearBank Group Holdings Limited, was inserted above ClearBank Limited during FY2023 (business combination under common control, consolidated from 1 May 2023 - see Sources below) - the FY2024 opening balance is that new entity's own closing balance for its first reporting period (to 31 Dec 2023), not a continuation of the row above.</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>At 1 January 2024</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>189403</v>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n">
+        <v>3511</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>3598</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-17</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>196497</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year (FY2024)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n">
+        <v>-10318</v>
+      </c>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n">
+        <v>-10318</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss (FY2024)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n">
+        <v>-767</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>-767</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Issue of share capital (FY2024)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n">
+        <v>35000</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payments (FY2024)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n">
+        <v>5677</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n">
+        <v>5753</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Tax on share-based payments (FY2024)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n">
+        <v>-3874</v>
+      </c>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n">
+        <v>-3874</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>224403</v>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n">
+        <v>9188</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-10518</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-784</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>222291</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year (FY2025)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n">
+        <v>-15765</v>
+      </c>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n">
+        <v>-15765</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (FY2025)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n">
+        <v>1788</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payments (FY2025)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n">
+        <v>2754</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-1187</v>
+      </c>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Tax on share-based payments (FY2025)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n">
+        <v>2958</v>
+      </c>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n">
+        <v>2958</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2025</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>224403</v>
+      </c>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n">
+        <v>11942</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>-24512</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>1004</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>212839</v>
+      </c>
+    </row>
+    <row r="35" ht="380" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank's own Statement of Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, transcribed from each year's own report:
+FY2025/FY2024: Consolidated statements, ClearBank Group Holdings Limited Annual Report and Accounts 2025, pp.68-70 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2025.pdf
+FY2023: Company statements (no Consolidated statements published that year), ClearBank Annual Report and Accounts 2023, pp.69-72 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts-2023.pdf
+FY2022: Consolidated statements, own originally-published figures (not FY2023's restated comparative - see Note 32 of the FY2023 report), ClearBank Annual Report and Accounts 2022, pp.80-83 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts_2022.pdf
+FY2021: Consolidated statements, ClearBank Limited Annual Report and Accounts 2021, pp.60-63 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2021.pdf
+ENTITY-CHANGE NOTE (corrected on follow-up review against ClearBank Group Holdings Limited's own FY2023 Companies House filing, company 14254435): FY2021-FY2023 figures are ClearBank Limited's own statements (Companies House 09736376). FY2024/FY2025 figures are instead from the Annual Report and Accounts 2025, whose auditor's report and Statement of Financial Position are addressed to "ClearBank Group Holdings Limited" - a NEW intermediate holding entity (incorporated 25 July 2022) inserted above ClearBank Limited DURING FY2023, not between FY2023 and FY2024 as an earlier pass of this workbook stated. Per that entity's own first Group accounts (period ended 31 December 2023, filed at Companies House 18 May 2024 - https://find-and-update.company-information.service.gov.uk/company/14254435/filing-history/MzQyMTUzMzg4NGFkaXF6a2N4/document?format=pdf&amp;download=0), its inaugural subsidiary ClearBank Europe N.V. was incorporated 6 March 2023; it acquired 100% of ClearBank Limited on 8 December 2023 as a Business Combination Under Common Control, with ClearBank Limited's results consolidated from 1 May 2023 (the day after common control was established, 30 April 2023). "CB Growth Holdings Limited" (named in AR2023's own equity note 3, and confirmed in ClearBank Group Holdings Limited's own Note 1.4 as "its parent") is a GENUINELY SEPARATE, higher entity in the group chain - not an earlier name for ClearBank Group Holdings Limited (no Companies House previous-names record exists for company 14254435, and its own filing history shows no rename). The corrected chain, top to bottom, is: CB Growth Holdings Limited -&gt; ClearBank Group Holdings Limited (14254435) -&gt; ClearBank Limited. This is a genuine change of reporting entity, not a presentation choice: the Statement of Changes in Equity's FY2024 opening balance (£196,497k) does not equal FY2023's own closing balance (£129,526k) below, and the two entities' equity bases are not directly comparable, so no plug/bridging row is used across that boundary in this sheet. However, a genuine bridge DOES exist and is now cited for traceability: ClearBank Group Holdings Limited's own stub-period Consolidated statement of changes in equity (in the filing above) runs from £(812)k total equity at 1 March 2023 (its own first reporting date) to exactly £196,497k at 31 December 2023 - i.e. this workbook's existing FY2024 opening figure is that entity's own closing balance for its first, ~10-month accounting period, built mostly from a £179,405k share capital issuance (the mechanism for the ClearBank Limited acquisition) rather than organic trading profit. This bridging period is not added as its own column here since it doesn't align with this workbook's FY-year grid, but the £196,497k figure is now independently verified against its true source rather than only appearing as an unexplained opening balance. Balance Sheet and P&amp;L totals for each year are still internally consistent (assets = liabilities + equity; income - expenses = profit/loss) since each is a same-entity, same-year snapshot - only the cross-year equity roll-forward is affected. FY2023's own Statement of Financial Position/Comprehensive Income are Company-only (ClearBank Limited did not publish Consolidated statements that year - see the Company vs Consolidated presentation note below); FY2021/FY2022/FY2024/FY2025 are Consolidated. Per project convention, each year's own originally-published figures are used throughout (FY2022's own AR2022 Consolidated figures, not AR2023's restated comparative - see CASH_FLOW_SOURCES' existing ENTITY_NOTE for the same convention applied to Cash Flow).
+PRESENTATION NOTE: FY2021's own Statement of Comprehensive Income discloses only Net interest income and Net fee income (no separate Interest income/expense or Fee income/expense split) - per AR2022's own footnote, "In 2021, only net interest income and net fee income were presented without splitting for gross amounts." FY2023's own Statement of Comprehensive Income additionally has an "Expenses recharged" line (income, not cost) not present in any other year, resulting in a positive "Operating profit" that year rather than the "Operating loss" label used elsewhere - both reproduced as reported. Balance Sheet: "Loans and advances to banks" (an interbank placement, not a customer loan) appears as its own line FY2021-FY2023 only - dropped from FY2024/FY2025's presentation (folded into Cash and cash equivalents per the Group's own accounting policy note). "Due from UK tax authorities" (FY2022/FY2023) and "Current tax asset" (FY2024/FY2025) are the same concept under different labels; FY2021 has neither line. Equity: "Share-based payment reserve" (FY2021/FY2022) was replaced by "Capital contribution reserve" from FY2023 onward (see the entity-change note above); "Treasury shares" and "Translation reserve" are absent from FY2023's Company-only presentation, present in every other year's Consolidated presentation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A35:I35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2815,16 +6637,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2835,421 +6657,167 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — CET1 Capital</t>
+          <t>ClearBank — Asset Quality / Credit Risk Disclosures</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>£'000. ClearBank does not lend to customers - see the structural finding in the source note below.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 (£'000)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 (£'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 (£'000)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 (£'000)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2021 (£'000)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>132</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>141</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>126</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>36.7</v>
-      </c>
-    </row>
-    <row r="6" ht="190" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
-FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
-FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Loan book</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Customer loans and advances</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Loss allowance on customer loans</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Interbank treasury placements ('Loans and advances to banks')</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Carrying amount</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n">
+        <v>19525</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>9156</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>5962</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Loss allowance recognised</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="280" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank's own "Credit risk" and "Impairment of financial assets" notes (Note 21/2.6), read in full for all 5 years:
+FY2025/FY2024: ClearBank Group Holdings Limited Annual Report and Accounts 2025, pp.77,88 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2025.pdf
+FY2023: ClearBank Annual Report and Accounts 2023, credit risk/impairment notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts-2023.pdf
+FY2022/FY2021: ClearBank Annual Report and Accounts 2022, credit risk/impairment notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts_2022.pdf
+GENUINE STRUCTURAL FINDING, NOT A DATA GAP: ClearBank does not lend to customers at all. Its own FY2025 Annual Report states plainly: "The Group does not provide any credit facilities which are not fully collateralised to its customers and is therefore not exposed to associated credit risks" and "the Group's trade receivables and hence ECL are immaterial, with no further ECL-related disclosures considered necessary by management." This wording (or its equivalent) recurs across all 5 years reviewed. There is therefore no customer loan book, no IFRS 9 stage split, and no loss allowance of any kind recognised in any year - ClearBank's only credit exposure is to its treasury counterparties (predominantly the Bank of England) and to collateral it holds FROM clients (an asset-side benefit, not a risk), both deemed low/immaterial risk by the Group's own policy. "Loans and advances to banks" on the Balance Sheet (FY2021-FY2023 only, see Presentation Note on the Balance Sheet sheet) is an interbank treasury placement, not customer lending.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ClearBank Limited — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>% of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>49.75%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>67.02%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>77.45%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>87.66%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>139.70%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="190" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
-FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
-FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ClearBank Limited — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£m (= CET1 capital; no AT1 instruments)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>132</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>141</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>126</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>36.7</v>
-      </c>
-    </row>
-    <row r="6" ht="190" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
-FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
-FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ClearBank Limited — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>% of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>49.75%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>67.02%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>77.45%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>87.66%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>139.70%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="190" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
-FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
-FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3275,14 +6843,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — Total Capital</t>
+          <t>ClearBank Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m (= CET1 capital; no Tier 2 instruments)</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -3321,7 +6889,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
+          <t>Common Equity Tier 1 (CET1) capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
@@ -3380,7 +6948,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — Total Capital Ratio</t>
+          <t>ClearBank Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -3426,7 +6994,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
+          <t>Common Equity Tier 1 ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3495,14 +7063,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — Total RWAs</t>
+          <t>ClearBank Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>£m (= CET1 capital; no AT1 instruments)</t>
         </is>
       </c>
     </row>
@@ -3541,23 +7109,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
+          <t>Tier 1 capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>266</v>
+        <v>132</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>211</v>
+        <v>141</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>26</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="6" ht="190" customHeight="1">

--- a/banks/CLEARBANK FINANCIALS.xlsx
+++ b/banks/CLEARBANK FINANCIALS.xlsx
@@ -236,7 +236,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!I6</f>
+              <f>'Overview'!M6</f>
             </strRef>
           </tx>
           <spPr>
@@ -246,12 +246,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$N$5:$V$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$6:$N$6</f>
+              <f>'Overview'!$N$6:$V$6</f>
             </numRef>
           </val>
         </ser>
@@ -260,7 +260,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!I7</f>
+              <f>'Overview'!M7</f>
             </strRef>
           </tx>
           <spPr>
@@ -270,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$N$5:$V$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$7:$N$7</f>
+              <f>'Overview'!$N$7:$V$7</f>
             </numRef>
           </val>
         </ser>
@@ -284,7 +284,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!I8</f>
+              <f>'Overview'!M8</f>
             </strRef>
           </tx>
           <spPr>
@@ -294,12 +294,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$N$5:$V$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$8:$N$8</f>
+              <f>'Overview'!$N$8:$V$8</f>
             </numRef>
           </val>
         </ser>
@@ -410,7 +410,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q12</f>
+              <f>'Overview'!Y12</f>
             </strRef>
           </tx>
           <spPr>
@@ -420,12 +420,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$11:$V$11</f>
+              <f>'Overview'!$Z$11:$AH$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$Z$12:$AH$12</f>
             </numRef>
           </val>
         </ser>
@@ -434,7 +434,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q13</f>
+              <f>'Overview'!Y13</f>
             </strRef>
           </tx>
           <spPr>
@@ -444,12 +444,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$11:$V$11</f>
+              <f>'Overview'!$Z$11:$AH$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$13:$V$13</f>
+              <f>'Overview'!$Z$13:$AH$13</f>
             </numRef>
           </val>
         </ser>
@@ -458,7 +458,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q14</f>
+              <f>'Overview'!Y14</f>
             </strRef>
           </tx>
           <spPr>
@@ -468,12 +468,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$11:$V$11</f>
+              <f>'Overview'!$Z$11:$AH$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$14:$V$14</f>
+              <f>'Overview'!$Z$14:$AH$14</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y18</f>
+              <f>'Overview'!AK18</f>
             </strRef>
           </tx>
           <spPr>
@@ -594,12 +594,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$17:$AD$17</f>
+              <f>'Overview'!$AL$17:$AT$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AL$18:$AT$18</f>
             </numRef>
           </val>
         </ser>
@@ -608,7 +608,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y19</f>
+              <f>'Overview'!AK19</f>
             </strRef>
           </tx>
           <spPr>
@@ -618,12 +618,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$17:$AD$17</f>
+              <f>'Overview'!$AL$17:$AT$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$19:$AD$19</f>
+              <f>'Overview'!$AL$19:$AT$19</f>
             </numRef>
           </val>
         </ser>
@@ -632,7 +632,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y20</f>
+              <f>'Overview'!AK20</f>
             </strRef>
           </tx>
           <spPr>
@@ -642,12 +642,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$17:$AD$17</f>
+              <f>'Overview'!$AL$17:$AT$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$20:$AD$20</f>
+              <f>'Overview'!$AL$20:$AT$20</f>
             </numRef>
           </val>
         </ser>
@@ -656,7 +656,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y21</f>
+              <f>'Overview'!AK21</f>
             </strRef>
           </tx>
           <spPr>
@@ -666,12 +666,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$17:$AD$17</f>
+              <f>'Overview'!$AL$17:$AT$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$21:$AD$21</f>
+              <f>'Overview'!$AL$21:$AT$21</f>
             </numRef>
           </val>
         </ser>
@@ -782,7 +782,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG25</f>
+              <f>'Overview'!AW25</f>
             </strRef>
           </tx>
           <spPr>
@@ -792,12 +792,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$24:$AL$24</f>
+              <f>'Overview'!$AX$24:$BF$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$AX$25:$BF$25</f>
             </numRef>
           </val>
         </ser>
@@ -806,7 +806,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG26</f>
+              <f>'Overview'!AW26</f>
             </strRef>
           </tx>
           <spPr>
@@ -816,12 +816,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$24:$AL$24</f>
+              <f>'Overview'!$AX$24:$BF$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$26:$AL$26</f>
+              <f>'Overview'!$AX$26:$BF$26</f>
             </numRef>
           </val>
         </ser>
@@ -830,7 +830,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG27</f>
+              <f>'Overview'!AW27</f>
             </strRef>
           </tx>
           <spPr>
@@ -840,12 +840,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$24:$AL$24</f>
+              <f>'Overview'!$AX$24:$BF$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$27:$AL$27</f>
+              <f>'Overview'!$AX$27:$BF$27</f>
             </numRef>
           </val>
         </ser>
@@ -854,7 +854,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG28</f>
+              <f>'Overview'!AW28</f>
             </strRef>
           </tx>
           <spPr>
@@ -864,12 +864,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$24:$AL$24</f>
+              <f>'Overview'!$AX$24:$BF$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$28:$AL$28</f>
+              <f>'Overview'!$AX$28:$BF$28</f>
             </numRef>
           </val>
         </ser>
@@ -979,7 +979,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO6</f>
+              <f>'Overview'!BI6</f>
             </strRef>
           </tx>
           <spPr>
@@ -997,12 +997,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BJ$5:$BR$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$6:$AT$6</f>
+              <f>'Overview'!$BJ$6:$BR$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1012,7 +1012,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO7</f>
+              <f>'Overview'!BI7</f>
             </strRef>
           </tx>
           <spPr>
@@ -1030,12 +1030,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BJ$5:$BR$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$7:$AT$7</f>
+              <f>'Overview'!$BJ$7:$BR$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1045,7 +1045,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO8</f>
+              <f>'Overview'!BI8</f>
             </strRef>
           </tx>
           <spPr>
@@ -1063,12 +1063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BJ$5:$BR$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$8:$AT$8</f>
+              <f>'Overview'!$BJ$8:$BR$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1543,7 +1543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT36"/>
+  <dimension ref="A1:BR36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1552,10 +1552,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
-    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
-    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
-    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
     <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
@@ -1590,6 +1590,30 @@
     <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
     <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
     <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
+    <col hidden="1" width="13" customWidth="1" min="47" max="47"/>
+    <col hidden="1" width="13" customWidth="1" min="48" max="48"/>
+    <col hidden="1" width="13" customWidth="1" min="49" max="49"/>
+    <col hidden="1" width="13" customWidth="1" min="50" max="50"/>
+    <col hidden="1" width="13" customWidth="1" min="51" max="51"/>
+    <col hidden="1" width="13" customWidth="1" min="52" max="52"/>
+    <col hidden="1" width="13" customWidth="1" min="53" max="53"/>
+    <col hidden="1" width="13" customWidth="1" min="54" max="54"/>
+    <col hidden="1" width="13" customWidth="1" min="55" max="55"/>
+    <col hidden="1" width="13" customWidth="1" min="56" max="56"/>
+    <col hidden="1" width="13" customWidth="1" min="57" max="57"/>
+    <col hidden="1" width="13" customWidth="1" min="58" max="58"/>
+    <col hidden="1" width="13" customWidth="1" min="59" max="59"/>
+    <col hidden="1" width="13" customWidth="1" min="60" max="60"/>
+    <col hidden="1" width="13" customWidth="1" min="61" max="61"/>
+    <col hidden="1" width="13" customWidth="1" min="62" max="62"/>
+    <col hidden="1" width="13" customWidth="1" min="63" max="63"/>
+    <col hidden="1" width="13" customWidth="1" min="64" max="64"/>
+    <col hidden="1" width="13" customWidth="1" min="65" max="65"/>
+    <col hidden="1" width="13" customWidth="1" min="66" max="66"/>
+    <col hidden="1" width="13" customWidth="1" min="67" max="67"/>
+    <col hidden="1" width="13" customWidth="1" min="68" max="68"/>
+    <col hidden="1" width="13" customWidth="1" min="69" max="69"/>
+    <col hidden="1" width="13" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1644,52 +1668,112 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1716,44 +1800,80 @@
       <c r="F6" s="5" t="n">
         <v>2772608</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="G6" s="5" t="n">
+        <v>1052971</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>562825</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>87456</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>40015</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="N6" t="n">
+        <v>40015</v>
+      </c>
+      <c r="O6" t="n">
+        <v>87456</v>
+      </c>
+      <c r="P6" t="n">
+        <v>562825</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1052971</v>
+      </c>
+      <c r="R6" t="n">
         <v>2772608</v>
       </c>
-      <c r="K6" t="n">
+      <c r="S6" t="n">
         <v>3204409</v>
       </c>
-      <c r="L6" t="n">
+      <c r="T6" t="n">
         <v>6366850</v>
       </c>
-      <c r="M6" t="n">
+      <c r="U6" t="n">
         <v>11064063</v>
       </c>
-      <c r="N6" t="n">
+      <c r="V6" t="n">
         <v>18068355</v>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="BJ6" t="n">
+        <v>53</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>35</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>88</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="BN6" t="n">
         <v>139.7</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="BO6" t="n">
         <v>87.66</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="BP6" t="n">
         <v>77.45</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="BQ6" t="n">
         <v>67.02</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BR6" t="n">
         <v>49.75</v>
       </c>
     </row>
@@ -1778,44 +1898,80 @@
       <c r="F7" s="5" t="n">
         <v>2644756</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" s="5" t="n">
+        <v>925890</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>457981</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>44145</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1601</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Customer deposits</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="N7" t="n">
+        <v>1601</v>
+      </c>
+      <c r="O7" t="n">
+        <v>44145</v>
+      </c>
+      <c r="P7" t="n">
+        <v>457981</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>925890</v>
+      </c>
+      <c r="R7" t="n">
         <v>2644756</v>
       </c>
-      <c r="K7" t="n">
+      <c r="S7" t="n">
         <v>2982259</v>
       </c>
-      <c r="L7" t="n">
+      <c r="T7" t="n">
         <v>6147363</v>
       </c>
-      <c r="M7" t="n">
+      <c r="U7" t="n">
         <v>10818568</v>
       </c>
-      <c r="N7" t="n">
+      <c r="V7" t="n">
         <v>17826803</v>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="BJ7" t="n">
+        <v>84</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>74</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>30</v>
+      </c>
+      <c r="BN7" t="n">
         <v>38.79</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="BO7" t="n">
         <v>13.87</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BP7" t="n">
         <v>43.51</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BQ7" t="n">
         <v>26.07</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BR7" t="n">
         <v>20.05</v>
       </c>
     </row>
@@ -1840,44 +1996,80 @@
       <c r="F8" s="5" t="n">
         <v>72217</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="G8" s="5" t="n">
+        <v>58247</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>40242</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>36908</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>34047</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="N8" t="n">
+        <v>34047</v>
+      </c>
+      <c r="O8" t="n">
+        <v>36908</v>
+      </c>
+      <c r="P8" t="n">
+        <v>40242</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>58247</v>
+      </c>
+      <c r="R8" t="n">
         <v>72217</v>
       </c>
-      <c r="K8" t="n">
+      <c r="S8" t="n">
         <v>87312</v>
       </c>
-      <c r="L8" t="n">
+      <c r="T8" t="n">
         <v>129526</v>
       </c>
-      <c r="M8" t="n">
+      <c r="U8" t="n">
         <v>222291</v>
       </c>
-      <c r="N8" t="n">
+      <c r="V8" t="n">
         <v>212839</v>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="BJ8" t="n">
+        <v>3718</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>237</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>127</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>186</v>
+      </c>
+      <c r="BN8" t="n">
         <v>185.94</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="BO8" t="n">
         <v>297.05</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BP8" t="n">
         <v>445.36</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BQ8" t="n">
         <v>381.88</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BR8" t="n">
         <v>396.85</v>
       </c>
     </row>
@@ -1919,27 +2111,67 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1966,24 +2198,48 @@
       <c r="F12" s="5" t="n">
         <v>21394</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="G12" s="5" t="n">
+        <v>10618</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>5318</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>838</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Total income</t>
         </is>
       </c>
-      <c r="R12" t="n">
+      <c r="Z12" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>838</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>5318</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10618</v>
+      </c>
+      <c r="AD12" t="n">
         <v>21394</v>
       </c>
-      <c r="S12" t="n">
+      <c r="AE12" t="n">
         <v>58284</v>
       </c>
-      <c r="T12" t="n">
+      <c r="AF12" t="n">
         <v>111347</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AG12" t="n">
         <v>112086</v>
       </c>
-      <c r="V12" t="n">
+      <c r="AH12" t="n">
         <v>132684</v>
       </c>
     </row>
@@ -2008,24 +2264,48 @@
       <c r="F13" s="5" t="n">
         <v>-52439</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="G13" s="5" t="n">
+        <v>-41283</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>-39092</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>-30371</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>-17597</v>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="Z13" t="n">
+        <v>-17597</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-30371</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-39092</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-41283</v>
+      </c>
+      <c r="AD13" t="n">
         <v>-52439</v>
       </c>
-      <c r="S13" t="n">
+      <c r="AE13" t="n">
         <v>-77638</v>
       </c>
-      <c r="T13" t="n">
+      <c r="AF13" t="n">
         <v>-105783</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AG13" t="n">
         <v>-122035</v>
       </c>
-      <c r="V13" t="n">
+      <c r="AH13" t="n">
         <v>-148934</v>
       </c>
     </row>
@@ -2050,24 +2330,48 @@
       <c r="F14" s="5" t="n">
         <v>-28200</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="G14" s="5" t="n">
+        <v>-29796</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>-33996</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>-24844</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>-13899</v>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Profit/(loss) for the year after taxation</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="Z14" t="n">
+        <v>-13899</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-24844</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-33996</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-29796</v>
+      </c>
+      <c r="AD14" t="n">
         <v>-28200</v>
       </c>
-      <c r="S14" t="n">
+      <c r="AE14" t="n">
         <v>6818</v>
       </c>
-      <c r="T14" t="n">
+      <c r="AF14" t="n">
         <v>22396</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AG14" t="n">
         <v>-10318</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AH14" t="n">
         <v>-15765</v>
       </c>
     </row>
@@ -2109,27 +2413,67 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AQ17" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AR17" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AS17" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AT17" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2156,24 +2500,48 @@
       <c r="F18" s="5" t="n">
         <v>58247</v>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="G18" s="5" t="n">
+        <v>40242</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>36908</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>34047</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>19479</v>
+      </c>
+      <c r="AK18" t="inlineStr">
         <is>
           <t>Opening equity</t>
         </is>
       </c>
-      <c r="Z18" t="n">
+      <c r="AL18" t="n">
+        <v>19479</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>34047</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>36908</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>40242</v>
+      </c>
+      <c r="AP18" t="n">
         <v>58247</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AQ18" t="n">
         <v>72217</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AR18" t="n">
         <v>87312</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AS18" t="n">
         <v>196497</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AT18" t="n">
         <v>222291</v>
       </c>
     </row>
@@ -2198,24 +2566,48 @@
       <c r="F19" s="5" t="n">
         <v>-28201</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="G19" s="5" t="n">
+        <v>-29903</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>-33963</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>-24844</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>-13899</v>
+      </c>
+      <c r="AK19" t="inlineStr">
         <is>
           <t>Total comprehensive income/(loss) for the year</t>
         </is>
       </c>
-      <c r="Z19" t="n">
+      <c r="AL19" t="n">
+        <v>-13899</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-24844</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-33963</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-29903</v>
+      </c>
+      <c r="AP19" t="n">
         <v>-28201</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AQ19" t="n">
         <v>6819</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AR19" t="n">
         <v>22396</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AS19" t="n">
         <v>-11085</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AT19" t="n">
         <v>-13977</v>
       </c>
     </row>
@@ -2240,24 +2632,48 @@
       <c r="F20" s="5" t="n">
         <v>42171</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="G20" s="5" t="n">
+        <v>47908</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>37297</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>27705</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>28467</v>
+      </c>
+      <c r="AK20" t="inlineStr">
         <is>
           <t>Other equity movements, net</t>
         </is>
       </c>
-      <c r="Z20" t="n">
+      <c r="AL20" t="n">
+        <v>28467</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>27705</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>37297</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>47908</v>
+      </c>
+      <c r="AP20" t="n">
         <v>42171</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AQ20" t="n">
         <v>8276</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AR20" t="n">
         <v>19818</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AS20" t="n">
         <v>36879</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AT20" t="n">
         <v>4525</v>
       </c>
     </row>
@@ -2282,24 +2698,48 @@
       <c r="F21" s="5" t="n">
         <v>72217</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="G21" s="5" t="n">
+        <v>58247</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>40242</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>36908</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>34047</v>
+      </c>
+      <c r="AK21" t="inlineStr">
         <is>
           <t>Closing equity</t>
         </is>
       </c>
-      <c r="Z21" t="n">
+      <c r="AL21" t="n">
+        <v>34047</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>36908</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>40242</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>58247</v>
+      </c>
+      <c r="AP21" t="n">
         <v>72217</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AQ21" t="n">
         <v>87312</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AR21" t="n">
         <v>129526</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AS21" t="n">
         <v>222291</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AT21" t="n">
         <v>212839</v>
       </c>
     </row>
@@ -2341,27 +2781,67 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AH24" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="BC24" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
+      <c r="BD24" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AK24" t="inlineStr">
+      <c r="BE24" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
+      <c r="BF24" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2388,24 +2868,48 @@
       <c r="F25" s="5" t="n">
         <v>1683715</v>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="G25" s="5" t="n">
+        <v>453624</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>439707</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>19481</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>-13651</v>
+      </c>
+      <c r="AW25" t="inlineStr">
         <is>
           <t>Net cash from operating activities</t>
         </is>
       </c>
-      <c r="AH25" t="n">
+      <c r="AX25" t="n">
+        <v>-13651</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>19481</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>439707</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>453624</v>
+      </c>
+      <c r="BB25" t="n">
         <v>1683715</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="BC25" t="n">
         <v>413627</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="BD25" t="n">
         <v>3142548</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="BE25" t="n">
         <v>4690772</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="BF25" t="n">
         <v>7017191</v>
       </c>
     </row>
@@ -2430,24 +2934,48 @@
       <c r="F26" s="5" t="n">
         <v>-8624</v>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="G26" s="5" t="n">
+        <v>-8448</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>-8835</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>-8887</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>-5670</v>
+      </c>
+      <c r="AW26" t="inlineStr">
         <is>
           <t>Net cash used in investing activities</t>
         </is>
       </c>
-      <c r="AH26" t="n">
+      <c r="AX26" t="n">
+        <v>-5670</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>-8887</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>-8835</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>-8448</v>
+      </c>
+      <c r="BB26" t="n">
         <v>-8624</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="BC26" t="n">
         <v>-8144</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="BD26" t="n">
         <v>-21778</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="BE26" t="n">
         <v>-24096</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="BF26" t="n">
         <v>-15684</v>
       </c>
     </row>
@@ -2472,24 +3000,48 @@
       <c r="F27" s="5" t="n">
         <v>32492</v>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="G27" s="5" t="n">
+        <v>41462</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>33195</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>24871</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>27908</v>
+      </c>
+      <c r="AW27" t="inlineStr">
         <is>
           <t>Net cash from/(used in) financing activities</t>
         </is>
       </c>
-      <c r="AH27" t="n">
+      <c r="AX27" t="n">
+        <v>27908</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>24871</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>33195</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>41462</v>
+      </c>
+      <c r="BB27" t="n">
         <v>32492</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="BC27" t="n">
         <v>-384</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="BD27" t="n">
         <v>9537</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="BE27" t="n">
         <v>33433</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="BF27" t="n">
         <v>-1603</v>
       </c>
     </row>
@@ -2514,24 +3066,48 @@
       <c r="F28" s="5" t="n">
         <v>2720797</v>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="G28" s="5" t="n">
+        <v>1013224</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>526594</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>62527</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>27062</v>
+      </c>
+      <c r="AW28" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at end of year</t>
         </is>
       </c>
-      <c r="AH28" t="n">
+      <c r="AX28" t="n">
+        <v>27062</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>62527</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>526594</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1013224</v>
+      </c>
+      <c r="BB28" t="n">
         <v>2720797</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="BC28" t="n">
         <v>3125862</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="BD28" t="n">
         <v>6256126</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="BE28" t="n">
         <v>10961293</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="BF28" t="n">
         <v>17956976</v>
       </c>
     </row>
@@ -2573,6 +3149,26 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -2605,6 +3201,26 @@
           <t>139.70%</t>
         </is>
       </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>114.20%</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -2637,6 +3253,26 @@
           <t>38.79%</t>
         </is>
       </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -2669,17 +3305,37 @@
           <t>185.94%</t>
         </is>
       </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>186%</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>127%</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>237%</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>3718%</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="45" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Statement of Changes in Equity Summary: FY2024's Opening equity is a new ultimate parent entity's own balance (ClearBank Group Holdings Limited, inserted above ClearBank Limited during FY2024), not a continuation of FY2023's Closing equity - see the Statement of Changes in Equity sheet for the full entity-change note. NSFR omitted from this chart (values in the thousands of percent would flatten every other series) - see the NSFR sheet directly.</t>
+          <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Statement of Changes in Equity Summary: FY2024's Opening equity is a new ultimate parent entity's own balance (ClearBank Group Holdings Limited, inserted above ClearBank Limited during FY2024), not a continuation of FY2023's Closing equity - see the Statement of Changes in Equity sheet for the full entity-change note. NSFR omitted from this chart (values in the thousands of percent would flatten every other series) - see the NSFR sheet directly. HD-019: this workbook's year range now extends back to FY2017, ClearBank's independently-verified floor (first year with any customer deposits/income, following the bank's actual opening to customers in October 2017) - not FY2015, which an earlier ticket-generation pass had assumed purely from the entity's GLEIF incorporation date. See the HD-019 FLOOR VERIFICATION comment block near the top of build_clearbank.py and the Balance Sheet sheet's Sources note for the full evidence trail.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A36:J36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2692,7 +3348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2701,6 +3357,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2748,6 +3408,26 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2778,6 +3458,26 @@
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>139.70%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>114.20%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>53%</t>
         </is>
       </c>
     </row>
@@ -2788,14 +3488,19 @@
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2807,7 +3512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2816,6 +3521,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2863,6 +3572,26 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2884,6 +3613,18 @@
       </c>
       <c r="F4" s="6" t="n">
         <v>36.7</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>29.952</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>17.461</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>23.681</v>
       </c>
     </row>
     <row r="6" ht="190" customHeight="1">
@@ -2893,14 +3634,19 @@
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2912,7 +3658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2921,6 +3667,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2968,6 +3718,26 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2998,6 +3768,26 @@
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>139.70%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>114.20%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>53%</t>
         </is>
       </c>
     </row>
@@ -3008,14 +3798,19 @@
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3027,7 +3822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3036,6 +3831,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3083,6 +3882,26 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3105,6 +3924,12 @@
       <c r="F4" s="6" t="n">
         <v>26</v>
       </c>
+      <c r="G4" s="6" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
     </row>
     <row r="6" ht="190" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -3113,14 +3938,19 @@
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3132,7 +3962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3141,6 +3971,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3186,6 +4020,26 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£'000)</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£'000)</t>
         </is>
       </c>
     </row>
@@ -3200,6 +4054,10 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3222,6 +4080,18 @@
       <c r="F5" s="6" t="n">
         <v>17000</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>17450</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>15664</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>9184</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>2366</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3244,6 +4114,12 @@
       <c r="F6" s="6" t="n">
         <v>9000</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>8750</v>
+      </c>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -3266,6 +4142,12 @@
       <c r="F7" s="5" t="n">
         <v>26000</v>
       </c>
+      <c r="G7" s="5" t="n">
+        <v>26200</v>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
     </row>
     <row r="9" ht="340" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
@@ -3275,6 +4157,10 @@
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.11 (ClearBank Group column) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022: ClearBank Pillar 3 disclosure 2022, p.15 (own originally-published figures, not FY2023's restated comparative - see note below) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf
 FY2021: ClearBank Pillar 3 disclosure 2022, p.15 (FY2021 comparative column) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf
+FY2020: derived from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column - Total RWA £26.2m (COREP own-funds template, line 60) and Operational risk Pillar 1 capital requirement £0.7m (implying Operational RWA = £0.7m / 8% = £8.75m by definition); Credit risk RWA (£17.45m) is the residual (Total - Operational), not itself a directly-disclosed single line item - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: Credit risk RWA (£15,664k) is ClearBank's own explicitly-disclosed "credit risk exposure by asset and exposure class" table (ClearBank Annual Report and Accounts 2019, financial review section) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf. No operational-risk RWA or Total RWA figure is disclosed anywhere in the FY2019 Annual Report, so Operational risk and Total RWAs are left blank for FY2019 rather than estimated.
+FY2018: Credit risk RWA (£9,184k) is ClearBank's own explicitly-disclosed credit risk exposure table (ClearBank Limited 2018 Annual Report, p.22) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf. Same gap as FY2019: no operational-risk RWA or Total RWA disclosed, left blank.
+FY2017: Credit risk RWA (£2,366k) is ClearBank's own explicitly-disclosed credit risk exposure table (ClearBank Limited 2017 Annual Report, p.19) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf. Same gap: no operational-risk RWA or Total RWA disclosed, left blank.
 Only two risk categories are disclosed in any year: Credit risk (excluding CCR, Standardised Approach) and Operational risk (Basic Indicator Approach) - no market risk, CCR, or CVA charge in any year (consistent with a clearing/embedded-banking bank with no trading book).
 FY2024's Total here (£212m = £34m + £178m) is £1m higher than the FY2024 figure on this workbook's own Total RWAs sheet (£211m) - an immaterial rounding artifact in ClearBank's own Pillar 3 table, reproduced as disclosed rather than force-matched.
 RESTATEMENT NOTE: ClearBank's own FY2022 Pillar 3 disclosure (2022 edition) states Operational risk RWA of £22m (Total £38m), matching this workbook's existing Total RWAs sheet. The FY2023 Pillar 3 disclosure's own FY2022 comparative column instead shows Operational risk RWA of £55m (Total £71m) - a large restatement between Pillar 3 vintages with no explanation given. Per project convention, FY2022's own originally-published figures (£16m credit / £22m operational / £38m total) are used here, not the later restated comparative.</t>
@@ -3283,7 +4169,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A9:J9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3295,7 +4181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3304,6 +4190,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3351,6 +4241,26 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3381,6 +4291,26 @@
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>38.79%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>84%</t>
         </is>
       </c>
     </row>
@@ -3398,15 +4328,20 @@
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A7:J7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3418,7 +4353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3427,6 +4362,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3474,6 +4413,26 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3504,6 +4463,26 @@
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>185.94%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>186%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>127%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>237%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>3718%</t>
         </is>
       </c>
     </row>
@@ -3514,14 +4493,19 @@
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3533,7 +4517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3542,6 +4526,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3589,6 +4577,26 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3619,6 +4627,26 @@
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>11701.32%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>3298%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>324%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>432%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>878%</t>
         </is>
       </c>
     </row>
@@ -3636,15 +4664,20 @@
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A7:J7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3656,7 +4689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3665,6 +4698,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3708,6 +4745,26 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3740,11 +4797,31 @@
           <t>Not publicly disclosed</t>
         </is>
       </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed - no MREL ratio or qualitative MREL statement found in any Pillar 3 document reviewed (FY2021-FY2025), no reason given.</t>
+          <t>Note: Not publicly disclosed - no MREL ratio or qualitative MREL statement found in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.</t>
         </is>
       </c>
     </row>
@@ -3755,15 +4832,20 @@
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A7:J7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3775,7 +4857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3784,6 +4866,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3829,6 +4915,26 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£'000)</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£'000)</t>
         </is>
       </c>
     </row>
@@ -3843,6 +4949,10 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3864,6 +4974,18 @@
       </c>
       <c r="F5" s="6" t="n">
         <v>2720797</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1013224</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>526594</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>62527</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>27062</v>
       </c>
     </row>
     <row r="6">
@@ -3883,6 +5005,10 @@
       <c r="F6" s="6" t="n">
         <v>5962</v>
       </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -3905,6 +5031,18 @@
       <c r="F7" s="6" t="n">
         <v>406</v>
       </c>
+      <c r="G7" s="6" t="n">
+        <v>370</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>315</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -3927,6 +5065,18 @@
       <c r="F8" s="6" t="n">
         <v>4478</v>
       </c>
+      <c r="G8" s="6" t="n">
+        <v>4565</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>3900</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>1487</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1176</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -3947,6 +5097,10 @@
         <v>4363</v>
       </c>
       <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -3969,6 +5123,14 @@
       <c r="F10" s="6" t="n">
         <v>510</v>
       </c>
+      <c r="G10" s="6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>4530</v>
+      </c>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -3991,6 +5153,18 @@
       <c r="F11" s="6" t="n">
         <v>451</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>673</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>351</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>819</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>1082</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4013,6 +5187,18 @@
       <c r="F12" s="6" t="n">
         <v>27479</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>22475</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>18751</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>13924</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>6728</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -4035,6 +5221,18 @@
       <c r="F13" s="6" t="n">
         <v>12525</v>
       </c>
+      <c r="G13" s="6" t="n">
+        <v>9484</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>8335</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>8335</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>3652</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -4056,6 +5254,18 @@
       </c>
       <c r="F14" s="5" t="n">
         <v>2772608</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1052971</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>562825</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>87456</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>40015</v>
       </c>
     </row>
     <row r="15">
@@ -4069,6 +5279,10 @@
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4091,6 +5305,18 @@
       <c r="F16" s="6" t="n">
         <v>2644756</v>
       </c>
+      <c r="G16" s="6" t="n">
+        <v>925890</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>457981</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>44145</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>1601</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4113,6 +5339,18 @@
       <c r="F17" s="6" t="n">
         <v>9897</v>
       </c>
+      <c r="G17" s="6" t="n">
+        <v>6591</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>8570</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>6403</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>4367</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -4135,6 +5373,14 @@
       <c r="F18" s="6" t="n">
         <v>509</v>
       </c>
+      <c r="G18" s="6" t="n">
+        <v>2483</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>4520</v>
+      </c>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -4157,6 +5403,14 @@
       <c r="F19" s="6" t="n">
         <v>45229</v>
       </c>
+      <c r="G19" s="6" t="n">
+        <v>59760</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>51512</v>
+      </c>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -4171,6 +5425,10 @@
       </c>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -4192,6 +5450,18 @@
       </c>
       <c r="F21" s="5" t="n">
         <v>2700391</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>994724</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>522583</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>50548</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>5968</v>
       </c>
     </row>
     <row r="22">
@@ -4205,6 +5475,10 @@
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -4221,6 +5495,10 @@
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -4242,6 +5520,18 @@
       </c>
       <c r="F24" s="6" t="n">
         <v>191816</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>157316</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>113204</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>78329</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>53458</v>
       </c>
     </row>
     <row r="25">
@@ -4259,6 +5549,18 @@
       <c r="F25" s="6" t="n">
         <v>-204</v>
       </c>
+      <c r="G25" s="6" t="n">
+        <v>-204</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-204</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>-204</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>-204</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -4277,6 +5579,10 @@
       </c>
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -4293,6 +5599,18 @@
       <c r="F27" s="6" t="n">
         <v>17190</v>
       </c>
+      <c r="G27" s="6" t="n">
+        <v>9519</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>5723</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>3301</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>467</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -4314,6 +5632,18 @@
       </c>
       <c r="F28" s="6" t="n">
         <v>-136468</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>-108268</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>-78472</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>-44518</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>-19674</v>
       </c>
     </row>
     <row r="29">
@@ -4335,6 +5665,14 @@
       <c r="F29" s="6" t="n">
         <v>-117</v>
       </c>
+      <c r="G29" s="6" t="n">
+        <v>-116</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -4357,6 +5695,18 @@
       <c r="F30" s="5" t="n">
         <v>72217</v>
       </c>
+      <c r="G30" s="5" t="n">
+        <v>58247</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>40242</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>36908</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>34047</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -4378,6 +5728,18 @@
       </c>
       <c r="F31" s="5" t="n">
         <v>2772608</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>1052971</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>562825</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>87456</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>40015</v>
       </c>
     </row>
     <row r="33" ht="380" customHeight="1">
@@ -4388,14 +5750,20 @@
 FY2023: Company statements (no Consolidated statements published that year), ClearBank Annual Report and Accounts 2023, pp.69-72 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts-2023.pdf
 FY2022: Consolidated statements, own originally-published figures (not FY2023's restated comparative - see Note 32 of the FY2023 report), ClearBank Annual Report and Accounts 2022, pp.80-83 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts_2022.pdf
 FY2021: Consolidated statements, ClearBank Limited Annual Report and Accounts 2021, pp.60-63 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2021.pdf
+FY2020: Consolidated statements, ClearBank Limited Annual Report and Accounts 2020, pp.66-70 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf
+FY2019: Consolidated statements, ClearBank Limited Annual Report and Accounts 2019, pp.66-71 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: Consolidated statements, ClearBank Limited 2018 Annual Report, pp.54-58 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: Consolidated statements, ClearBank Limited 2017 Annual Report, pp.46-52 (own-year figures; cross-checked against AR2018's own FY2017 comparative column, which matches exactly - no restatement between vintages for this year) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+FLOOR VERIFICATION NOTE (HD-019): ClearBank Limited was incorporated 17 August 2015, but its first Annual Report covers a 16-month pre-operational stub period (17 Aug 2015 - 31 Dec 2016) with nil customer accounts, nil lending, and nil income throughout - see the HD-019 FLOOR VERIFICATION comment block near the top of this script for the full evidence trail. FY2017 (the first year with any customer deposits or income at all, following the bank's actual opening to customers in October 2017) is the confirmed, independently verified floor for this workbook - not FY2015/FY2016.
 ENTITY-CHANGE NOTE (corrected on follow-up review against ClearBank Group Holdings Limited's own FY2023 Companies House filing, company 14254435): FY2021-FY2023 figures are ClearBank Limited's own statements (Companies House 09736376). FY2024/FY2025 figures are instead from the Annual Report and Accounts 2025, whose auditor's report and Statement of Financial Position are addressed to "ClearBank Group Holdings Limited" - a NEW intermediate holding entity (incorporated 25 July 2022) inserted above ClearBank Limited DURING FY2023, not between FY2023 and FY2024 as an earlier pass of this workbook stated. Per that entity's own first Group accounts (period ended 31 December 2023, filed at Companies House 18 May 2024 - https://find-and-update.company-information.service.gov.uk/company/14254435/filing-history/MzQyMTUzMzg4NGFkaXF6a2N4/document?format=pdf&amp;download=0), its inaugural subsidiary ClearBank Europe N.V. was incorporated 6 March 2023; it acquired 100% of ClearBank Limited on 8 December 2023 as a Business Combination Under Common Control, with ClearBank Limited's results consolidated from 1 May 2023 (the day after common control was established, 30 April 2023). "CB Growth Holdings Limited" (named in AR2023's own equity note 3, and confirmed in ClearBank Group Holdings Limited's own Note 1.4 as "its parent") is a GENUINELY SEPARATE, higher entity in the group chain - not an earlier name for ClearBank Group Holdings Limited (no Companies House previous-names record exists for company 14254435, and its own filing history shows no rename). The corrected chain, top to bottom, is: CB Growth Holdings Limited -&gt; ClearBank Group Holdings Limited (14254435) -&gt; ClearBank Limited. This is a genuine change of reporting entity, not a presentation choice: the Statement of Changes in Equity's FY2024 opening balance (£196,497k) does not equal FY2023's own closing balance (£129,526k) below, and the two entities' equity bases are not directly comparable, so no plug/bridging row is used across that boundary in this sheet. However, a genuine bridge DOES exist and is now cited for traceability: ClearBank Group Holdings Limited's own stub-period Consolidated statement of changes in equity (in the filing above) runs from £(812)k total equity at 1 March 2023 (its own first reporting date) to exactly £196,497k at 31 December 2023 - i.e. this workbook's existing FY2024 opening figure is that entity's own closing balance for its first, ~10-month accounting period, built mostly from a £179,405k share capital issuance (the mechanism for the ClearBank Limited acquisition) rather than organic trading profit. This bridging period is not added as its own column here since it doesn't align with this workbook's FY-year grid, but the £196,497k figure is now independently verified against its true source rather than only appearing as an unexplained opening balance. Balance Sheet and P&amp;L totals for each year are still internally consistent (assets = liabilities + equity; income - expenses = profit/loss) since each is a same-entity, same-year snapshot - only the cross-year equity roll-forward is affected. FY2023's own Statement of Financial Position/Comprehensive Income are Company-only (ClearBank Limited did not publish Consolidated statements that year - see the Company vs Consolidated presentation note below); FY2021/FY2022/FY2024/FY2025 are Consolidated. Per project convention, each year's own originally-published figures are used throughout (FY2022's own AR2022 Consolidated figures, not AR2023's restated comparative - see CASH_FLOW_SOURCES' existing ENTITY_NOTE for the same convention applied to Cash Flow).
-PRESENTATION NOTE: FY2021's own Statement of Comprehensive Income discloses only Net interest income and Net fee income (no separate Interest income/expense or Fee income/expense split) - per AR2022's own footnote, "In 2021, only net interest income and net fee income were presented without splitting for gross amounts." FY2023's own Statement of Comprehensive Income additionally has an "Expenses recharged" line (income, not cost) not present in any other year, resulting in a positive "Operating profit" that year rather than the "Operating loss" label used elsewhere - both reproduced as reported. Balance Sheet: "Loans and advances to banks" (an interbank placement, not a customer loan) appears as its own line FY2021-FY2023 only - dropped from FY2024/FY2025's presentation (folded into Cash and cash equivalents per the Group's own accounting policy note). "Due from UK tax authorities" (FY2022/FY2023) and "Current tax asset" (FY2024/FY2025) are the same concept under different labels; FY2021 has neither line. Equity: "Share-based payment reserve" (FY2021/FY2022) was replaced by "Capital contribution reserve" from FY2023 onward (see the entity-change note above); "Treasury shares" and "Translation reserve" are absent from FY2023's Company-only presentation, present in every other year's Consolidated presentation.</t>
+PRESENTATION NOTE: FY2021's own Statement of Comprehensive Income discloses only Net interest income and Net fee income (no separate Interest income/expense or Fee income/expense split) - per AR2022's own footnote, "In 2021, only net interest income and net fee income were presented without splitting for gross amounts." FY2023's own Statement of Comprehensive Income additionally has an "Expenses recharged" line (income, not cost) not present in any other year, resulting in a positive "Operating profit" that year rather than the "Operating loss" label used elsewhere - both reproduced as reported. Balance Sheet: "Loans and advances to banks" (an interbank placement, not a customer loan) appears as its own line FY2021-FY2023 only - dropped from FY2024/FY2025's presentation (folded into Cash and cash equivalents per the Group's own accounting policy note). "Due from UK tax authorities" (FY2022/FY2023) and "Current tax asset" (FY2024/FY2025) are the same concept under different labels; FY2021 has neither line. Equity: "Share-based payment reserve" (FY2021/FY2022) was replaced by "Capital contribution reserve" from FY2023 onward (see the entity-change note above); "Treasury shares" and "Translation reserve" are absent from FY2023's Company-only presentation, present in every other year's Consolidated presentation.
+FY2017-FY2020 presentation: "Amounts due to customers" (FY2017 label) and "Customer deposits" (FY2018-FY2020 label) are the same concept under different labels - ClearBank opened to customers in October 2017, so FY2017's figure (£1,601k) reflects barely two months of customer-facing activity. "Right-of-use assets"/"Lease obligations" first appear in FY2019 (adoption of IFRS 16, replacing IAS 17 - see the Group's own Note 3.1) - absent FY2017/FY2018. "Translation reserve" first appears in FY2019 (a small foreign currency translation difference of £33k) - absent FY2017/FY2018, which had no foreign operations giving rise to translation differences. "Deferred income" first appears in FY2019 - absent FY2017/FY2018. FY2017's Statement of Comprehensive Income shows no Interest expense line (Net interest income was not yet split into gross Interest income/expense until FY2019) and no Impairments line (first appears FY2019).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A33:J33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4407,7 +5775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4416,6 +5784,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4461,6 +5833,26 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£'000)</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£'000)</t>
         </is>
       </c>
     </row>
@@ -4475,6 +5867,10 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4495,6 +5891,18 @@
         <v>43774</v>
       </c>
       <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n">
+        <v>900</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1664</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4515,6 +5923,12 @@
         <v>-9911</v>
       </c>
       <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n">
+        <v>-567</v>
+      </c>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -4537,6 +5951,18 @@
       <c r="F7" s="5" t="n">
         <v>1842</v>
       </c>
+      <c r="G7" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1097</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -4557,6 +5983,10 @@
         <v>25455</v>
       </c>
       <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4577,6 +6007,10 @@
         <v>-1047</v>
       </c>
       <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -4599,6 +6033,18 @@
       <c r="F10" s="5" t="n">
         <v>18614</v>
       </c>
+      <c r="G10" s="5" t="n">
+        <v>8785</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>3441</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>660</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -4621,6 +6067,14 @@
       <c r="F11" s="6" t="n">
         <v>938</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>933</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>780</v>
+      </c>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -4642,6 +6096,18 @@
       </c>
       <c r="F12" s="5" t="n">
         <v>21394</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>10618</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>5318</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>838</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -4655,6 +6121,10 @@
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -4677,6 +6147,18 @@
       <c r="F14" s="6" t="n">
         <v>-27719</v>
       </c>
+      <c r="G14" s="6" t="n">
+        <v>-20995</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-16573</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-14439</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-7377</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -4699,6 +6181,18 @@
       <c r="F15" s="6" t="n">
         <v>-2145</v>
       </c>
+      <c r="G15" s="6" t="n">
+        <v>-3432</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-2891</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>-620</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-490</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4721,6 +6215,18 @@
       <c r="F16" s="6" t="n">
         <v>-5791</v>
       </c>
+      <c r="G16" s="6" t="n">
+        <v>-3750</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-2914</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-1745</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-334</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4743,6 +6249,14 @@
       <c r="F17" s="6" t="n">
         <v>-337</v>
       </c>
+      <c r="G17" s="6" t="n">
+        <v>-549</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-1032</v>
+      </c>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -4765,6 +6279,18 @@
       <c r="F18" s="6" t="n">
         <v>-16447</v>
       </c>
+      <c r="G18" s="6" t="n">
+        <v>-12557</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-15682</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>-13567</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>-9396</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -4786,6 +6312,18 @@
       </c>
       <c r="F19" s="5" t="n">
         <v>-52439</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-41283</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>-39092</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>-30371</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>-17597</v>
       </c>
     </row>
     <row r="20">
@@ -4803,6 +6341,10 @@
         <v>8587</v>
       </c>
       <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -4825,6 +6367,18 @@
       <c r="F21" s="5" t="n">
         <v>-31045</v>
       </c>
+      <c r="G21" s="5" t="n">
+        <v>-30665</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>-33774</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>-29533</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>-17548</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -4847,6 +6401,16 @@
       <c r="F22" s="6" t="n">
         <v>5</v>
       </c>
+      <c r="G22" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -4869,6 +6433,16 @@
       <c r="F23" s="6" t="n">
         <v>-34</v>
       </c>
+      <c r="G23" s="6" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-73</v>
+      </c>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -4891,6 +6465,18 @@
       <c r="F24" s="5" t="n">
         <v>-31074</v>
       </c>
+      <c r="G24" s="5" t="n">
+        <v>-30777</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-33843</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>-29527</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>-17551</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -4913,6 +6499,18 @@
       <c r="F25" s="6" t="n">
         <v>2874</v>
       </c>
+      <c r="G25" s="6" t="n">
+        <v>981</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-153</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>4683</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>3652</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -4934,6 +6532,18 @@
       </c>
       <c r="F26" s="5" t="n">
         <v>-28200</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>-29796</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>-33996</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>-24844</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>-13899</v>
       </c>
     </row>
     <row r="27">
@@ -4947,6 +6557,10 @@
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -4967,6 +6581,14 @@
       <c r="F28" s="6" t="n">
         <v>-1</v>
       </c>
+      <c r="G28" s="6" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -4988,6 +6610,18 @@
       </c>
       <c r="F29" s="5" t="n">
         <v>-28201</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-29903</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-33963</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>-24844</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>-13899</v>
       </c>
     </row>
     <row r="31" ht="380" customHeight="1">
@@ -4998,14 +6632,20 @@
 FY2023: Company statements (no Consolidated statements published that year), ClearBank Annual Report and Accounts 2023, pp.69-72 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts-2023.pdf
 FY2022: Consolidated statements, own originally-published figures (not FY2023's restated comparative - see Note 32 of the FY2023 report), ClearBank Annual Report and Accounts 2022, pp.80-83 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts_2022.pdf
 FY2021: Consolidated statements, ClearBank Limited Annual Report and Accounts 2021, pp.60-63 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2021.pdf
+FY2020: Consolidated statements, ClearBank Limited Annual Report and Accounts 2020, pp.66-70 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf
+FY2019: Consolidated statements, ClearBank Limited Annual Report and Accounts 2019, pp.66-71 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: Consolidated statements, ClearBank Limited 2018 Annual Report, pp.54-58 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: Consolidated statements, ClearBank Limited 2017 Annual Report, pp.46-52 (own-year figures; cross-checked against AR2018's own FY2017 comparative column, which matches exactly - no restatement between vintages for this year) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+FLOOR VERIFICATION NOTE (HD-019): ClearBank Limited was incorporated 17 August 2015, but its first Annual Report covers a 16-month pre-operational stub period (17 Aug 2015 - 31 Dec 2016) with nil customer accounts, nil lending, and nil income throughout - see the HD-019 FLOOR VERIFICATION comment block near the top of this script for the full evidence trail. FY2017 (the first year with any customer deposits or income at all, following the bank's actual opening to customers in October 2017) is the confirmed, independently verified floor for this workbook - not FY2015/FY2016.
 ENTITY-CHANGE NOTE (corrected on follow-up review against ClearBank Group Holdings Limited's own FY2023 Companies House filing, company 14254435): FY2021-FY2023 figures are ClearBank Limited's own statements (Companies House 09736376). FY2024/FY2025 figures are instead from the Annual Report and Accounts 2025, whose auditor's report and Statement of Financial Position are addressed to "ClearBank Group Holdings Limited" - a NEW intermediate holding entity (incorporated 25 July 2022) inserted above ClearBank Limited DURING FY2023, not between FY2023 and FY2024 as an earlier pass of this workbook stated. Per that entity's own first Group accounts (period ended 31 December 2023, filed at Companies House 18 May 2024 - https://find-and-update.company-information.service.gov.uk/company/14254435/filing-history/MzQyMTUzMzg4NGFkaXF6a2N4/document?format=pdf&amp;download=0), its inaugural subsidiary ClearBank Europe N.V. was incorporated 6 March 2023; it acquired 100% of ClearBank Limited on 8 December 2023 as a Business Combination Under Common Control, with ClearBank Limited's results consolidated from 1 May 2023 (the day after common control was established, 30 April 2023). "CB Growth Holdings Limited" (named in AR2023's own equity note 3, and confirmed in ClearBank Group Holdings Limited's own Note 1.4 as "its parent") is a GENUINELY SEPARATE, higher entity in the group chain - not an earlier name for ClearBank Group Holdings Limited (no Companies House previous-names record exists for company 14254435, and its own filing history shows no rename). The corrected chain, top to bottom, is: CB Growth Holdings Limited -&gt; ClearBank Group Holdings Limited (14254435) -&gt; ClearBank Limited. This is a genuine change of reporting entity, not a presentation choice: the Statement of Changes in Equity's FY2024 opening balance (£196,497k) does not equal FY2023's own closing balance (£129,526k) below, and the two entities' equity bases are not directly comparable, so no plug/bridging row is used across that boundary in this sheet. However, a genuine bridge DOES exist and is now cited for traceability: ClearBank Group Holdings Limited's own stub-period Consolidated statement of changes in equity (in the filing above) runs from £(812)k total equity at 1 March 2023 (its own first reporting date) to exactly £196,497k at 31 December 2023 - i.e. this workbook's existing FY2024 opening figure is that entity's own closing balance for its first, ~10-month accounting period, built mostly from a £179,405k share capital issuance (the mechanism for the ClearBank Limited acquisition) rather than organic trading profit. This bridging period is not added as its own column here since it doesn't align with this workbook's FY-year grid, but the £196,497k figure is now independently verified against its true source rather than only appearing as an unexplained opening balance. Balance Sheet and P&amp;L totals for each year are still internally consistent (assets = liabilities + equity; income - expenses = profit/loss) since each is a same-entity, same-year snapshot - only the cross-year equity roll-forward is affected. FY2023's own Statement of Financial Position/Comprehensive Income are Company-only (ClearBank Limited did not publish Consolidated statements that year - see the Company vs Consolidated presentation note below); FY2021/FY2022/FY2024/FY2025 are Consolidated. Per project convention, each year's own originally-published figures are used throughout (FY2022's own AR2022 Consolidated figures, not AR2023's restated comparative - see CASH_FLOW_SOURCES' existing ENTITY_NOTE for the same convention applied to Cash Flow).
-PRESENTATION NOTE: FY2021's own Statement of Comprehensive Income discloses only Net interest income and Net fee income (no separate Interest income/expense or Fee income/expense split) - per AR2022's own footnote, "In 2021, only net interest income and net fee income were presented without splitting for gross amounts." FY2023's own Statement of Comprehensive Income additionally has an "Expenses recharged" line (income, not cost) not present in any other year, resulting in a positive "Operating profit" that year rather than the "Operating loss" label used elsewhere - both reproduced as reported. Balance Sheet: "Loans and advances to banks" (an interbank placement, not a customer loan) appears as its own line FY2021-FY2023 only - dropped from FY2024/FY2025's presentation (folded into Cash and cash equivalents per the Group's own accounting policy note). "Due from UK tax authorities" (FY2022/FY2023) and "Current tax asset" (FY2024/FY2025) are the same concept under different labels; FY2021 has neither line. Equity: "Share-based payment reserve" (FY2021/FY2022) was replaced by "Capital contribution reserve" from FY2023 onward (see the entity-change note above); "Treasury shares" and "Translation reserve" are absent from FY2023's Company-only presentation, present in every other year's Consolidated presentation.</t>
+PRESENTATION NOTE: FY2021's own Statement of Comprehensive Income discloses only Net interest income and Net fee income (no separate Interest income/expense or Fee income/expense split) - per AR2022's own footnote, "In 2021, only net interest income and net fee income were presented without splitting for gross amounts." FY2023's own Statement of Comprehensive Income additionally has an "Expenses recharged" line (income, not cost) not present in any other year, resulting in a positive "Operating profit" that year rather than the "Operating loss" label used elsewhere - both reproduced as reported. Balance Sheet: "Loans and advances to banks" (an interbank placement, not a customer loan) appears as its own line FY2021-FY2023 only - dropped from FY2024/FY2025's presentation (folded into Cash and cash equivalents per the Group's own accounting policy note). "Due from UK tax authorities" (FY2022/FY2023) and "Current tax asset" (FY2024/FY2025) are the same concept under different labels; FY2021 has neither line. Equity: "Share-based payment reserve" (FY2021/FY2022) was replaced by "Capital contribution reserve" from FY2023 onward (see the entity-change note above); "Treasury shares" and "Translation reserve" are absent from FY2023's Company-only presentation, present in every other year's Consolidated presentation.
+FY2017-FY2020 presentation: "Amounts due to customers" (FY2017 label) and "Customer deposits" (FY2018-FY2020 label) are the same concept under different labels - ClearBank opened to customers in October 2017, so FY2017's figure (£1,601k) reflects barely two months of customer-facing activity. "Right-of-use assets"/"Lease obligations" first appear in FY2019 (adoption of IFRS 16, replacing IAS 17 - see the Group's own Note 3.1) - absent FY2017/FY2018. "Translation reserve" first appears in FY2019 (a small foreign currency translation difference of £33k) - absent FY2017/FY2018, which had no foreign operations giving rise to translation differences. "Deferred income" first appears in FY2019 - absent FY2017/FY2018. FY2017's Statement of Comprehensive Income shows no Interest expense line (Net interest income was not yet split into gross Interest income/expense until FY2019) and no Impairments line (first appears FY2019).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A31:J31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5017,7 +6657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5095,34 +6735,28 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>At 1 January 2021</t>
+          <t>At 1 January 2017</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n">
-        <v>157316</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>-204</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>9519</v>
-      </c>
+        <v>25254</v>
+      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n">
-        <v>-108268</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>-116</v>
-      </c>
+        <v>-5775</v>
+      </c>
+      <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>58247</v>
+        <v>19479</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Loss for the year (FY2021)</t>
+          <t>Loss for the year (FY2017)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
@@ -5131,101 +6765,99 @@
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n">
-        <v>-28200</v>
+        <v>-13899</v>
       </c>
       <c r="H5" s="6" t="n"/>
       <c r="I5" s="6" t="n">
-        <v>-28200</v>
+        <v>-13899</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive loss (FY2021)</t>
+          <t>Issue of share capital (FY2017)</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>28204</v>
+      </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n">
-        <v>-1</v>
-      </c>
+      <c r="H6" s="6" t="n"/>
       <c r="I6" s="6" t="n">
-        <v>-1</v>
+        <v>28204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Issue of share capital (FY2021)</t>
+          <t>Own shares acquired (FY2017)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n">
-        <v>34500</v>
-      </c>
-      <c r="D7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n">
+        <v>-204</v>
+      </c>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="6" t="n">
-        <v>34500</v>
+        <v>-204</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Share-based payments (FY2021)</t>
+          <t>Share-based payments (FY2017)</t>
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n">
-        <v>7671</v>
+        <v>467</v>
       </c>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="6" t="n">
-        <v>7671</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>At 31 December 2021</t>
+          <t>At 31 December 2017</t>
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n">
-        <v>191816</v>
+        <v>53458</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>-204</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>17190</v>
+        <v>467</v>
       </c>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n">
-        <v>-136468</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>-117</v>
-      </c>
+        <v>-19674</v>
+      </c>
+      <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n">
-        <v>72217</v>
+        <v>34047</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Profit for the year (FY2022)</t>
+          <t>Loss for the year (FY2018)</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
@@ -5234,101 +6866,99 @@
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n">
-        <v>6818</v>
+        <v>-24844</v>
       </c>
       <c r="H10" s="6" t="n"/>
       <c r="I10" s="6" t="n">
-        <v>6818</v>
+        <v>-24844</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive income (FY2022)</t>
+          <t>Issue of share capital (FY2018)</t>
         </is>
       </c>
       <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>24871</v>
+      </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="n">
-        <v>1</v>
+        <v>24871</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Issue of share capital (FY2022)</t>
+          <t>Share-based payments (FY2018)</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n">
-        <v>533</v>
-      </c>
+      <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
+      <c r="E12" s="6" t="n">
+        <v>2834</v>
+      </c>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n">
-        <v>533</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Share-based payments (FY2022)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n">
-        <v>7743</v>
-      </c>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n">
-        <v>7743</v>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2018</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n">
+        <v>78329</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-204</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>3301</v>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n">
+        <v>-44518</v>
+      </c>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n">
+        <v>36908</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>At 31 December 2022</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n">
-        <v>192349</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>-204</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>24933</v>
-      </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n">
-        <v>-129650</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>-116</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>87312</v>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year (FY2019)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n">
+        <v>-33996</v>
+      </c>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n">
+        <v>-33996</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Note: FY2023's own report is Company-only - Treasury shares/Translation reserve columns are not disclosed that year (see Presentation Note); the FY2022 closing balance it re-presents (£87,312k Total) matches the Consolidated total above exactly.</t>
+          <t>Other comprehensive income (FY2019)</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
@@ -5337,116 +6967,120 @@
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
+      <c r="H15" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Profit for the year (FY2023)</t>
+          <t>Issue of share capital (FY2019)</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
+      <c r="C16" s="6" t="n">
+        <v>34875</v>
+      </c>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n">
-        <v>22396</v>
-      </c>
+      <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="n">
-        <v>22396</v>
+        <v>34875</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Issue of share capital (FY2023)</t>
+          <t>Share-based payments (FY2019)</t>
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n">
-        <v>11300</v>
-      </c>
+      <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
+      <c r="E17" s="6" t="n">
+        <v>2422</v>
+      </c>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n">
-        <v>11300</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Share-based payments and reserve transfer (FY2023)</t>
+          <t>Other movements (FY2019, reserve transfer)</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n">
-        <v>-21408</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>26805</v>
-      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n">
-        <v>1332</v>
-      </c>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n">
-        <v>6729</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-42</v>
+      </c>
+      <c r="I18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Tax on share-based payments (FY2023)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n">
-        <v>1789</v>
-      </c>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n">
-        <v>1789</v>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2019</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n">
+        <v>113204</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-204</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>5723</v>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n">
+        <v>-78472</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>40242</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>At 31 December 2023</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n">
-        <v>203445</v>
-      </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n">
-        <v>26805</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-100724</v>
-      </c>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n">
-        <v>129526</v>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year (FY2020)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n">
+        <v>-29796</v>
+      </c>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n">
+        <v>-29796</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>ENTITY-CHANGE NOTE: a new intermediate parent, ClearBank Group Holdings Limited, was inserted above ClearBank Limited during FY2023 (business combination under common control, consolidated from 1 May 2023 - see Sources below) - the FY2024 opening balance is that new entity's own closing balance for its first reporting period (to 31 Dec 2023), not a continuation of the row above.</t>
+          <t>Other comprehensive loss (FY2020)</t>
         </is>
       </c>
       <c r="B21" s="6" t="n"/>
@@ -5455,183 +7089,185 @@
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
+      <c r="H21" s="6" t="n">
+        <v>-107</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>-107</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>At 1 January 2024</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>189403</v>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n">
-        <v>3511</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>3598</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>-17</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>196497</v>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Issue of share capital (FY2020)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n">
+        <v>44112</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n">
+        <v>44112</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Loss for the year (FY2024)</t>
+          <t>Share-based payments (FY2020)</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
+      <c r="E23" s="6" t="n">
+        <v>3796</v>
+      </c>
       <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n">
-        <v>-10318</v>
-      </c>
+      <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
       <c r="I23" s="6" t="n">
-        <v>-10318</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Other comprehensive loss (FY2024)</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n">
-        <v>-767</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>-767</v>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2020 (= At 1 January 2021)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n">
+        <v>157316</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-204</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>9519</v>
+      </c>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n">
+        <v>-108268</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>58247</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Issue of share capital (FY2024)</t>
+          <t>Loss for the year (FY2021)</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n">
-        <v>35000</v>
-      </c>
+      <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
+      <c r="G25" s="6" t="n">
+        <v>-28200</v>
+      </c>
       <c r="H25" s="6" t="n"/>
       <c r="I25" s="6" t="n">
-        <v>35000</v>
+        <v>-28200</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Share-based payments (FY2024)</t>
+          <t>Other comprehensive loss (FY2021)</t>
         </is>
       </c>
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n">
-        <v>5677</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>76</v>
-      </c>
-      <c r="H26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n">
+        <v>-1</v>
+      </c>
       <c r="I26" s="6" t="n">
-        <v>5753</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Tax on share-based payments (FY2024)</t>
+          <t>Issue of share capital (FY2021)</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
+      <c r="C27" s="6" t="n">
+        <v>34500</v>
+      </c>
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n">
-        <v>-3874</v>
-      </c>
+      <c r="G27" s="6" t="n"/>
       <c r="H27" s="6" t="n"/>
       <c r="I27" s="6" t="n">
-        <v>-3874</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>At 31 December 2024</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>224403</v>
-      </c>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n">
-        <v>9188</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>-10518</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>-784</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>222291</v>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payments (FY2021)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n">
+        <v>7671</v>
+      </c>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n">
+        <v>7671</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Loss for the year (FY2025)</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n">
-        <v>-15765</v>
-      </c>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n">
-        <v>-15765</v>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n">
+        <v>191816</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-204</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>17190</v>
+      </c>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n">
+        <v>-136468</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>72217</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive income (FY2025)</t>
+          <t>Profit for the year (FY2022)</t>
         </is>
       </c>
       <c r="B30" s="6" t="n"/>
@@ -5639,97 +7275,509 @@
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n">
-        <v>1788</v>
-      </c>
+      <c r="G30" s="6" t="n">
+        <v>6818</v>
+      </c>
+      <c r="H30" s="6" t="n"/>
       <c r="I30" s="6" t="n">
-        <v>1788</v>
+        <v>6818</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Share-based payments (FY2025)</t>
+          <t>Other comprehensive income (FY2022)</t>
         </is>
       </c>
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="6" t="n"/>
       <c r="D31" s="6" t="n"/>
       <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n">
-        <v>2754</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>-1187</v>
-      </c>
-      <c r="H31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="I31" s="6" t="n">
-        <v>1567</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Tax on share-based payments (FY2025)</t>
+          <t>Issue of share capital (FY2022)</t>
         </is>
       </c>
       <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
+      <c r="C32" s="6" t="n">
+        <v>533</v>
+      </c>
       <c r="D32" s="6" t="n"/>
       <c r="E32" s="6" t="n"/>
       <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n">
-        <v>2958</v>
-      </c>
+      <c r="G32" s="6" t="n"/>
       <c r="H32" s="6" t="n"/>
       <c r="I32" s="6" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payments (FY2022)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n">
+        <v>7743</v>
+      </c>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n">
+        <v>7743</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n">
+        <v>192349</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>-204</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>24933</v>
+      </c>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n">
+        <v>-129650</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>87312</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Note: FY2023's own report is Company-only - Treasury shares/Translation reserve columns are not disclosed that year (see Presentation Note); the FY2022 closing balance it re-presents (£87,312k Total) matches the Consolidated total above exactly.</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year (FY2023)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n">
+        <v>22396</v>
+      </c>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n">
+        <v>22396</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Issue of share capital (FY2023)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n">
+        <v>11300</v>
+      </c>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n">
+        <v>11300</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payments and reserve transfer (FY2023)</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n">
+        <v>-21408</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>26805</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>1332</v>
+      </c>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="6" t="n">
+        <v>6729</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Tax on share-based payments (FY2023)</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n">
+        <v>1789</v>
+      </c>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n">
+        <v>203445</v>
+      </c>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n">
+        <v>26805</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>-100724</v>
+      </c>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n">
+        <v>129526</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>ENTITY-CHANGE NOTE: a new intermediate parent, ClearBank Group Holdings Limited, was inserted above ClearBank Limited during FY2023 (business combination under common control, consolidated from 1 May 2023 - see Sources below) - the FY2024 opening balance is that new entity's own closing balance for its first reporting period (to 31 Dec 2023), not a continuation of the row above.</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>At 1 January 2024</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>189403</v>
+      </c>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n">
+        <v>3511</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>3598</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>-17</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>196497</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year (FY2024)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n">
+        <v>-10318</v>
+      </c>
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="n">
+        <v>-10318</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss (FY2024)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n">
+        <v>-767</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>-767</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Issue of share capital (FY2024)</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n">
+        <v>35000</v>
+      </c>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="6" t="n">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payments (FY2024)</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n">
+        <v>5677</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="H46" s="6" t="n"/>
+      <c r="I46" s="6" t="n">
+        <v>5753</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Tax on share-based payments (FY2024)</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n"/>
+      <c r="G47" s="6" t="n">
+        <v>-3874</v>
+      </c>
+      <c r="H47" s="6" t="n"/>
+      <c r="I47" s="6" t="n">
+        <v>-3874</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>224403</v>
+      </c>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n">
+        <v>9188</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-10518</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>-784</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>222291</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year (FY2025)</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n">
+        <v>-15765</v>
+      </c>
+      <c r="H49" s="6" t="n"/>
+      <c r="I49" s="6" t="n">
+        <v>-15765</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (FY2025)</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="6" t="n">
+        <v>1788</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payments (FY2025)</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n">
+        <v>2754</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>-1187</v>
+      </c>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6" t="n">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Tax on share-based payments (FY2025)</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="n">
         <v>2958</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="H52" s="6" t="n"/>
+      <c r="I52" s="6" t="n">
+        <v>2958</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>At 31 December 2025</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B53" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C53" s="5" t="n">
         <v>224403</v>
       </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n">
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n">
         <v>11942</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="G53" s="5" t="n">
         <v>-24512</v>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H53" s="5" t="n">
         <v>1004</v>
       </c>
-      <c r="I33" s="5" t="n">
+      <c r="I53" s="5" t="n">
         <v>212839</v>
       </c>
     </row>
-    <row r="35" ht="380" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="55" ht="380" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank's own Statement of Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, transcribed from each year's own report:
 FY2025/FY2024: Consolidated statements, ClearBank Group Holdings Limited Annual Report and Accounts 2025, pp.68-70 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2025.pdf
 FY2023: Company statements (no Consolidated statements published that year), ClearBank Annual Report and Accounts 2023, pp.69-72 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts-2023.pdf
 FY2022: Consolidated statements, own originally-published figures (not FY2023's restated comparative - see Note 32 of the FY2023 report), ClearBank Annual Report and Accounts 2022, pp.80-83 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts_2022.pdf
 FY2021: Consolidated statements, ClearBank Limited Annual Report and Accounts 2021, pp.60-63 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2021.pdf
+FY2020: Consolidated statements, ClearBank Limited Annual Report and Accounts 2020, pp.66-70 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf
+FY2019: Consolidated statements, ClearBank Limited Annual Report and Accounts 2019, pp.66-71 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: Consolidated statements, ClearBank Limited 2018 Annual Report, pp.54-58 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: Consolidated statements, ClearBank Limited 2017 Annual Report, pp.46-52 (own-year figures; cross-checked against AR2018's own FY2017 comparative column, which matches exactly - no restatement between vintages for this year) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+FLOOR VERIFICATION NOTE (HD-019): ClearBank Limited was incorporated 17 August 2015, but its first Annual Report covers a 16-month pre-operational stub period (17 Aug 2015 - 31 Dec 2016) with nil customer accounts, nil lending, and nil income throughout - see the HD-019 FLOOR VERIFICATION comment block near the top of this script for the full evidence trail. FY2017 (the first year with any customer deposits or income at all, following the bank's actual opening to customers in October 2017) is the confirmed, independently verified floor for this workbook - not FY2015/FY2016.
 ENTITY-CHANGE NOTE (corrected on follow-up review against ClearBank Group Holdings Limited's own FY2023 Companies House filing, company 14254435): FY2021-FY2023 figures are ClearBank Limited's own statements (Companies House 09736376). FY2024/FY2025 figures are instead from the Annual Report and Accounts 2025, whose auditor's report and Statement of Financial Position are addressed to "ClearBank Group Holdings Limited" - a NEW intermediate holding entity (incorporated 25 July 2022) inserted above ClearBank Limited DURING FY2023, not between FY2023 and FY2024 as an earlier pass of this workbook stated. Per that entity's own first Group accounts (period ended 31 December 2023, filed at Companies House 18 May 2024 - https://find-and-update.company-information.service.gov.uk/company/14254435/filing-history/MzQyMTUzMzg4NGFkaXF6a2N4/document?format=pdf&amp;download=0), its inaugural subsidiary ClearBank Europe N.V. was incorporated 6 March 2023; it acquired 100% of ClearBank Limited on 8 December 2023 as a Business Combination Under Common Control, with ClearBank Limited's results consolidated from 1 May 2023 (the day after common control was established, 30 April 2023). "CB Growth Holdings Limited" (named in AR2023's own equity note 3, and confirmed in ClearBank Group Holdings Limited's own Note 1.4 as "its parent") is a GENUINELY SEPARATE, higher entity in the group chain - not an earlier name for ClearBank Group Holdings Limited (no Companies House previous-names record exists for company 14254435, and its own filing history shows no rename). The corrected chain, top to bottom, is: CB Growth Holdings Limited -&gt; ClearBank Group Holdings Limited (14254435) -&gt; ClearBank Limited. This is a genuine change of reporting entity, not a presentation choice: the Statement of Changes in Equity's FY2024 opening balance (£196,497k) does not equal FY2023's own closing balance (£129,526k) below, and the two entities' equity bases are not directly comparable, so no plug/bridging row is used across that boundary in this sheet. However, a genuine bridge DOES exist and is now cited for traceability: ClearBank Group Holdings Limited's own stub-period Consolidated statement of changes in equity (in the filing above) runs from £(812)k total equity at 1 March 2023 (its own first reporting date) to exactly £196,497k at 31 December 2023 - i.e. this workbook's existing FY2024 opening figure is that entity's own closing balance for its first, ~10-month accounting period, built mostly from a £179,405k share capital issuance (the mechanism for the ClearBank Limited acquisition) rather than organic trading profit. This bridging period is not added as its own column here since it doesn't align with this workbook's FY-year grid, but the £196,497k figure is now independently verified against its true source rather than only appearing as an unexplained opening balance. Balance Sheet and P&amp;L totals for each year are still internally consistent (assets = liabilities + equity; income - expenses = profit/loss) since each is a same-entity, same-year snapshot - only the cross-year equity roll-forward is affected. FY2023's own Statement of Financial Position/Comprehensive Income are Company-only (ClearBank Limited did not publish Consolidated statements that year - see the Company vs Consolidated presentation note below); FY2021/FY2022/FY2024/FY2025 are Consolidated. Per project convention, each year's own originally-published figures are used throughout (FY2022's own AR2022 Consolidated figures, not AR2023's restated comparative - see CASH_FLOW_SOURCES' existing ENTITY_NOTE for the same convention applied to Cash Flow).
-PRESENTATION NOTE: FY2021's own Statement of Comprehensive Income discloses only Net interest income and Net fee income (no separate Interest income/expense or Fee income/expense split) - per AR2022's own footnote, "In 2021, only net interest income and net fee income were presented without splitting for gross amounts." FY2023's own Statement of Comprehensive Income additionally has an "Expenses recharged" line (income, not cost) not present in any other year, resulting in a positive "Operating profit" that year rather than the "Operating loss" label used elsewhere - both reproduced as reported. Balance Sheet: "Loans and advances to banks" (an interbank placement, not a customer loan) appears as its own line FY2021-FY2023 only - dropped from FY2024/FY2025's presentation (folded into Cash and cash equivalents per the Group's own accounting policy note). "Due from UK tax authorities" (FY2022/FY2023) and "Current tax asset" (FY2024/FY2025) are the same concept under different labels; FY2021 has neither line. Equity: "Share-based payment reserve" (FY2021/FY2022) was replaced by "Capital contribution reserve" from FY2023 onward (see the entity-change note above); "Treasury shares" and "Translation reserve" are absent from FY2023's Company-only presentation, present in every other year's Consolidated presentation.</t>
+PRESENTATION NOTE: FY2021's own Statement of Comprehensive Income discloses only Net interest income and Net fee income (no separate Interest income/expense or Fee income/expense split) - per AR2022's own footnote, "In 2021, only net interest income and net fee income were presented without splitting for gross amounts." FY2023's own Statement of Comprehensive Income additionally has an "Expenses recharged" line (income, not cost) not present in any other year, resulting in a positive "Operating profit" that year rather than the "Operating loss" label used elsewhere - both reproduced as reported. Balance Sheet: "Loans and advances to banks" (an interbank placement, not a customer loan) appears as its own line FY2021-FY2023 only - dropped from FY2024/FY2025's presentation (folded into Cash and cash equivalents per the Group's own accounting policy note). "Due from UK tax authorities" (FY2022/FY2023) and "Current tax asset" (FY2024/FY2025) are the same concept under different labels; FY2021 has neither line. Equity: "Share-based payment reserve" (FY2021/FY2022) was replaced by "Capital contribution reserve" from FY2023 onward (see the entity-change note above); "Treasury shares" and "Translation reserve" are absent from FY2023's Company-only presentation, present in every other year's Consolidated presentation.
+FY2017-FY2020 presentation: "Amounts due to customers" (FY2017 label) and "Customer deposits" (FY2018-FY2020 label) are the same concept under different labels - ClearBank opened to customers in October 2017, so FY2017's figure (£1,601k) reflects barely two months of customer-facing activity. "Right-of-use assets"/"Lease obligations" first appear in FY2019 (adoption of IFRS 16, replacing IAS 17 - see the Group's own Note 3.1) - absent FY2017/FY2018. "Translation reserve" first appears in FY2019 (a small foreign currency translation difference of £33k) - absent FY2017/FY2018, which had no foreign operations giving rise to translation differences. "Deferred income" first appears in FY2019 - absent FY2017/FY2018. FY2017's Statement of Comprehensive Income shows no Interest expense line (Net interest income was not yet split into gross Interest income/expense until FY2019) and no Impairments line (first appears FY2019).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A55:I55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5741,7 +7789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -5750,6 +7798,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5795,6 +7847,26 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£'000)</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£'000)</t>
         </is>
       </c>
     </row>
@@ -5809,6 +7881,10 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5831,6 +7907,18 @@
       <c r="F5" s="6" t="n">
         <v>-28200</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>-29796</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-33996</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-24844</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-13899</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -5852,6 +7940,18 @@
       </c>
       <c r="F6" s="6" t="n">
         <v>475</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>462</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>651</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>620</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>490</v>
       </c>
     </row>
     <row r="7">
@@ -5869,769 +7969,1162 @@
       <c r="F7" s="6" t="n">
         <v>15</v>
       </c>
+      <c r="G7" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Depreciation of right-of-use assets</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>2202</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>1624</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>1702</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>1030</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>1670</v>
-      </c>
+          <t>Impairment of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Amortisation of intangible assets</t>
+          <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>15706</v>
+        <v>2202</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>11643</v>
+        <v>1624</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>8869</v>
+        <v>1702</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>7824</v>
+        <v>1030</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>5791</v>
-      </c>
+        <v>1670</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>2969</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2240</v>
+      </c>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Impairment of intangible assets</t>
+          <t>Amortisation of intangible assets</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>936</v>
+        <v>15706</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1584</v>
+        <v>11643</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>246</v>
+        <v>8869</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>676</v>
+        <v>7824</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>337</v>
+        <v>5791</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>3723</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2939</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1745</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>334</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Share-based payment expense</t>
+          <t>Impairment of intangible assets</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>1567</v>
+        <v>936</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5753</v>
+        <v>1584</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6729</v>
+        <v>246</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>7743</v>
+        <v>676</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>7671</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>549</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1032</v>
+      </c>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Recognition of right-of-use assets</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
+          <t>Share-based payment expense</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>1567</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>5753</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>6729</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>7743</v>
+      </c>
       <c r="F12" s="6" t="n">
-        <v>34</v>
+        <v>7671</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>3796</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2422</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2834</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>467</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Tax benefit/(charge)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>-945</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>74</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>-3967</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>-17794</v>
-      </c>
+          <t>Recognition of right-of-use assets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n">
-        <v>-2874</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-570</v>
+      </c>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Costs of share issue / raising finance (included in professional fees)</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>10</v>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Net interest income</t>
+          <t>Tax benefit/(charge)</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>-70963</v>
+        <v>-945</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>-67110</v>
+        <v>74</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>-81914</v>
+        <v>-3967</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-33863</v>
+        <v>-17794</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-1842</v>
+        <v>-2874</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-981</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>153</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>-4683</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-3652</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>-798</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>-678</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>-380</v>
-      </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
+          <t>Finance costs</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Foreign currency differences (non-cash items)</t>
+          <t>Net interest income</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>30</v>
+        <v>-70963</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>18</v>
+        <v>-67110</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>43</v>
+        <v>-81914</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1</v>
+        <v>-33863</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-1</v>
-      </c>
+        <v>-1842</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-900</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-1097</v>
+      </c>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Operating cash flows before changes in working capital</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>-67967</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>-57342</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>-45766</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>-27240</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>-16914</v>
-      </c>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>-798</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>-678</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>-380</v>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Increase/(decrease) in collateral</t>
+          <t>Foreign currency differences (non-cash items)</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>859</v>
+        <v>30</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>-16</v>
+        <v>18</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-919</v>
+        <v>43</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-27</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-36</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>(Increase)/decrease in loans and advances to banks</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n">
-        <v>19525</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>-10369</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>-3194</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>-5962</v>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Operating cash flows before changes in working capital</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-67967</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-57342</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-45766</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-27240</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-16914</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>-20248</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>-26114</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>-24323</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>-16168</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Increase in receivables</t>
+          <t>Increase/(decrease) in collateral</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>-6288</v>
+        <v>859</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>-1877</v>
+        <v>-16</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>-3547</v>
+        <v>-919</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>-1734</v>
+        <v>-27</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-294</v>
+        <v>-36</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n">
+        <v>-49</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>-315</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Increase/(decrease) in payables</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>6359</v>
-      </c>
+          <t>(Increase)/decrease in loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n">
-        <v>46</v>
+        <v>19525</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>-26935</v>
+        <v>-10369</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>99410</v>
+        <v>-3194</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>3306</v>
-      </c>
+        <v>-5962</v>
+      </c>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Increase/(decrease) in deferred income</t>
+          <t>Increase in receivables</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>113</v>
+        <v>-6288</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>-6167</v>
+        <v>-1877</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>-16298</v>
+        <v>-3547</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>-24954</v>
+        <v>-1734</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>-17307</v>
+        <v>-294</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-842</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-2565</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-311</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-689</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Increase in customer deposits/amounts due to customers</t>
+          <t>Increase/(decrease) in payables</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>7006677</v>
+        <v>6359</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>4654971</v>
+        <v>46</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>3152204</v>
+        <v>-26935</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>335213</v>
+        <v>99410</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1718866</v>
+        <v>3306</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>-2143</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1942</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1620</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>1920</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Foreign currency differences (working capital)</t>
+          <t>Increase/(decrease) in deferred income</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5979</v>
+        <v>113</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>-3846</v>
-      </c>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
+        <v>-6167</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-16298</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-24954</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-17307</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>8045</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>51512</v>
+      </c>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Cash generated by/from operations</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>6945732</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>4605294</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>3048370</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>377474</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>1681659</v>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Increase in customer deposits/amounts due to customers</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>7006677</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>4654971</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>3152204</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>335213</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>1718866</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>467909</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>413836</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>42544</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>1601</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Interest received</t>
+          <t>Foreign currency differences (working capital)</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>625779</v>
+        <v>5979</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>425289</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>243957</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>43774</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>2056</v>
-      </c>
+        <v>-3846</v>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Interest paid</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>-553258</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>-341945</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>-149139</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>-7621</v>
-      </c>
-      <c r="F28" s="6" t="n"/>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Cash generated by/from operations</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>6945732</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>4605294</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3048370</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>377474</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>1681659</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>452715</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>438611</v>
+      </c>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
+          <t>Interest received</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>625779</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>425289</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>243957</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>43774</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>2056</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>909</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>1096</v>
+      </c>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Interest paid</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>-553258</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>-341945</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>-149139</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>-7621</v>
+      </c>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
           <t>Tax (paid)/received</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B31" s="6" t="n">
         <v>-1062</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C31" s="6" t="n">
         <v>2134</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D31" s="6" t="n">
         <v>-640</v>
       </c>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Net cash generated from operating activities</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>7017191</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>4690772</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>3142548</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>413627</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>1683715</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Investing activities</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Net cash generated from operating activities</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>7017191</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>4690772</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3142548</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>413627</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>1683715</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>453624</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>439707</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>19481</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>-13651</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Purchase of property, plant and equipment</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B34" s="6" t="n">
         <v>-29</v>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="C34" s="6" t="n">
         <v>-5</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D34" s="6" t="n">
         <v>-41</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E34" s="6" t="n">
         <v>-408</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F34" s="6" t="n">
         <v>-268</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="G34" s="6" t="n">
+        <v>-800</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>-262</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>-320</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>-640</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B35" s="6" t="n">
         <v>-15655</v>
       </c>
-      <c r="C33" s="6" t="n">
+      <c r="C35" s="6" t="n">
         <v>-24091</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D35" s="6" t="n">
         <v>-21737</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E35" s="6" t="n">
         <v>-7736</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F35" s="6" t="n">
         <v>-8356</v>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="G35" s="6" t="n">
+        <v>-7648</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>-8573</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>-8567</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>-5030</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Net cash used in investing activities</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B36" s="5" t="n">
         <v>-15684</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C36" s="5" t="n">
         <v>-24096</v>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D36" s="5" t="n">
         <v>-21778</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E36" s="5" t="n">
         <v>-8144</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F36" s="5" t="n">
         <v>-8624</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="G36" s="5" t="n">
+        <v>-8448</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>-8835</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>-8887</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>-5670</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Financing activities</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Proceeds from issue of Ordinary Shares</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="6" t="n">
-        <v>35000</v>
-      </c>
-      <c r="D36" s="6" t="n">
-        <v>11300</v>
-      </c>
-      <c r="E36" s="6" t="n">
-        <v>533</v>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>34500</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Direct costs paid for lease acquisition</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n">
-        <v>-24</v>
-      </c>
+      <c r="B37" s="6" t="n"/>
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="6" t="n"/>
       <c r="E37" s="6" t="n"/>
       <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Principal paid on lease liabilities</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n">
-        <v>-1579</v>
-      </c>
+          <t>Proceeds from issue of Ordinary Shares</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
       <c r="C38" s="6" t="n">
-        <v>-1567</v>
+        <v>35000</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>-1763</v>
+        <v>11300</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>-917</v>
+        <v>533</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-1974</v>
+        <v>34500</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>44112</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>34875</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>24871</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>28000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Interest paid on lease liabilities</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="n"/>
+          <t>Direct costs paid for lease acquisition</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>-24</v>
+      </c>
       <c r="C39" s="6" t="n"/>
       <c r="D39" s="6" t="n"/>
       <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="n">
-        <v>-34</v>
-      </c>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n"/>
+      <c r="J39" s="6" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Net cash generated from/(used in) financing activities</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>-1603</v>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>33433</v>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>9537</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>-384</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>32492</v>
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Cost of raising finance</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
+      <c r="J40" s="6" t="n">
+        <v>-92</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Net increase in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>6999904</v>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>4700109</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>3130307</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>405099</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>1707583</v>
-      </c>
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Principal paid on lease liabilities</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>-1579</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>-1567</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>-1763</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>-917</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>-1974</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>-2650</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>-1607</v>
+      </c>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at the beginning of the year</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n">
-        <v>10961293</v>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>6258123</v>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>3125862</v>
-      </c>
-      <c r="E42" s="6" t="n">
-        <v>2720797</v>
-      </c>
+          <t>Interest paid on lease liabilities</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
       <c r="F42" s="6" t="n">
-        <v>1013224</v>
-      </c>
+        <v>-34</v>
+      </c>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n">
+        <v>-73</v>
+      </c>
+      <c r="I42" s="6" t="n"/>
+      <c r="J42" s="6" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Effect of foreign exchange rate changes</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n">
-        <v>-4221</v>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>3061</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>-43</v>
-      </c>
-      <c r="E43" s="6" t="n">
-        <v>-34</v>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>-10</v>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Net cash generated from/(used in) financing activities</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>-1603</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>33433</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>9537</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>-384</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>32492</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>41462</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>33195</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>24871</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>27908</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>Net increase in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>6999904</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>4700109</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>3130307</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>405099</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>1707583</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>486638</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>464067</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>35465</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>8587</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at the beginning of the year</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>10961293</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>6258123</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>3125862</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>2720797</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>1013224</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>526594</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>62527</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>27062</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>18475</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Effect of foreign exchange rate changes</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>-4221</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>3061</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>-43</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>-34</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H46" s="6" t="n"/>
+      <c r="I46" s="6" t="n"/>
+      <c r="J46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
           <t>Cash and cash equivalents at the end of the year</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B47" s="5" t="n">
         <v>17956976</v>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C47" s="5" t="n">
         <v>10961293</v>
       </c>
-      <c r="D44" s="5" t="n">
+      <c r="D47" s="5" t="n">
         <v>6256126</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E47" s="5" t="n">
         <v>3125862</v>
       </c>
-      <c r="F44" s="5" t="n">
+      <c r="F47" s="5" t="n">
         <v>2720797</v>
       </c>
-    </row>
-    <row r="46" ht="280" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="G47" s="5" t="n">
+        <v>1013224</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>526594</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>62527</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>27062</v>
+      </c>
+    </row>
+    <row r="49" ht="280" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are ClearBank Limited's own Consolidated Statement of Cash Flows:
 FY2025/FY2024: ClearBank Annual Report and Accounts 2025, p.71 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2025.pdf
 FY2023: ClearBank Annual Report and Accounts 2023, p.73 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts-2023.pdf
 FY2022: ClearBank Annual Report and Accounts 2022, p.43 (own originally-published figures, not FY2023's restated comparative) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts_2022.pdf
 FY2021: ClearBank Annual Report and Accounts 2021, p.66 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2021.pdf
+FY2020: ClearBank Annual Report and Accounts 2020, p.70 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, p.71 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, p.59 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.52 (own-year figures; cross-checked against AR2018's own FY2017 comparative column, which matches exactly, so no restatement between vintages for this year) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
 ClearBank Limited (FRN 754568, company 09736376), a UK clearing/embedded-banking infrastructure bank. Group basis throughout (parent-only figures are not materially different - the Group is essentially the Bank plus dormant/minor subsidiaries). Does NOT take the FRS 101/102 cash-flow-statement exemption - full Consolidated Statement of Cash Flows every year.
 FY2022's own figures (from the FY2022 Annual Report itself) are used here rather than FY2023's report's restated FY2022 comparative (Note 32 of the FY2023 report flags a restatement, e.g. profit for the year after tax 6,818 as originally reported vs. 10,760 restated, and net cash from operating activities 413,627 vs. 416,088 restated) - each year's own originally-published figures are used throughout this workbook, per project convention.
 A genuine, small, undocumented cross-vintage gap exists between FY2023's own closing cash balance (£6,256,126k) and FY2024's own opening balance per the FY2025 Annual Report's comparative (£6,258,123k) - a ~£1,997k difference with no explanation found in either source; both figures are shown exactly as each report states them, not force-reconciled.
-"Foreign currency differences" appears twice with different values in the FY2025/FY2024 presentation - once within the non-cash adjustments (a small figure) and again within the working-capital-changes section (a much larger figure driven by FX movement on customer deposit balances) - both are genuine distinct line items in the source, not a duplicate.</t>
+"Foreign currency differences" appears twice with different values in the FY2025/FY2024 presentation - once within the non-cash adjustments (a small figure) and again within the working-capital-changes section (a much larger figure driven by FX movement on customer deposit balances) - both are genuine distinct line items in the source, not a duplicate.
+FY2020's own "Operating cash flows before changes in working capital" subtotal ((20,248)) does not equal the sum of its own component adjustment lines as disclosed (which sum to (20,032), a £216k difference) - a genuine, unexplained arithmetic inconsistency within ClearBank's own FY2020 Annual Report and Accounts, reproduced exactly as published rather than force-reconciled.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A49:J49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6643,7 +9136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -6652,6 +9145,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6697,6 +9194,26 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£'000)</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£'000)</t>
         </is>
       </c>
     </row>
@@ -6711,6 +9228,10 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -6733,6 +9254,18 @@
       <c r="F5" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -6753,6 +9286,18 @@
         <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6767,6 +9312,10 @@
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -6785,6 +9334,10 @@
       <c r="F8" s="6" t="n">
         <v>5962</v>
       </c>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -6803,21 +9356,29 @@
       <c r="F9" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
     </row>
     <row r="11" ht="280" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Sources - ClearBank's own "Credit risk" and "Impairment of financial assets" notes (Note 21/2.6), read in full for all 5 years:
+          <t>Sources - ClearBank's own "Credit risk" and "Impairment of financial assets" notes (Note 21/2.6), read in full for all 9 years:
 FY2025/FY2024: ClearBank Group Holdings Limited Annual Report and Accounts 2025, pp.77,88 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2025.pdf
 FY2023: ClearBank Annual Report and Accounts 2023, credit risk/impairment notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts-2023.pdf
 FY2022/FY2021: ClearBank Annual Report and Accounts 2022, credit risk/impairment notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts_2022.pdf
-GENUINE STRUCTURAL FINDING, NOT A DATA GAP: ClearBank does not lend to customers at all. Its own FY2025 Annual Report states plainly: "The Group does not provide any credit facilities which are not fully collateralised to its customers and is therefore not exposed to associated credit risks" and "the Group's trade receivables and hence ECL are immaterial, with no further ECL-related disclosures considered necessary by management." This wording (or its equivalent) recurs across all 5 years reviewed. There is therefore no customer loan book, no IFRS 9 stage split, and no loss allowance of any kind recognised in any year - ClearBank's only credit exposure is to its treasury counterparties (predominantly the Bank of England) and to collateral it holds FROM clients (an asset-side benefit, not a risk), both deemed low/immaterial risk by the Group's own policy. "Loans and advances to banks" on the Balance Sheet (FY2021-FY2023 only, see Presentation Note on the Balance Sheet sheet) is an interbank treasury placement, not customer lending.</t>
+FY2020: ClearBank Annual Report and Accounts 2020, credit risk section - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, credit risk section - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, credit risk section - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.19 ("Currently, the bank has not started lending to customers and hence has no direct credit exposure") - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+GENUINE STRUCTURAL FINDING, NOT A DATA GAP: ClearBank does not lend to customers at all. Its own FY2025 Annual Report states plainly: "The Group does not provide any credit facilities which are not fully collateralised to its customers and is therefore not exposed to associated credit risks" and "the Group's trade receivables and hence ECL are immaterial, with no further ECL-related disclosures considered necessary by management." This wording (or its equivalent) recurs across all 9 years reviewed (FY2017-FY2019: "the bank has not started lending to customers and hence has no direct credit exposure"). There is therefore no customer loan book, no IFRS 9 stage split, and no loss allowance of any kind recognised in any year - ClearBank's only credit exposure is to its treasury counterparties (predominantly the Bank of England) and to collateral it holds FROM clients (an asset-side benefit, not a risk), both deemed low/immaterial risk by the Group's own policy. "Loans and advances to banks" on the Balance Sheet (FY2021-FY2023 only, see Presentation Note on the Balance Sheet sheet) is an interbank treasury placement, not customer lending.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6829,7 +9390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -6838,6 +9399,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6885,6 +9450,26 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6906,6 +9491,18 @@
       </c>
       <c r="F4" s="6" t="n">
         <v>36.7</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>29.952</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>17.461</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>23.681</v>
       </c>
     </row>
     <row r="6" ht="190" customHeight="1">
@@ -6915,14 +9512,19 @@
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6934,7 +9536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -6943,6 +9545,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6990,6 +9596,26 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -7020,6 +9646,26 @@
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>139.70%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>114.20%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>53%</t>
         </is>
       </c>
     </row>
@@ -7030,14 +9676,19 @@
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7049,7 +9700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -7058,6 +9709,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7105,6 +9760,26 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -7126,6 +9801,18 @@
       </c>
       <c r="F4" s="6" t="n">
         <v>36.7</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>29.952</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>17.461</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>23.681</v>
       </c>
     </row>
     <row r="6" ht="190" customHeight="1">
@@ -7135,14 +9822,19 @@
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document reviewed, no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward.</t>
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/CLEARBANK FINANCIALS.xlsx
+++ b/banks/CLEARBANK FINANCIALS.xlsx
@@ -3485,6 +3485,7 @@
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
@@ -3631,6 +3632,7 @@
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
@@ -3795,6 +3797,7 @@
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
@@ -3935,6 +3938,7 @@
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
@@ -4325,6 +4329,7 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
@@ -4490,6 +4495,7 @@
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
@@ -4661,6 +4667,7 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
@@ -4829,6 +4836,7 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
@@ -9114,7 +9122,8 @@
 FY2019: ClearBank Annual Report and Accounts 2019, p.71 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
 FY2018: ClearBank Limited 2018 Annual Report, p.59 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
 FY2017: ClearBank Limited 2017 Annual Report, p.52 (own-year figures; cross-checked against AR2018's own FY2017 comparative column, which matches exactly, so no restatement between vintages for this year) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-ClearBank Limited (FRN 754568, company 09736376), a UK clearing/embedded-banking infrastructure bank. Group basis throughout (parent-only figures are not materially different - the Group is essentially the Bank plus dormant/minor subsidiaries). Does NOT take the FRS 101/102 cash-flow-statement exemption - full Consolidated Statement of Cash Flows every year.
+ClearBank Limited (FRN 754568, company 09736376), a UK clearing/embedded-banking infrastructure bank. Group basis throughout. Does NOT take the FRS 101/102 cash-flow-statement exemption - full Consolidated Statement of Cash Flows every year.
+WHICH GROUP (corrected 2026-09-16, entity-basis sweep): 'Group' does NOT mean the same thing across this workbook, and the earlier wording here - 'the Group is essentially the Bank plus dormant/minor subsidiaries' - is only true up to FY2022. FY2017-FY2022: the Group is ClearBank Limited and its own subsidiaries, i.e. the workbook entity's own consolidation. FY2023 onward it is a DIFFERENT legal entity's consolidation: ClearBank Group Holdings Limited (company 14254435), which received formal PRA approval as a bank holding company in Q4 2023 and consolidates BOTH ClearBank Limited and ClearBank Europe N.V., a separately and fully regulated Netherlands bank that sits alongside (not inside) ClearBank Limited. Primary sources: ClearBank Pillar 3 Disclosure 2023, 'Scope of consolidation' - 'The Group comprises of ClearBank Group Holdings Limited, a regulated financial holding company, and its 100% owned and controlled subsidiaries, ClearBank Limited (the "UK Bank", a fully regulated UK bank) and ClearBank Europe N.V. ClearBank Limited is currently the only material subsidiary within the Group... Any reference to comparative metrics are for the required disclosures relating to the material subsidiary, ClearBank Limited only' (https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf); and ClearBank Pillar 3 Disclosure 2025, same section, which repeats the three-entity composition with no materiality carve-out (https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf). So FY2023's comparatives are Bank-only but its own-year figures are CBGH-consolidated, and FY2024/FY2025 are CBGH-consolidated outright. See the ENTITY-CHANGE NOTE on the Statement of Changes in Equity sheet for the same boundary on the statement sheets, which is already documented there.
 FY2022's own figures (from the FY2022 Annual Report itself) are used here rather than FY2023's report's restated FY2022 comparative (Note 32 of the FY2023 report flags a restatement, e.g. profit for the year after tax 6,818 as originally reported vs. 10,760 restated, and net cash from operating activities 413,627 vs. 416,088 restated) - each year's own originally-published figures are used throughout this workbook, per project convention.
 A genuine, small, undocumented cross-vintage gap exists between FY2023's own closing cash balance (£6,256,126k) and FY2024's own opening balance per the FY2025 Annual Report's comparative (£6,258,123k) - a ~£1,997k difference with no explanation found in either source; both figures are shown exactly as each report states them, not force-reconciled.
 "Foreign currency differences" appears twice with different values in the FY2025/FY2024 presentation - once within the non-cash adjustments (a small figure) and again within the working-capital-changes section (a much larger figure driven by FX movement on customer deposit balances) - both are genuine distinct line items in the source, not a duplicate.
@@ -9509,6 +9518,7 @@
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
@@ -9673,6 +9683,7 @@
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
@@ -9819,6 +9830,7 @@
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
 FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf

--- a/banks/CLEARBANK FINANCIALS.xlsx
+++ b/banks/CLEARBANK FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3366,14 +3367,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — Tier 1 Ratio</t>
+          <t>ClearBank Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£m (= CET1 capital; no AT1 instruments)</t>
         </is>
       </c>
     </row>
@@ -3432,53 +3433,35 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>49.75%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>67.02%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>77.45%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>87.66%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>139.70%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>114.20%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>29.952</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>17.461</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>23.681</v>
       </c>
     </row>
     <row r="6" ht="190" customHeight="1">
@@ -3486,14 +3469,22 @@
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
 REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
 FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
 FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
@@ -3531,14 +3522,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — Total Capital</t>
+          <t>ClearBank Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m (= CET1 capital; no Tier 2 instruments)</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -3597,35 +3588,53 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>132</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>141</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>126</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>29.952</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>17.461</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>23.681</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>49.75%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>67.02%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>77.45%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>87.66%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>139.70%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>114.20%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="190" customHeight="1">
@@ -3633,14 +3642,22 @@
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
 REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
 FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
 FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
@@ -3678,14 +3695,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — Total Capital Ratio</t>
+          <t>ClearBank Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£m (= CET1 capital; no Tier 2 instruments)</t>
         </is>
       </c>
     </row>
@@ -3744,53 +3761,35 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>49.75%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>67.02%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>77.45%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>87.66%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>139.70%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>114.20%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>29.952</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>17.461</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>23.681</v>
       </c>
     </row>
     <row r="6" ht="190" customHeight="1">
@@ -3798,14 +3797,22 @@
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
 REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
 FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
 FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
@@ -3843,14 +3850,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — Total RWAs</t>
+          <t>ClearBank Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -3909,44 +3916,76 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>266</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>211</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>163</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>49.75%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>67.02%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>77.45%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>87.66%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>139.70%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>114.20%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="190" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
 REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
 FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
 FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
@@ -3961,6 +4000,155 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>266</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>211</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>163</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+    </row>
+    <row r="6" ht="190" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
+FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
+FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:J6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4179,7 +4367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4330,14 +4518,22 @@
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
 REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
 FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
 FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
@@ -4352,7 +4548,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4496,14 +4692,22 @@
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
 REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
 FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
 FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
@@ -4517,7 +4721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4668,14 +4872,22 @@
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
 REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
 FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
 FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
@@ -4690,7 +4902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4837,14 +5049,22 @@
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
 REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
 FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
 FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
@@ -9399,10 +9619,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -9417,21 +9637,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — CET1 Capital</t>
+          <t>ClearBank — KM1 Key Metrics</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>ClearBank's own published key-metrics table, reproduced in its row order, labels and printed precision. ClearBank prints the UK KM1 template unnumbered, headed simply 'Key metrics', and abridged to the rows it reports against. Amounts in £m, ratios as printed. FY2021/FY2022 are ClearBank Limited's consolidation; FY2023-FY2025 are ClearBank Group Holdings Limited's. FY2020 and earlier are blank - those editions use a different disclosure format entirely, not an earlier KM1. See source note below.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -9481,60 +9701,912 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Available own funds (£m)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 ('CET 1') capital (£m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>132</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C5" s="6" t="n">
         <v>141</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D5" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E5" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="F4" s="6" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>29.952</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>17.461</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>23.681</v>
-      </c>
-    </row>
-    <row r="6" ht="190" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
-REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
-FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
-FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
-FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
-FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
+      <c r="F5" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 capital (£m)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Total capital (£m)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted assets ('RWA') (£m)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount (£m)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>266</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>211</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>163</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Capital ratios (% of RWA)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>49.75%</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>67.02%</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>77.45%</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>87.66%</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>139.70%</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>49.75%</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>67.02%</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>77.45%</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>87.66%</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>139.70%</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Total Capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>49.75%</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>67.02%</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>77.45%</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>87.66%</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>139.70%</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements based on SREP (% of RWA)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Additional CET1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>7.38%</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>9.89%</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>13.12%</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>17.58%</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Combined buffer requirements (% of RWA)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Capital conservation buffer (%)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Institution specific countercyclical capital buffer (%)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Overall capital requirements (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>17.62%</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>22.08%</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>22.11%</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>17.49%</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>21.77%</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>CET1 available after meeting the total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>36.63%</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>49.44%</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>77.26%</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>79.45%</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>83.83%</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Total exposure measure excluding claims on central banks (£m)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>658</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>542</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>289</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>241</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>20.05%</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>26.07%</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>43.51%</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>13.87%</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>38.79%</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio ('LCR')</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Total high-quality liquid assets ('HQLA') (Weighted value-average) (£m)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>17909</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>10914</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>6187</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>3081</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>2719</v>
+      </c>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Cash outflows - Total weighted value (£m)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>4521</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>2873</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>1398</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>1053</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>1462</v>
+      </c>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Cash inflows - Total weighted value (£m)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Total net outflows (adjusted value) (£m)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>4513</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>2858</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>1389</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>1037</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1462</v>
+      </c>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity coverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>396.85%</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>381.88%</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>445.36%</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>297.05%</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>185.94%</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio ('NSFR')</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Total available stable funding (£m)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>14804</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>8718</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>5032</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1190</v>
+      </c>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Total required stable funding (£m)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n"/>
+      <c r="J34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>NSFR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>20366.50%</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>15959.22%</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>10,153.88%</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>5429.15%</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>11701.32%</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="6" t="n"/>
+    </row>
+    <row r="37" ht="520" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank's own published key-metrics table, reproduced as printed. Each column is transcribed from the edition in which that year is the reporting year, except FY2021 (see below).
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf
+FY2023: ClearBank Pillar 3 Disclosure 2023, 'Key metrics' / 'Key metrics continued', pp.4-5 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
+FY2022: ClearBank Pillar 3 disclosure 2022, 'Key metrics', pp.4-5 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf
+FY2021: the FY2022 edition's own '31 Dec 2021' comparative column, same table - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf. FY2021's OWN edition has no key-metrics table to transcribe (see below), so this is the first time ClearBank presented that year in template shape.
+NO TEMPLATE BEFORE FY2022 - A POSITIVE FINDING, NOT A FAILED SEARCH. Every ClearBank Pillar 3 edition from FY2016 to FY2021 was downloaded and read on 2026-09-16 (all live on clear.bank, all HTTP 200 / application/pdf / %PDF, all with real text layers). Each uses a bespoke 'Summary Analysis' section - 'Table 1: Capital and leverage ratios' (CET1 / Tier 1 / Total regulatory capital as PERCENTAGES only, plus a 'CRD leverage ratio' and a 'UK leverage ratio' side by side) and 'Table 2: Own funds' (the equity-to-CET1 build-up in £'000). That is a different disclosure from KM1, not an earlier version of it, so those years are blank on this sheet and their figures live on the single-metric sheets instead. Those pages were additionally checked for an image-only table (pdfimages) after a sister bank was found publishing its KM1 as a bitmap: ClearBank's pre-FY2022 editions contain only cover art and photography, no table images.
+UNNUMBERED AND ABRIDGED. ClearBank never writes 'KM1' and never prints the template's row numbers; the heading is simply 'Key metrics'. The rows it does print are the UK KM1's rows, in the template's order, under the template's own section headings. The rows it does NOT print anywhere - UK 7b, UK 7c, UK 8a, UK 9a, 10, UK 10a and 14a-14e - are omitted here too rather than shown empty, because ClearBank omits them from the table itself; that is a statement about ClearBank's disclosure, and it is recorded here rather than represented as blank cells that could be mistaken for a gap in this workbook.
+ENTITY CHANGES MID-SERIES, AND THE TABLE HEADER SAYS SO. The FY2022 edition heads its columns '31 Dec 2022 / 31 Dec 2021' and its narrative speaks of 'the Bank' - ClearBank Limited's own consolidation. The FY2023 edition heads its single column 'ClearBank Group / 31 Dec 2023', and FY2024/FY2025 continue on that basis: ClearBank Group Holdings Limited (company 14254435), which also consolidates ClearBank Europe N.V. FY2023-FY2025 are therefore group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2021/FY2022 columns. Same caveat as the other Pillar 3 sheets.
+TWO INCONSISTENCIES IN CLEARBANK'S OWN PRINTING, recorded and not reconciled:
+• FY2023 total risk-weighted exposure amount is 163 in the FY2023 edition and 162 in the FY2024 edition's FY2023 comparative. The 163 shown here is FY2023's own edition.
+• The FY2025 edition prints FY2024 total RWEA as 211 on its Key metrics table and 212 on its 'Overview of risk weighted exposure amounts' table, two pages apart in the same document. This sheet shows 211 (the key-metrics figure); the RWA Breakdown sheet shows 212, its own table's total. Both are as published.
+FY2023 SREP ROWS LOOK WRONG IN THE SOURCE, AND ARE REPRODUCED ANYWAY. The FY2023 edition prints 'Additional CET1 SREP requirements 0.00%' and 'Total SREP own funds requirements 0.00%' - a total SREP own funds requirement of zero is not possible (the Pillar 1 minimum alone is 8%), and the same edition's own 'Overall capital requirements' row prints 22.11%. The FY2024 edition's FY2023 comparative instead prints 9.91% and 17.61% for those two rows, and 59.84% rather than 77.26% for 'CET1 available after meeting the total SREP own funds requirements'. Under this project's rule that each year comes from its own edition, the FY2023 column here carries the FY2023 edition's figures; the FY2024 edition's restated comparatives are recorded in this note so nothing is lost. The FY2022 edition prints 0.00% for those rows in both its columns, and a 0.00% capital conservation buffer, which is likewise as published.
+EXPECTED DISAGREEMENT WITH THE CET1/TIER 1/TOTAL CAPITAL SHEETS, FY2021 ONLY - not an error in either place. This sheet shows 37 for FY2021 because that is what the FY2022 edition's comparative column prints: ClearBank rounds the whole key-metrics table to whole £m. The CET1 Capital / Tier 1 Capital / Total Capital sheets show 36.7, because those sheets take FY2021 from FY2021's OWN Pillar 3 edition, whose 'Table 2: Own funds' gives the figure to the pound (£36,739k). Same quantity, two precisions, two documents. The workbook's automated KM1-vs-metric-sheet cross-check flags this pair; it is left as published rather than re-rounded in either direction, because rounding 36,739 to '37' is ClearBank's act, not this workbook's, and re-deriving '36.7' onto a reproduction sheet would print a number the key-metrics table never contained.
+PRINTED PRECISION AND LABELS ARE AS EACH EDITION HAS THEM. The FY2023 edition prints the NSFR ratio with a thousands separator ('10,153.88%') where the others do not; the FY2025/FY2024 editions caption the LCR row 'Total net outflows (adjusted value)' where the FY2023/FY2022 editions caption it 'Total net cash outflows (adjusted value)', and capitalise 'Total Capital ratio' where the earlier ones write 'Total capital ratio'. The most recent edition's wording is used for the row label and the variants are recorded here.
+LATEST-EDITION CHECK, 2026-09-16: taken from clear.bank's own sitemap rather than from the URLs previously cited here, because the visible /pillar-3-disclosure page does not link every file. The newest documents published are the Pillar 3 Disclosure 2025 and the Annual Report and Accounts 2025; there is no FY2026 edition of either, which is expected for a 31 December year-end (ClearBank-Annual-Report-2026.pdf returns an honest 404 while the 2025 file serves 22.2 MB of PDF). Checked, none newer. The same sweep turned up the previously-uncited FY2024 Pillar 3 and the FY2016-FY2020 Pillar 3 documents - see the correction on the other Pillar 3 sheets.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A37:J37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9564,14 +10636,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — CET1 Ratio</t>
+          <t>ClearBank Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -9630,53 +10702,35 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>49.75%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>67.02%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>77.45%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>87.66%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>139.70%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>114.20%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>29.952</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>17.461</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>23.681</v>
       </c>
     </row>
     <row r="6" ht="190" customHeight="1">
@@ -9684,14 +10738,22 @@
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
 REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
 FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
 FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
@@ -9729,14 +10791,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — Tier 1 Capital</t>
+          <t>ClearBank Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m (= CET1 capital; no AT1 instruments)</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -9795,35 +10857,53 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>132</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>141</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>126</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>29.952</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>17.461</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>23.681</v>
+          <t>Common Equity Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>49.75%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>67.02%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>77.45%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>87.66%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>139.70%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>114.20%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="190" customHeight="1">
@@ -9831,14 +10911,22 @@
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
 REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025/FY2024: ClearBank Pillar 3 Disclosure 2025, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
 FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
 FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
 FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
 FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
 FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE: ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020 - these years' capital/leverage/liquidity metrics are instead embedded within the ordinary Annual Report's Strategic Report and financial-statement notes. FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>

--- a/banks/CLEARBANK FINANCIALS.xlsx
+++ b/banks/CLEARBANK FINANCIALS.xlsx
@@ -10598,7 +10598,7 @@
 • FY2023 total risk-weighted exposure amount is 163 in the FY2023 edition and 162 in the FY2024 edition's FY2023 comparative. The 163 shown here is FY2023's own edition.
 • The FY2025 edition prints FY2024 total RWEA as 211 on its Key metrics table and 212 on its 'Overview of risk weighted exposure amounts' table, two pages apart in the same document. This sheet shows 211 (the key-metrics figure); the RWA Breakdown sheet shows 212, its own table's total. Both are as published.
 FY2023 SREP ROWS LOOK WRONG IN THE SOURCE, AND ARE REPRODUCED ANYWAY. The FY2023 edition prints 'Additional CET1 SREP requirements 0.00%' and 'Total SREP own funds requirements 0.00%' - a total SREP own funds requirement of zero is not possible (the Pillar 1 minimum alone is 8%), and the same edition's own 'Overall capital requirements' row prints 22.11%. The FY2024 edition's FY2023 comparative instead prints 9.91% and 17.61% for those two rows, and 59.84% rather than 77.26% for 'CET1 available after meeting the total SREP own funds requirements'. Under this project's rule that each year comes from its own edition, the FY2023 column here carries the FY2023 edition's figures; the FY2024 edition's restated comparatives are recorded in this note so nothing is lost. The FY2022 edition prints 0.00% for those rows in both its columns, and a 0.00% capital conservation buffer, which is likewise as published.
-EXPECTED DISAGREEMENT WITH THE CET1/TIER 1/TOTAL CAPITAL SHEETS, FY2021 ONLY - not an error in either place. This sheet shows 37 for FY2021 because that is what the FY2022 edition's comparative column prints: ClearBank rounds the whole key-metrics table to whole £m. The CET1 Capital / Tier 1 Capital / Total Capital sheets show 36.7, because those sheets take FY2021 from FY2021's OWN Pillar 3 edition, whose 'Table 2: Own funds' gives the figure to the pound (£36,739k). Same quantity, two precisions, two documents. The workbook's automated KM1-vs-metric-sheet cross-check flags this pair; it is left as published rather than re-rounded in either direction, because rounding 36,739 to '37' is ClearBank's act, not this workbook's, and re-deriving '36.7' onto a reproduction sheet would print a number the key-metrics table never contained.
+TWO PRINTED PRECISIONS FOR THE SAME FY2021 QUANTITY, ON THIS SHEET AND ON THE CET1/TIER 1/TOTAL CAPITAL SHEETS - not an error in either place. This sheet shows 37 for FY2021 because that is what the FY2022 edition's comparative column prints: ClearBank rounds the whole key-metrics table to whole £m. The CET1 Capital / Tier 1 Capital / Total Capital sheets show 36.7, because those sheets take FY2021 from FY2021's OWN Pillar 3 edition, whose 'Table 2: Own funds' gives the figure to the pound (£36,739k). Same quantity, two precisions, two documents. Both are left as published rather than re-rounded in either direction, because rounding 36,739 to '37' is ClearBank's act, not this workbook's, and re-deriving '36.7' onto a reproduction sheet would print a number the key-metrics table never contained.
 PRINTED PRECISION AND LABELS ARE AS EACH EDITION HAS THEM. The FY2023 edition prints the NSFR ratio with a thousands separator ('10,153.88%') where the others do not; the FY2025/FY2024 editions caption the LCR row 'Total net outflows (adjusted value)' where the FY2023/FY2022 editions caption it 'Total net cash outflows (adjusted value)', and capitalise 'Total Capital ratio' where the earlier ones write 'Total capital ratio'. The most recent edition's wording is used for the row label and the variants are recorded here.
 LATEST-EDITION CHECK, 2026-09-16: taken from clear.bank's own sitemap rather than from the URLs previously cited here, because the visible /pillar-3-disclosure page does not link every file. The newest documents published are the Pillar 3 Disclosure 2025 and the Annual Report and Accounts 2025; there is no FY2026 edition of either, which is expected for a 31 December year-end (ClearBank-Annual-Report-2026.pdf returns an honest 404 while the 2025 file serves 22.2 MB of PDF). Checked, none newer. The same sweep turned up the previously-uncited FY2024 Pillar 3 and the FY2016-FY2020 Pillar 3 documents - see the correction on the other Pillar 3 sheets.</t>
         </is>

--- a/banks/CLEARBANK FINANCIALS.xlsx
+++ b/banks/CLEARBANK FINANCIALS.xlsx
@@ -4005,7 +4005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4015,9 +4015,6 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4070,21 +4067,6 @@
           <t>FY2020</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4110,9 +4092,6 @@
       <c r="G4" s="6" t="n">
         <v>26.2</v>
       </c>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
     </row>
     <row r="6" ht="190" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -4142,7 +4121,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9619,7 +9598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -9628,10 +9607,6 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9677,26 +9652,6 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
         </is>
       </c>
     </row>
@@ -9711,10 +9666,6 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -9737,10 +9688,6 @@
       <c r="F5" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -9763,10 +9710,6 @@
       <c r="F6" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -9789,10 +9732,6 @@
       <c r="F7" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -9805,10 +9744,6 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -9831,10 +9766,6 @@
       <c r="F9" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -9847,10 +9778,6 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -9883,10 +9810,6 @@
           <t>139.70%</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -9919,10 +9842,6 @@
           <t>139.70%</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -9955,10 +9874,6 @@
           <t>139.70%</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -9971,10 +9886,6 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -10007,10 +9918,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -10043,10 +9950,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -10059,10 +9962,6 @@
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -10095,10 +9994,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -10131,10 +10026,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -10167,10 +10058,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -10203,10 +10090,6 @@
           <t>21.77%</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -10239,10 +10122,6 @@
           <t>83.83%</t>
         </is>
       </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -10255,10 +10134,6 @@
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -10281,10 +10156,6 @@
       <c r="F24" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -10317,10 +10188,6 @@
           <t>38.79%</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -10333,10 +10200,6 @@
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -10359,10 +10222,6 @@
       <c r="F27" s="6" t="n">
         <v>2719</v>
       </c>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -10385,10 +10244,6 @@
       <c r="F28" s="6" t="n">
         <v>1462</v>
       </c>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -10411,10 +10266,6 @@
       <c r="F29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -10437,10 +10288,6 @@
       <c r="F30" s="6" t="n">
         <v>1462</v>
       </c>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -10473,10 +10320,6 @@
           <t>185.94%</t>
         </is>
       </c>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -10489,10 +10332,6 @@
       <c r="D32" s="6" t="n"/>
       <c r="E32" s="6" t="n"/>
       <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
-      <c r="J32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -10515,10 +10354,6 @@
       <c r="F33" s="6" t="n">
         <v>1190</v>
       </c>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -10541,10 +10376,6 @@
       <c r="F34" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G34" s="6" t="n"/>
-      <c r="H34" s="6" t="n"/>
-      <c r="I34" s="6" t="n"/>
-      <c r="J34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -10577,10 +10408,6 @@
           <t>11701.32%</t>
         </is>
       </c>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
-      <c r="J35" s="6" t="n"/>
     </row>
     <row r="37" ht="520" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
@@ -10606,7 +10433,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A37:F37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/CLEARBANK FINANCIALS.xlsx
+++ b/banks/CLEARBANK FINANCIALS.xlsx
@@ -1631,6 +1631,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3485,7 +3486,7 @@
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
 Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
@@ -3658,7 +3659,7 @@
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
 Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
@@ -3813,7 +3814,7 @@
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
 Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
@@ -3986,7 +3987,7 @@
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
 Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
@@ -4114,7 +4115,7 @@
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
 Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
@@ -4513,7 +4514,7 @@
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
 Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
@@ -4687,7 +4688,7 @@
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
 Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
@@ -4867,7 +4868,7 @@
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
 Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
@@ -4972,54 +4973,54 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure; FY2024 Pillar 3 (PDF p.8) says only that the 2024 Resolution Communication left resolution strategy and MREL unchanged for 2025</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – FY2021 Pillar 3 MREL section (PDF p.11): 'Currently, ClearBank is not required to hold any additional capital in respect of MREL'</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure; FY2017 Pillar 3 says only that MREL applied from 1 Jan 2016, fully phased in by 1 Jan 2022</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed - no MREL ratio or qualitative MREL statement found in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.</t>
+          <t>Note: CORRECTED 2026-09-19 (GA-020). This note previously said no qualitative MREL statement appears in any Pillar 3 or Annual Report. That was wrong: the Pillar 3 documents carry an MREL section in FY2017 (phase-in dates only), FY2018 (PDF p.10), FY2019 (p.10), FY2020 (p.10) and FY2021 (p.11) - the last four stating that ClearBank has been informed by the PRA that it is not currently required to hold any additional capital in respect of MREL - and FY2024 (p.8) notes that the 2024 Resolution Communication left its resolution strategy and MREL unchanged for 2025. No MREL ratio or requirement figure is published in any year and none is derived. FY2022, FY2023 and FY2025 Pillar 3 documents and every Annual Report FY2016-FY2025 available return zero hits for 'MREL' (full-text search 2026-09-19).</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5045,7 @@
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
 Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
@@ -10581,7 +10582,7 @@
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
 Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
@@ -10754,7 +10755,7 @@
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
 Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). MREL not disclosed anywhere in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025), no reason given.
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>

--- a/banks/CLEARBANK FINANCIALS.xlsx
+++ b/banks/CLEARBANK FINANCIALS.xlsx
@@ -116,7 +116,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="45" customHeight="1">
+    <row r="36" ht="65" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. Statement of Changes in Equity Summary: FY2024's Opening equity is a new ultimate parent entity's own balance (ClearBank Group Holdings Limited, inserted above ClearBank Limited during FY2024), not a continuation of FY2023's Closing equity - see the Statement of Changes in Equity sheet for the full entity-change note. NSFR omitted from this chart (values in the thousands of percent would flatten every other series) - see the NSFR sheet directly. HD-019: this workbook's year range now extends back to FY2017, ClearBank's independently-verified floor (first year with any customer deposits/income, following the bank's actual opening to customers in October 2017) - not FY2015, which an earlier ticket-generation pass had assumed purely from the entity's GLEIF incorporation date. See the HD-019 FLOOR VERIFICATION comment block near the top of build_clearbank.py and the Balance Sheet sheet's Sources note for the full evidence trail.</t>
@@ -3350,7 +3350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3465,7 +3465,7 @@
         <v>23.681</v>
       </c>
     </row>
-    <row r="6" ht="190" customHeight="1">
+    <row r="6" ht="377" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
@@ -3484,7 +3484,14 @@
   FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
   FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
-Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="190" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
@@ -3492,8 +3499,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A8:J8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3505,7 +3513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3638,7 +3646,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="190" customHeight="1">
+    <row r="6" ht="377" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
@@ -3657,7 +3665,14 @@
   FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
   FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
-Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="190" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
@@ -3665,8 +3680,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A8:J8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3678,7 +3694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3793,7 +3809,7 @@
         <v>23.681</v>
       </c>
     </row>
-    <row r="6" ht="190" customHeight="1">
+    <row r="6" ht="377" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
@@ -3812,7 +3828,14 @@
   FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
   FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
-Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="190" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
@@ -3820,8 +3843,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A8:J8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3833,7 +3857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3966,7 +3990,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="190" customHeight="1">
+    <row r="6" ht="377" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
@@ -3985,7 +4009,14 @@
   FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
   FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
-Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="190" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
@@ -3993,8 +4024,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A8:J8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4006,7 +4038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4094,7 +4126,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="6" ht="190" customHeight="1">
+    <row r="6" ht="364" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
@@ -4112,7 +4144,14 @@
   FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
   FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
   FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
-  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="208" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
@@ -4121,7 +4160,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4353,7 +4393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4486,14 +4526,572 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="156" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 figure is on the "UK leverage ratio" basis (39% as originally disclosed in ClearBank's own FY2021 Pillar 3 document), consistent with the "excluding claims on central banks" basis used FY2022 onward - see the LEVERAGE RATIO BASIS NOTE in this sheet's source citation for the very different "CRD leverage ratio" (1%) also disclosed for FY2021 on a different exposure-measure definition.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="190" customHeight="1">
+          <t xml:space="preserve">Note: FY2021 figure is on the "UK leverage ratio" basis (39% as originally disclosed in ClearBank's own FY2021 Pillar 3 document), consistent with the "excluding claims on central banks" basis used FY2022 onward - see the LEVERAGE RATIO BASIS NOTE in this sheet's source citation for the very different "CRD leverage ratio" (1%) also disclosed for FY2021 on a different exposure-measure definition.
+ONE LEVERAGE BASIS ONLY - CHECKED AND RECORDED 2026-10-09 (GA-026). Template UK LR2 (LRCom) asks for BOTH leverage measures - rows 24 and UK-25c on the including-claims-on-central-banks basis, UK-24b and 25 on the excluding basis, with the reconciling deduction at UK-24a - and 47 workbooks in this corpus carry both. This sheet carries the excluding side alone because that is all this bank publishes, not because the including side was missed.
+HOW THAT WAS ESTABLISHED: all 10 source URLs cited on this sheet and its KM1 sheet were re-fetched on 2026-10-09 (10 returned a real PDF, %PDF magic bytes checked), and each document's full text was searched for an LR2/LRCom template and for the 'including claims on central banks' wording. Every match was opened and read on 2026-10-09; none is an in-scope disclosure. In PRE-2022 editions the hit is the OLD CRR 'Leverage ratio common disclosure', not the UK dual-basis template: it prints a single 'Leverage ratio total exposure measure' with no excluding/including split, which is why those same documents carry no 'excluding claims on central banks' wording either. The UK split took effect only for periods from 1 January 2022, so those editions confirm the dual basis did not yet exist rather than offering a figure to carry. The bank files UK KM1, whose leverage block (rows 13 and 14) asks only for the excluding measure; a KM1 filer that publishes no LR2 therefore discloses one basis.
+THIS IS A RECORDED FINDING, NOT AN UNCHECKED GAP. Do not reopen it on the sheet's shape alone. It should be reopened when a NEW edition appears, since a bank can begin printing LR2 at any time - Aldermore's FY2026 report is the first of its eight editions to do so. And note the method's own limit: the text search is defeated by a figure wrapping into the middle of a label (UBP's KM1 renders as '...excluding claims  4,407,957  on central banks'), so a hit was always read by hand and only a clean zero across every edition supports this finding. </t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="377" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
+FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
+FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="190" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A9:J9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank Limited — LCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>396.85%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>381.88%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>445.36%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>297.05%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>185.94%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>186%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>127%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>237%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>3718%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="377" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
+FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
+FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="190" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A8:J8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank Limited — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20366.50%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>15959.22%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>10153.88%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>5429.15%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>11701.32%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>3298%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>324%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>432%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>878%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Extreme values (5,000%-20,000%+) are genuine, not a transcription error - ClearBank's clearing-bank business model holds very large customer deposit balances relative to a small lending book, so required stable funding is tiny relative to available stable funding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="377" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
+FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
+FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="190" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A9:J9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank Limited — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure; FY2024 Pillar 3 (PDF p.8) says only that the 2024 Resolution Communication left resolution strategy and MREL unchanged for 2025</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – FY2021 Pillar 3 MREL section (PDF p.11): 'Currently, ClearBank is not required to hold any additional capital in respect of MREL'</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure; FY2017 Pillar 3 says only that MREL applied from 1 Jan 2016, fully phased in by 1 Jan 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: CORRECTED 2026-09-19 (GA-020). This note previously said no qualitative MREL statement appears in any Pillar 3 or Annual Report. That was wrong: the Pillar 3 documents carry an MREL section in FY2017 (phase-in dates only), FY2018 (PDF p.10), FY2019 (p.10), FY2020 (p.10) and FY2021 (p.11) - the last four stating that ClearBank has been informed by the PRA that it is not currently required to hold any additional capital in respect of MREL - and FY2024 (p.8) notes that the 2024 Resolution Communication left its resolution strategy and MREL unchanged for 2025. No MREL ratio or requirement figure is published in any year and none is derived. FY2022, FY2023 and FY2025 Pillar 3 documents and every Annual Report FY2016-FY2025 available return zero hits for 'MREL' (full-text search 2026-09-19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="390" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
@@ -4513,31 +5111,39 @@
   FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
 Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
-FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A9:J9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -4552,514 +5158,910 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — LCR</t>
+          <t>ClearBank — Consolidated Statement of Financial Position</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£'000. FY2023 is Company-only (no Consolidated statements published that year). See source note at bottom.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 (£'000)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 (£'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 (£'000)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 (£'000)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2021 (£'000)</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY2020 (£'000)</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY2019 (£'000)</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY2018 (£'000)</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>FY2017</t>
+          <t>FY2017 (£'000)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Liquidity Coverage Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>396.85%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>381.88%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>445.36%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>297.05%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>185.94%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>186%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>127%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>237%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>3718%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="190" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
-REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
-FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
-FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
-FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
-FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
-FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
-  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
-  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
-  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
-  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
-  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
-Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
-FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>17956976</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>10961293</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>6256126</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>3125862</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>2720797</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1013224</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>526594</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>62527</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>27062</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n">
+        <v>19525</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>9156</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>5962</v>
+      </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Collateral placed</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>509</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1368</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1352</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>433</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>406</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>370</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>364</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>17296</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>10408</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>9768</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>6212</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>4478</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>4565</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>3900</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>1487</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Current tax asset / due from UK tax authorities</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1563</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>753</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>3542</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Right-of-use asset</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>549</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>2111</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>952</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>2677</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>4530</v>
+      </c>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>566</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>451</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>673</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>351</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>819</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>51683</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>52670</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>41806</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>29184</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>27479</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>22475</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>18751</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>13924</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>6728</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax asset</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>39779</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>35426</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>33682</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>25956</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>12525</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>9484</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>8335</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>8335</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>3652</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>18068355</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>11064063</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>6366850</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>3204409</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>2772608</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1052971</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>562825</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>87456</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>40015</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Customer deposits</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>17826803</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>10818568</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>6147363</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>2982259</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>2644756</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>925890</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>457981</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>44145</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Other payables</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>27067</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>20708</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>82372</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>109307</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>9897</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>6591</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>8570</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>6403</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>4367</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Lease obligations</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1256</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>2219</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1003</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>2789</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>509</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>2483</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>4520</v>
+      </c>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Deferred income</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>390</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>277</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>6444</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>22742</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>45229</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>59760</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>51512</v>
+      </c>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Current tax liability</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n">
+        <v>142</v>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>17855516</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>10841772</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>6237324</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>3117097</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>2700391</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>994724</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>522583</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>50548</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>5968</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Called up share capital</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Share premium</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>224403</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>224403</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>203445</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>192349</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>191816</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>157316</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>113204</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>78329</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>53458</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Treasury shares</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n">
+        <v>-204</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-204</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-204</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-204</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>-204</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>-204</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Capital contribution reserve</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>11942</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>9188</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>26805</v>
+      </c>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Share-based payment reserve</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n">
+        <v>24933</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>17190</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>9519</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>5723</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>3301</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Retained earnings/(losses)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>-24512</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>-10518</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>-100724</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>-129650</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>-136468</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>-108268</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>-78472</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>-44518</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>-19674</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Translation reserve</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>1004</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>-784</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n">
+        <v>-116</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>-117</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-116</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>212839</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>222291</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>129526</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>87312</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>72217</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>58247</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>40242</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>36908</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>34047</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>18068355</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>11064063</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>6366850</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>3204409</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>2772608</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>1052971</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>562825</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>87456</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>40015</v>
+      </c>
+    </row>
+    <row r="33" ht="390" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank's own Statement of Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, transcribed from each year's own report:
+FY2025/FY2024: Consolidated statements, ClearBank Group Holdings Limited Annual Report and Accounts 2025, pp.68-70 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2025.pdf
+FY2023: Company statements (no Consolidated statements published that year), ClearBank Annual Report and Accounts 2023, pp.69-72 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts-2023.pdf
+FY2022: Consolidated statements, own originally-published figures (not FY2023's restated comparative - see Note 32 of the FY2023 report), ClearBank Annual Report and Accounts 2022, pp.80-83 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts_2022.pdf
+FY2021: Consolidated statements, ClearBank Limited Annual Report and Accounts 2021, pp.60-63 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2021.pdf
+FY2020: Consolidated statements, ClearBank Limited Annual Report and Accounts 2020, pp.66-70 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf
+FY2019: Consolidated statements, ClearBank Limited Annual Report and Accounts 2019, pp.66-71 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: Consolidated statements, ClearBank Limited 2018 Annual Report, pp.54-58 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: Consolidated statements, ClearBank Limited 2017 Annual Report, pp.46-52 (own-year figures; cross-checked against AR2018's own FY2017 comparative column, which matches exactly - no restatement between vintages for this year) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+FLOOR VERIFICATION NOTE (HD-019): ClearBank Limited was incorporated 17 August 2015, but its first Annual Report covers a 16-month pre-operational stub period (17 Aug 2015 - 31 Dec 2016) with nil customer accounts, nil lending, and nil income throughout - see the HD-019 FLOOR VERIFICATION comment block near the top of this script for the full evidence trail. FY2017 (the first year with any customer deposits or income at all, following the bank's actual opening to customers in October 2017) is the confirmed, independently verified floor for this workbook - not FY2015/FY2016.
+ENTITY-CHANGE NOTE (corrected on follow-up review against ClearBank Group Holdings Limited's own FY2023 Companies House filing, company 14254435): FY2021-FY2023 figures are ClearBank Limited's own statements (Companies House 09736376). FY2024/FY2025 figures are instead from the Annual Report and Accounts 2025, whose auditor's report and Statement of Financial Position are addressed to "ClearBank Group Holdings Limited" - a NEW intermediate holding entity (incorporated 25 July 2022) inserted above ClearBank Limited DURING FY2023, not between FY2023 and FY2024 as an earlier pass of this workbook stated. Per that entity's own first Group accounts (period ended 31 December 2023, filed at Companies House 18 May 2024 - https://find-and-update.company-information.service.gov.uk/company/14254435/filing-history/MzQyMTUzMzg4NGFkaXF6a2N4/document?format=pdf&amp;download=0), its inaugural subsidiary ClearBank Europe N.V. was incorporated 6 March 2023; it acquired 100% of ClearBank Limited on 8 December 2023 as a Business Combination Under Common Control, with ClearBank Limited's results consolidated from 1 May 2023 (the day after common control was established, 30 April 2023). "CB Growth Holdings Limited" (named in AR2023's own equity note 3, and confirmed in ClearBank Group Holdings Limited's own Note 1.4 as "its parent") is a GENUINELY SEPARATE, higher entity in the group chain - not an earlier name for ClearBank Group Holdings Limited (no Companies House previous-names record exists for company 14254435, and its own filing history shows no rename). The corrected chain, top to bottom, is: CB Growth Holdings Limited -&gt; ClearBank Group Holdings Limited (14254435) -&gt; ClearBank Limited. This is a genuine change of reporting entity, not a presentation choice: the Statement of Changes in Equity's FY2024 opening balance (£196,497k) does not equal FY2023's own closing balance (£129,526k) below, and the two entities' equity bases are not directly comparable, so no plug/bridging row is used across that boundary in this sheet. However, a genuine bridge DOES exist and is now cited for traceability: ClearBank Group Holdings Limited's own stub-period Consolidated statement of changes in equity (in the filing above) runs from £(812)k total equity at 1 March 2023 (its own first reporting date) to exactly £196,497k at 31 December 2023 - i.e. this workbook's existing FY2024 opening figure is that entity's own closing balance for its first, ~10-month accounting period, built mostly from a £179,405k share capital issuance (the mechanism for the ClearBank Limited acquisition) rather than organic trading profit. This bridging period is not added as its own column here since it doesn't align with this workbook's FY-year grid, but the £196,497k figure is now independently verified against its true source rather than only appearing as an unexplained opening balance. Balance Sheet and P&amp;L totals for each year are still internally consistent (assets = liabilities + equity; income - expenses = profit/loss) since each is a same-entity, same-year snapshot - only the cross-year equity roll-forward is affected. FY2023's own Statement of Financial Position/Comprehensive Income are Company-only (ClearBank Limited did not publish Consolidated statements that year - see the Company vs Consolidated presentation note below); FY2021/FY2022/FY2024/FY2025 are Consolidated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="380" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Per project convention, each year's own originally-published figures are used throughout (FY2022's own AR2022 Consolidated figures, not AR2023's restated comparative - see CASH_FLOW_SOURCES' existing ENTITY_NOTE for the same convention applied to Cash Flow).
+PRESENTATION NOTE: FY2021's own Statement of Comprehensive Income discloses only Net interest income and Net fee income (no separate Interest income/expense or Fee income/expense split) - per AR2022's own footnote, "In 2021, only net interest income and net fee income were presented without splitting for gross amounts." FY2023's own Statement of Comprehensive Income additionally has an "Expenses recharged" line (income, not cost) not present in any other year, resulting in a positive "Operating profit" that year rather than the "Operating loss" label used elsewhere - both reproduced as reported. Balance Sheet: "Loans and advances to banks" (an interbank placement, not a customer loan) appears as its own line FY2021-FY2023 only - dropped from FY2024/FY2025's presentation (folded into Cash and cash equivalents per the Group's own accounting policy note). "Due from UK tax authorities" (FY2022/FY2023) and "Current tax asset" (FY2024/FY2025) are the same concept under different labels; FY2021 has neither line. Equity: "Share-based payment reserve" (FY2021/FY2022) was replaced by "Capital contribution reserve" from FY2023 onward (see the entity-change note above); "Treasury shares" and "Translation reserve" are absent from FY2023's Company-only presentation, present in every other year's Consolidated presentation.
+FY2017-FY2020 presentation: "Amounts due to customers" (FY2017 label) and "Customer deposits" (FY2018-FY2020 label) are the same concept under different labels - ClearBank opened to customers in October 2017, so FY2017's figure (£1,601k) reflects barely two months of customer-facing activity. "Right-of-use assets"/"Lease obligations" first appear in FY2019 (adoption of IFRS 16, replacing IAS 17 - see the Group's own Note 3.1) - absent FY2017/FY2018. "Translation reserve" first appears in FY2019 (a small foreign currency translation difference of £33k) - absent FY2017/FY2018, which had no foreign operations giving rise to translation differences. "Deferred income" first appears in FY2019 - absent FY2017/FY2018. FY2017's Statement of Comprehensive Income shows no Interest expense line (Net interest income was not yet split into gross Interest income/expense until FY2019) and no Impairments line (first appears FY2019).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:J6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A33:J33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ClearBank Limited — NSFR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Net Stable Funding Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20366.50%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>15959.22%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>10153.88%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>5429.15%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>11701.32%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>3298%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>324%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>432%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>878%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Extreme values (5,000%-20,000%+) are genuine, not a transcription error - ClearBank's clearing-bank business model holds very large customer deposit balances relative to a small lending book, so required stable funding is tiny relative to available stable funding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="190" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
-REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
-FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
-FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
-FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
-FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
-FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
-  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
-  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
-  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
-  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
-  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
-Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
-FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A7:J7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ClearBank Limited — MREL Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>MREL Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure; FY2024 Pillar 3 (PDF p.8) says only that the 2024 Resolution Communication left resolution strategy and MREL unchanged for 2025</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – FY2021 Pillar 3 MREL section (PDF p.11): 'Currently, ClearBank is not required to hold any additional capital in respect of MREL'</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure; FY2017 Pillar 3 says only that MREL applied from 1 Jan 2016, fully phased in by 1 Jan 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: CORRECTED 2026-09-19 (GA-020). This note previously said no qualitative MREL statement appears in any Pillar 3 or Annual Report. That was wrong: the Pillar 3 documents carry an MREL section in FY2017 (phase-in dates only), FY2018 (PDF p.10), FY2019 (p.10), FY2020 (p.10) and FY2021 (p.11) - the last four stating that ClearBank has been informed by the PRA that it is not currently required to hold any additional capital in respect of MREL - and FY2024 (p.8) notes that the 2024 Resolution Communication left its resolution strategy and MREL unchanged for 2025. No MREL ratio or requirement figure is published in any year and none is derived. FY2022, FY2023 and FY2025 Pillar 3 documents and every Annual Report FY2016-FY2025 available return zero hits for 'MREL' (full-text search 2026-09-19).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
-REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
-FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
-FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
-FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
-FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
-FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
-  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
-  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
-  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
-  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
-  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
-Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
-FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A7:J7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5083,7 +6085,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank — Consolidated Statement of Financial Position</t>
+          <t>ClearBank — Consolidated Statement of Comprehensive Income</t>
         </is>
       </c>
     </row>
@@ -5149,7 +6151,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Assets</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -5165,144 +6167,136 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>17956976</v>
+        <v>625779</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>10961293</v>
+        <v>425289</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>6256126</v>
+        <v>243956</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>3125862</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>2720797</v>
-      </c>
+        <v>43774</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n">
-        <v>1013224</v>
+        <v>900</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>526594</v>
+        <v>1664</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>62527</v>
+        <v>178</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>27062</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Loans and advances to banks</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-554816</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-358179</v>
+      </c>
       <c r="D6" s="6" t="n">
-        <v>19525</v>
+        <v>-162042</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>9156</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>5962</v>
-      </c>
+        <v>-9911</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
+      <c r="H6" s="6" t="n">
+        <v>-567</v>
+      </c>
       <c r="I6" s="6" t="n"/>
       <c r="J6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Collateral placed</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>509</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>1368</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>1352</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>433</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>406</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>370</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>364</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>364</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>315</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>70963</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>67110</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>81914</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>33863</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1842</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1097</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Receivables</t>
+          <t>Fee income</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>17296</v>
+        <v>66183</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>10408</v>
+        <v>47141</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>9768</v>
+        <v>31390</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6212</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>4478</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>4565</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>3900</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>1487</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>1176</v>
-      </c>
+        <v>25455</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Current tax asset / due from UK tax authorities</t>
+          <t>Fee expenses</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>1563</v>
+        <v>-5268</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>753</v>
+        <v>-2952</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3542</v>
+        <v>-2620</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>4363</v>
+        <v>-1047</v>
       </c>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="n"/>
@@ -5311,327 +6305,333 @@
       <c r="J9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Right-of-use asset</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>549</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>2111</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>952</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>2677</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>510</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>2180</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>4530</v>
-      </c>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net fee income</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>60915</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>44189</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>28770</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>24408</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>18614</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>8785</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>3441</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>660</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Property, plant and equipment</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0</v>
+        <v>806</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>34</v>
+        <v>787</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>97</v>
+        <v>663</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>566</v>
+        <v>13</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>451</v>
+        <v>938</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>673</v>
+        <v>933</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>351</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>819</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>1082</v>
-      </c>
+        <v>780</v>
+      </c>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Intangible assets</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>51683</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>52670</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>41806</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>29184</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>27479</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>22475</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>18751</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>13924</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>6728</v>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>132684</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>112086</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>111347</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>58284</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>21394</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>10618</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>5318</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>838</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Deferred tax asset</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>39779</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>35426</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>33682</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>25956</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>12525</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>9484</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>8335</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>8335</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>3652</v>
-      </c>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Total assets</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>18068355</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>11064063</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>6366850</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>3204409</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>2772608</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>1052971</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>562825</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>87456</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>40015</v>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Staff costs</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>-78740</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-67335</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-55318</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-40095</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-27719</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-20995</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-16573</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-14439</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-7377</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Liabilities</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>-2265</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>-1693</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-2212</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-1334</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-2145</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-3432</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-2891</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>-620</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-490</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Customer deposits</t>
+          <t>Amortisation of intangibles</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>17826803</v>
+        <v>-15706</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>10818568</v>
+        <v>-11643</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>6147363</v>
+        <v>-8869</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>2982259</v>
+        <v>-7824</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>2644756</v>
+        <v>-5791</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>925890</v>
+        <v>-3750</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>457981</v>
+        <v>-2914</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>44145</v>
+        <v>-1745</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1601</v>
+        <v>-334</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Other payables</t>
+          <t>Impairment</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>27067</v>
+        <v>-936</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>20708</v>
+        <v>-1584</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>82372</v>
+        <v>-268</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>109307</v>
+        <v>-675</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>9897</v>
+        <v>-337</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>6591</v>
+        <v>-549</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>8570</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>6403</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>4367</v>
-      </c>
+        <v>-1032</v>
+      </c>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Lease obligations</t>
+          <t>Other operating expenses</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1256</v>
+        <v>-51287</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2219</v>
+        <v>-39780</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1003</v>
+        <v>-39116</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>2789</v>
+        <v>-27710</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>509</v>
+        <v>-16447</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>2483</v>
+        <v>-12557</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>4520</v>
-      </c>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
+        <v>-15682</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>-13567</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>-9396</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Deferred income</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>390</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>277</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>6444</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>22742</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>45229</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>59760</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>51512</v>
-      </c>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>-148934</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-122035</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-105783</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-77638</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-52439</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-41283</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>-39092</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>-30371</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>-17597</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Current tax liability</t>
+          <t>Expenses recharged</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n">
-        <v>142</v>
-      </c>
-      <c r="E20" s="6" t="n"/>
+        <v>13054</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>8587</v>
+      </c>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
@@ -5641,317 +6641,283 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>Operating profit/(loss)</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>17855516</v>
+        <v>-16250</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>10841772</v>
+        <v>-9949</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>6237324</v>
+        <v>18618</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>3117097</v>
+        <v>-10767</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>2700391</v>
+        <v>-31045</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>994724</v>
+        <v>-30665</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>522583</v>
+        <v>-33774</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>50548</v>
+        <v>-29533</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>5968</v>
+        <v>-17548</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Other gains/(losses)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>-354</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>-165</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>-111</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>-181</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>6</v>
+      </c>
       <c r="J22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Called up share capital</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>2</v>
+        <v>-106</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
+        <v>-130</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-78</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>-55</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-34</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-73</v>
+      </c>
       <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
+      <c r="J23" s="6" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Share premium</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>224403</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>224403</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>203445</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>192349</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>191816</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>157316</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>113204</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>78329</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>53458</v>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year before taxation</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-16710</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-10244</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>18429</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-11003</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-31074</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-30777</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-33843</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>-29527</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>-17551</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Treasury shares</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
+          <t>Taxation</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>945</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-74</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>3967</v>
+      </c>
       <c r="E25" s="6" t="n">
-        <v>-204</v>
+        <v>17821</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-204</v>
+        <v>2874</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-204</v>
+        <v>981</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-204</v>
+        <v>-153</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-204</v>
+        <v>4683</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>-204</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Capital contribution reserve</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>11942</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>9188</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>26805</v>
-      </c>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year after taxation</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-15765</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-10318</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>22396</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>6818</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-28200</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>-29796</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>-33996</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>-24844</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>-13899</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Share-based payment reserve</t>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n">
-        <v>24933</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>17190</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>9519</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>5723</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>3301</v>
-      </c>
-      <c r="J27" s="6" t="n">
-        <v>467</v>
-      </c>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Retained earnings/(losses)</t>
+          <t>Foreign currency translation differences</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>-24512</v>
+        <v>1788</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>-10518</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>-100724</v>
-      </c>
+        <v>-767</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
       <c r="E28" s="6" t="n">
-        <v>-129650</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>-136468</v>
+        <v>-1</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-108268</v>
+        <v>-107</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-78472</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>-44518</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>-19674</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Translation reserve</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>1004</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>-784</v>
-      </c>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n">
-        <v>-116</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>-117</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>-116</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>-9</v>
-      </c>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Total equity</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>212839</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>222291</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>129526</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>87312</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>72217</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>58247</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>40242</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>36908</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>34047</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Total liabilities and equity</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>18068355</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>11064063</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>6366850</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>3204409</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>2772608</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>1052971</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>562825</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>87456</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>40015</v>
-      </c>
-    </row>
-    <row r="33" ht="380" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>-13977</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>-11085</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>22396</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>6819</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-28201</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-29903</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-33963</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>-24844</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>-13899</v>
+      </c>
+    </row>
+    <row r="31" ht="390" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank's own Statement of Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, transcribed from each year's own report:
 FY2025/FY2024: Consolidated statements, ClearBank Group Holdings Limited Annual Report and Accounts 2025, pp.68-70 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2025.pdf
@@ -5963,896 +6929,23 @@
 FY2018: Consolidated statements, ClearBank Limited 2018 Annual Report, pp.54-58 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
 FY2017: Consolidated statements, ClearBank Limited 2017 Annual Report, pp.46-52 (own-year figures; cross-checked against AR2018's own FY2017 comparative column, which matches exactly - no restatement between vintages for this year) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
 FLOOR VERIFICATION NOTE (HD-019): ClearBank Limited was incorporated 17 August 2015, but its first Annual Report covers a 16-month pre-operational stub period (17 Aug 2015 - 31 Dec 2016) with nil customer accounts, nil lending, and nil income throughout - see the HD-019 FLOOR VERIFICATION comment block near the top of this script for the full evidence trail. FY2017 (the first year with any customer deposits or income at all, following the bank's actual opening to customers in October 2017) is the confirmed, independently verified floor for this workbook - not FY2015/FY2016.
-ENTITY-CHANGE NOTE (corrected on follow-up review against ClearBank Group Holdings Limited's own FY2023 Companies House filing, company 14254435): FY2021-FY2023 figures are ClearBank Limited's own statements (Companies House 09736376). FY2024/FY2025 figures are instead from the Annual Report and Accounts 2025, whose auditor's report and Statement of Financial Position are addressed to "ClearBank Group Holdings Limited" - a NEW intermediate holding entity (incorporated 25 July 2022) inserted above ClearBank Limited DURING FY2023, not between FY2023 and FY2024 as an earlier pass of this workbook stated. Per that entity's own first Group accounts (period ended 31 December 2023, filed at Companies House 18 May 2024 - https://find-and-update.company-information.service.gov.uk/company/14254435/filing-history/MzQyMTUzMzg4NGFkaXF6a2N4/document?format=pdf&amp;download=0), its inaugural subsidiary ClearBank Europe N.V. was incorporated 6 March 2023; it acquired 100% of ClearBank Limited on 8 December 2023 as a Business Combination Under Common Control, with ClearBank Limited's results consolidated from 1 May 2023 (the day after common control was established, 30 April 2023). "CB Growth Holdings Limited" (named in AR2023's own equity note 3, and confirmed in ClearBank Group Holdings Limited's own Note 1.4 as "its parent") is a GENUINELY SEPARATE, higher entity in the group chain - not an earlier name for ClearBank Group Holdings Limited (no Companies House previous-names record exists for company 14254435, and its own filing history shows no rename). The corrected chain, top to bottom, is: CB Growth Holdings Limited -&gt; ClearBank Group Holdings Limited (14254435) -&gt; ClearBank Limited. This is a genuine change of reporting entity, not a presentation choice: the Statement of Changes in Equity's FY2024 opening balance (£196,497k) does not equal FY2023's own closing balance (£129,526k) below, and the two entities' equity bases are not directly comparable, so no plug/bridging row is used across that boundary in this sheet. However, a genuine bridge DOES exist and is now cited for traceability: ClearBank Group Holdings Limited's own stub-period Consolidated statement of changes in equity (in the filing above) runs from £(812)k total equity at 1 March 2023 (its own first reporting date) to exactly £196,497k at 31 December 2023 - i.e. this workbook's existing FY2024 opening figure is that entity's own closing balance for its first, ~10-month accounting period, built mostly from a £179,405k share capital issuance (the mechanism for the ClearBank Limited acquisition) rather than organic trading profit. This bridging period is not added as its own column here since it doesn't align with this workbook's FY-year grid, but the £196,497k figure is now independently verified against its true source rather than only appearing as an unexplained opening balance. Balance Sheet and P&amp;L totals for each year are still internally consistent (assets = liabilities + equity; income - expenses = profit/loss) since each is a same-entity, same-year snapshot - only the cross-year equity roll-forward is affected. FY2023's own Statement of Financial Position/Comprehensive Income are Company-only (ClearBank Limited did not publish Consolidated statements that year - see the Company vs Consolidated presentation note below); FY2021/FY2022/FY2024/FY2025 are Consolidated. Per project convention, each year's own originally-published figures are used throughout (FY2022's own AR2022 Consolidated figures, not AR2023's restated comparative - see CASH_FLOW_SOURCES' existing ENTITY_NOTE for the same convention applied to Cash Flow).
+ENTITY-CHANGE NOTE (corrected on follow-up review against ClearBank Group Holdings Limited's own FY2023 Companies House filing, company 14254435): FY2021-FY2023 figures are ClearBank Limited's own statements (Companies House 09736376). FY2024/FY2025 figures are instead from the Annual Report and Accounts 2025, whose auditor's report and Statement of Financial Position are addressed to "ClearBank Group Holdings Limited" - a NEW intermediate holding entity (incorporated 25 July 2022) inserted above ClearBank Limited DURING FY2023, not between FY2023 and FY2024 as an earlier pass of this workbook stated. Per that entity's own first Group accounts (period ended 31 December 2023, filed at Companies House 18 May 2024 - https://find-and-update.company-information.service.gov.uk/company/14254435/filing-history/MzQyMTUzMzg4NGFkaXF6a2N4/document?format=pdf&amp;download=0), its inaugural subsidiary ClearBank Europe N.V. was incorporated 6 March 2023; it acquired 100% of ClearBank Limited on 8 December 2023 as a Business Combination Under Common Control, with ClearBank Limited's results consolidated from 1 May 2023 (the day after common control was established, 30 April 2023). "CB Growth Holdings Limited" (named in AR2023's own equity note 3, and confirmed in ClearBank Group Holdings Limited's own Note 1.4 as "its parent") is a GENUINELY SEPARATE, higher entity in the group chain - not an earlier name for ClearBank Group Holdings Limited (no Companies House previous-names record exists for company 14254435, and its own filing history shows no rename). The corrected chain, top to bottom, is: CB Growth Holdings Limited -&gt; ClearBank Group Holdings Limited (14254435) -&gt; ClearBank Limited. This is a genuine change of reporting entity, not a presentation choice: the Statement of Changes in Equity's FY2024 opening balance (£196,497k) does not equal FY2023's own closing balance (£129,526k) below, and the two entities' equity bases are not directly comparable, so no plug/bridging row is used across that boundary in this sheet. However, a genuine bridge DOES exist and is now cited for traceability: ClearBank Group Holdings Limited's own stub-period Consolidated statement of changes in equity (in the filing above) runs from £(812)k total equity at 1 March 2023 (its own first reporting date) to exactly £196,497k at 31 December 2023 - i.e. this workbook's existing FY2024 opening figure is that entity's own closing balance for its first, ~10-month accounting period, built mostly from a £179,405k share capital issuance (the mechanism for the ClearBank Limited acquisition) rather than organic trading profit. This bridging period is not added as its own column here since it doesn't align with this workbook's FY-year grid, but the £196,497k figure is now independently verified against its true source rather than only appearing as an unexplained opening balance. Balance Sheet and P&amp;L totals for each year are still internally consistent (assets = liabilities + equity; income - expenses = profit/loss) since each is a same-entity, same-year snapshot - only the cross-year equity roll-forward is affected. FY2023's own Statement of Financial Position/Comprehensive Income are Company-only (ClearBank Limited did not publish Consolidated statements that year - see the Company vs Consolidated presentation note below); FY2021/FY2022/FY2024/FY2025 are Consolidated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="380" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Per project convention, each year's own originally-published figures are used throughout (FY2022's own AR2022 Consolidated figures, not AR2023's restated comparative - see CASH_FLOW_SOURCES' existing ENTITY_NOTE for the same convention applied to Cash Flow).
 PRESENTATION NOTE: FY2021's own Statement of Comprehensive Income discloses only Net interest income and Net fee income (no separate Interest income/expense or Fee income/expense split) - per AR2022's own footnote, "In 2021, only net interest income and net fee income were presented without splitting for gross amounts." FY2023's own Statement of Comprehensive Income additionally has an "Expenses recharged" line (income, not cost) not present in any other year, resulting in a positive "Operating profit" that year rather than the "Operating loss" label used elsewhere - both reproduced as reported. Balance Sheet: "Loans and advances to banks" (an interbank placement, not a customer loan) appears as its own line FY2021-FY2023 only - dropped from FY2024/FY2025's presentation (folded into Cash and cash equivalents per the Group's own accounting policy note). "Due from UK tax authorities" (FY2022/FY2023) and "Current tax asset" (FY2024/FY2025) are the same concept under different labels; FY2021 has neither line. Equity: "Share-based payment reserve" (FY2021/FY2022) was replaced by "Capital contribution reserve" from FY2023 onward (see the entity-change note above); "Treasury shares" and "Translation reserve" are absent from FY2023's Company-only presentation, present in every other year's Consolidated presentation.
 FY2017-FY2020 presentation: "Amounts due to customers" (FY2017 label) and "Customer deposits" (FY2018-FY2020 label) are the same concept under different labels - ClearBank opened to customers in October 2017, so FY2017's figure (£1,601k) reflects barely two months of customer-facing activity. "Right-of-use assets"/"Lease obligations" first appear in FY2019 (adoption of IFRS 16, replacing IAS 17 - see the Group's own Note 3.1) - absent FY2017/FY2018. "Translation reserve" first appears in FY2019 (a small foreign currency translation difference of £33k) - absent FY2017/FY2018, which had no foreign operations giving rise to translation differences. "Deferred income" first appears in FY2019 - absent FY2017/FY2018. FY2017's Statement of Comprehensive Income shows no Interest expense line (Net interest income was not yet split into gross Interest income/expense until FY2019) and no Impairments line (first appears FY2019).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A33:J33"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ClearBank — Consolidated Statement of Comprehensive Income</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000. FY2023 is Company-only (no Consolidated statements published that year). See source note at bottom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025 (£'000)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024 (£'000)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023 (£'000)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022 (£'000)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021 (£'000)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020 (£'000)</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019 (£'000)</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018 (£'000)</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017 (£'000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>625779</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>425289</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>243956</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>43774</v>
-      </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n">
-        <v>900</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>1664</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>178</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>-554816</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>-358179</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>-162042</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>-9911</v>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n">
-        <v>-567</v>
-      </c>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Net interest income</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>70963</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>67110</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>81914</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>33863</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>1842</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>900</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>1097</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>178</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Fee income</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>66183</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>47141</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>31390</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>25455</v>
-      </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Fee expenses</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>-5268</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>-2952</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>-2620</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>-1047</v>
-      </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Net fee income</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>60915</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>44189</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>28770</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>24408</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>18614</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>8785</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>3441</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>660</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>806</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>787</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>663</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>938</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>933</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>780</v>
-      </c>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Total income</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>132684</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>112086</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>111347</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>58284</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>21394</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>10618</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>5318</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>838</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Staff costs</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>-78740</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>-67335</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>-55318</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>-40095</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>-27719</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>-20995</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>-16573</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>-14439</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>-7377</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>-2265</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>-1693</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>-2212</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>-1334</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>-2145</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>-3432</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>-2891</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>-620</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>-490</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Amortisation of intangibles</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>-15706</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>-11643</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>-8869</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>-7824</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>-5791</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>-3750</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>-2914</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>-1745</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>-334</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Impairment</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>-936</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>-1584</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>-268</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>-675</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>-337</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>-549</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>-1032</v>
-      </c>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Other operating expenses</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>-51287</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>-39780</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>-39116</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>-27710</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>-16447</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>-12557</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>-15682</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>-13567</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>-9396</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>-148934</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>-122035</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>-105783</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>-77638</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>-52439</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>-41283</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>-39092</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>-30371</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>-17597</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Expenses recharged</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n">
-        <v>13054</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>8587</v>
-      </c>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Operating profit/(loss)</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>-16250</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>-9949</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>18618</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>-10767</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>-31045</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>-30665</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>-33774</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>-29533</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>-17548</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Other gains/(losses)</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>-354</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>-165</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>-111</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>-181</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J22" s="6" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Finance costs</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>-106</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>-130</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>-78</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>-55</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>-34</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>-115</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>-73</v>
-      </c>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Profit/(loss) for the year before taxation</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>-16710</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>-10244</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>18429</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>-11003</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>-31074</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>-30777</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>-33843</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>-29527</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>-17551</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Taxation</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>945</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>-74</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>3967</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>17821</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>2874</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>981</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>-153</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>4683</v>
-      </c>
-      <c r="J25" s="6" t="n">
-        <v>3652</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Profit/(loss) for the year after taxation</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>-15765</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>-10318</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>22396</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>6818</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>-28200</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>-29796</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>-33996</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>-24844</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>-13899</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Other comprehensive income/(loss)</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Foreign currency translation differences</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>1788</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>-767</v>
-      </c>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>-107</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="6" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Total comprehensive income/(loss) for the year</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>-13977</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>-11085</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>22396</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>6819</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>-28201</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>-29903</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>-33963</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>-24844</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>-13899</v>
-      </c>
-    </row>
-    <row r="31" ht="380" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Sources - ClearBank's own Statement of Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, transcribed from each year's own report:
-FY2025/FY2024: Consolidated statements, ClearBank Group Holdings Limited Annual Report and Accounts 2025, pp.68-70 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2025.pdf
-FY2023: Company statements (no Consolidated statements published that year), ClearBank Annual Report and Accounts 2023, pp.69-72 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts-2023.pdf
-FY2022: Consolidated statements, own originally-published figures (not FY2023's restated comparative - see Note 32 of the FY2023 report), ClearBank Annual Report and Accounts 2022, pp.80-83 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-and-Accounts_2022.pdf
-FY2021: Consolidated statements, ClearBank Limited Annual Report and Accounts 2021, pp.60-63 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2021.pdf
-FY2020: Consolidated statements, ClearBank Limited Annual Report and Accounts 2020, pp.66-70 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf
-FY2019: Consolidated statements, ClearBank Limited Annual Report and Accounts 2019, pp.66-71 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
-FY2018: Consolidated statements, ClearBank Limited 2018 Annual Report, pp.54-58 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
-FY2017: Consolidated statements, ClearBank Limited 2017 Annual Report, pp.46-52 (own-year figures; cross-checked against AR2018's own FY2017 comparative column, which matches exactly - no restatement between vintages for this year) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-FLOOR VERIFICATION NOTE (HD-019): ClearBank Limited was incorporated 17 August 2015, but its first Annual Report covers a 16-month pre-operational stub period (17 Aug 2015 - 31 Dec 2016) with nil customer accounts, nil lending, and nil income throughout - see the HD-019 FLOOR VERIFICATION comment block near the top of this script for the full evidence trail. FY2017 (the first year with any customer deposits or income at all, following the bank's actual opening to customers in October 2017) is the confirmed, independently verified floor for this workbook - not FY2015/FY2016.
-ENTITY-CHANGE NOTE (corrected on follow-up review against ClearBank Group Holdings Limited's own FY2023 Companies House filing, company 14254435): FY2021-FY2023 figures are ClearBank Limited's own statements (Companies House 09736376). FY2024/FY2025 figures are instead from the Annual Report and Accounts 2025, whose auditor's report and Statement of Financial Position are addressed to "ClearBank Group Holdings Limited" - a NEW intermediate holding entity (incorporated 25 July 2022) inserted above ClearBank Limited DURING FY2023, not between FY2023 and FY2024 as an earlier pass of this workbook stated. Per that entity's own first Group accounts (period ended 31 December 2023, filed at Companies House 18 May 2024 - https://find-and-update.company-information.service.gov.uk/company/14254435/filing-history/MzQyMTUzMzg4NGFkaXF6a2N4/document?format=pdf&amp;download=0), its inaugural subsidiary ClearBank Europe N.V. was incorporated 6 March 2023; it acquired 100% of ClearBank Limited on 8 December 2023 as a Business Combination Under Common Control, with ClearBank Limited's results consolidated from 1 May 2023 (the day after common control was established, 30 April 2023). "CB Growth Holdings Limited" (named in AR2023's own equity note 3, and confirmed in ClearBank Group Holdings Limited's own Note 1.4 as "its parent") is a GENUINELY SEPARATE, higher entity in the group chain - not an earlier name for ClearBank Group Holdings Limited (no Companies House previous-names record exists for company 14254435, and its own filing history shows no rename). The corrected chain, top to bottom, is: CB Growth Holdings Limited -&gt; ClearBank Group Holdings Limited (14254435) -&gt; ClearBank Limited. This is a genuine change of reporting entity, not a presentation choice: the Statement of Changes in Equity's FY2024 opening balance (£196,497k) does not equal FY2023's own closing balance (£129,526k) below, and the two entities' equity bases are not directly comparable, so no plug/bridging row is used across that boundary in this sheet. However, a genuine bridge DOES exist and is now cited for traceability: ClearBank Group Holdings Limited's own stub-period Consolidated statement of changes in equity (in the filing above) runs from £(812)k total equity at 1 March 2023 (its own first reporting date) to exactly £196,497k at 31 December 2023 - i.e. this workbook's existing FY2024 opening figure is that entity's own closing balance for its first, ~10-month accounting period, built mostly from a £179,405k share capital issuance (the mechanism for the ClearBank Limited acquisition) rather than organic trading profit. This bridging period is not added as its own column here since it doesn't align with this workbook's FY-year grid, but the £196,497k figure is now independently verified against its true source rather than only appearing as an unexplained opening balance. Balance Sheet and P&amp;L totals for each year are still internally consistent (assets = liabilities + equity; income - expenses = profit/loss) since each is a same-entity, same-year snapshot - only the cross-year equity roll-forward is affected. FY2023's own Statement of Financial Position/Comprehensive Income are Company-only (ClearBank Limited did not publish Consolidated statements that year - see the Company vs Consolidated presentation note below); FY2021/FY2022/FY2024/FY2025 are Consolidated. Per project convention, each year's own originally-published figures are used throughout (FY2022's own AR2022 Consolidated figures, not AR2023's restated comparative - see CASH_FLOW_SOURCES' existing ENTITY_NOTE for the same convention applied to Cash Flow).
-PRESENTATION NOTE: FY2021's own Statement of Comprehensive Income discloses only Net interest income and Net fee income (no separate Interest income/expense or Fee income/expense split) - per AR2022's own footnote, "In 2021, only net interest income and net fee income were presented without splitting for gross amounts." FY2023's own Statement of Comprehensive Income additionally has an "Expenses recharged" line (income, not cost) not present in any other year, resulting in a positive "Operating profit" that year rather than the "Operating loss" label used elsewhere - both reproduced as reported. Balance Sheet: "Loans and advances to banks" (an interbank placement, not a customer loan) appears as its own line FY2021-FY2023 only - dropped from FY2024/FY2025's presentation (folded into Cash and cash equivalents per the Group's own accounting policy note). "Due from UK tax authorities" (FY2022/FY2023) and "Current tax asset" (FY2024/FY2025) are the same concept under different labels; FY2021 has neither line. Equity: "Share-based payment reserve" (FY2021/FY2022) was replaced by "Capital contribution reserve" from FY2023 onward (see the entity-change note above); "Treasury shares" and "Translation reserve" are absent from FY2023's Company-only presentation, present in every other year's Consolidated presentation.
-FY2017-FY2020 presentation: "Amounts due to customers" (FY2017 label) and "Customer deposits" (FY2018-FY2020 label) are the same concept under different labels - ClearBank opened to customers in October 2017, so FY2017's figure (£1,601k) reflects barely two months of customer-facing activity. "Right-of-use assets"/"Lease obligations" first appear in FY2019 (adoption of IFRS 16, replacing IAS 17 - see the Group's own Note 3.1) - absent FY2017/FY2018. "Translation reserve" first appears in FY2019 (a small foreign currency translation difference of £33k) - absent FY2017/FY2018, which had no foreign operations giving rise to translation differences. "Deferred income" first appears in FY2019 - absent FY2017/FY2018. FY2017's Statement of Comprehensive Income shows no Interest expense line (Net interest income was not yet split into gross Interest income/expense until FY2019) and no Impairments line (first appears FY2019).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
     <mergeCell ref="A31:J31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6865,7 +6958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -7964,7 +8057,7 @@
         <v>212839</v>
       </c>
     </row>
-    <row r="55" ht="380" customHeight="1">
+    <row r="55" ht="403" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank's own Statement of Comprehensive Income / Statement of Financial Position / Statement of Changes in Equity, transcribed from each year's own report:
@@ -7977,15 +8070,24 @@
 FY2018: Consolidated statements, ClearBank Limited 2018 Annual Report, pp.54-58 - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
 FY2017: Consolidated statements, ClearBank Limited 2017 Annual Report, pp.46-52 (own-year figures; cross-checked against AR2018's own FY2017 comparative column, which matches exactly - no restatement between vintages for this year) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
 FLOOR VERIFICATION NOTE (HD-019): ClearBank Limited was incorporated 17 August 2015, but its first Annual Report covers a 16-month pre-operational stub period (17 Aug 2015 - 31 Dec 2016) with nil customer accounts, nil lending, and nil income throughout - see the HD-019 FLOOR VERIFICATION comment block near the top of this script for the full evidence trail. FY2017 (the first year with any customer deposits or income at all, following the bank's actual opening to customers in October 2017) is the confirmed, independently verified floor for this workbook - not FY2015/FY2016.
-ENTITY-CHANGE NOTE (corrected on follow-up review against ClearBank Group Holdings Limited's own FY2023 Companies House filing, company 14254435): FY2021-FY2023 figures are ClearBank Limited's own statements (Companies House 09736376). FY2024/FY2025 figures are instead from the Annual Report and Accounts 2025, whose auditor's report and Statement of Financial Position are addressed to "ClearBank Group Holdings Limited" - a NEW intermediate holding entity (incorporated 25 July 2022) inserted above ClearBank Limited DURING FY2023, not between FY2023 and FY2024 as an earlier pass of this workbook stated. Per that entity's own first Group accounts (period ended 31 December 2023, filed at Companies House 18 May 2024 - https://find-and-update.company-information.service.gov.uk/company/14254435/filing-history/MzQyMTUzMzg4NGFkaXF6a2N4/document?format=pdf&amp;download=0), its inaugural subsidiary ClearBank Europe N.V. was incorporated 6 March 2023; it acquired 100% of ClearBank Limited on 8 December 2023 as a Business Combination Under Common Control, with ClearBank Limited's results consolidated from 1 May 2023 (the day after common control was established, 30 April 2023). "CB Growth Holdings Limited" (named in AR2023's own equity note 3, and confirmed in ClearBank Group Holdings Limited's own Note 1.4 as "its parent") is a GENUINELY SEPARATE, higher entity in the group chain - not an earlier name for ClearBank Group Holdings Limited (no Companies House previous-names record exists for company 14254435, and its own filing history shows no rename). The corrected chain, top to bottom, is: CB Growth Holdings Limited -&gt; ClearBank Group Holdings Limited (14254435) -&gt; ClearBank Limited. This is a genuine change of reporting entity, not a presentation choice: the Statement of Changes in Equity's FY2024 opening balance (£196,497k) does not equal FY2023's own closing balance (£129,526k) below, and the two entities' equity bases are not directly comparable, so no plug/bridging row is used across that boundary in this sheet. However, a genuine bridge DOES exist and is now cited for traceability: ClearBank Group Holdings Limited's own stub-period Consolidated statement of changes in equity (in the filing above) runs from £(812)k total equity at 1 March 2023 (its own first reporting date) to exactly £196,497k at 31 December 2023 - i.e. this workbook's existing FY2024 opening figure is that entity's own closing balance for its first, ~10-month accounting period, built mostly from a £179,405k share capital issuance (the mechanism for the ClearBank Limited acquisition) rather than organic trading profit. This bridging period is not added as its own column here since it doesn't align with this workbook's FY-year grid, but the £196,497k figure is now independently verified against its true source rather than only appearing as an unexplained opening balance. Balance Sheet and P&amp;L totals for each year are still internally consistent (assets = liabilities + equity; income - expenses = profit/loss) since each is a same-entity, same-year snapshot - only the cross-year equity roll-forward is affected. FY2023's own Statement of Financial Position/Comprehensive Income are Company-only (ClearBank Limited did not publish Consolidated statements that year - see the Company vs Consolidated presentation note below); FY2021/FY2022/FY2024/FY2025 are Consolidated. Per project convention, each year's own originally-published figures are used throughout (FY2022's own AR2022 Consolidated figures, not AR2023's restated comparative - see CASH_FLOW_SOURCES' existing ENTITY_NOTE for the same convention applied to Cash Flow).
+ENTITY-CHANGE NOTE (corrected on follow-up review against ClearBank Group Holdings Limited's own FY2023 Companies House filing, company 14254435): FY2021-FY2023 figures are ClearBank Limited's own statements (Companies House 09736376). FY2024/FY2025 figures are instead from the Annual Report and Accounts 2025, whose auditor's report and Statement of Financial Position are addressed to "ClearBank Group Holdings Limited" - a NEW intermediate holding entity (incorporated 25 July 2022) inserted above ClearBank Limited DURING FY2023, not between FY2023 and FY2024 as an earlier pass of this workbook stated. Per that entity's own first Group accounts (period ended 31 December 2023, filed at Companies House 18 May 2024 - https://find-and-update.company-information.service.gov.uk/company/14254435/filing-history/MzQyMTUzMzg4NGFkaXF6a2N4/document?format=pdf&amp;download=0), its inaugural subsidiary ClearBank Europe N.V. was incorporated 6 March 2023; it acquired 100% of ClearBank Limited on 8 December 2023 as a Business Combination Under Common Control, with ClearBank Limited's results consolidated from 1 May 2023 (the day after common control was established, 30 April 2023). "CB Growth Holdings Limited" (named in AR2023's own equity note 3, and confirmed in ClearBank Group Holdings Limited's own Note 1.4 as "its parent") is a GENUINELY SEPARATE, higher entity in the group chain - not an earlier name for ClearBank Group Holdings Limited (no Companies House previous-names record exists for company 14254435, and its own filing history shows no rename). The corrected chain, top to bottom, is: CB Growth Holdings Limited -&gt; ClearBank Group Holdings Limited (14254435) -&gt; ClearBank Limited. This is a genuine change of reporting entity, not a presentation choice: the Statement of Changes in Equity's FY2024 opening balance (£196,497k) does not equal FY2023's own closing balance (£129,526k) below, and the two entities' equity bases are not directly comparable, so no plug/bridging row is used across that boundary in this sheet. However, a genuine bridge DOES exist and is now cited for traceability: ClearBank Group Holdings Limited's own stub-period Consolidated statement of changes in equity (in the filing above) runs from £(812)k total equity at 1 March 2023 (its own first reporting date) to exactly £196,497k at 31 December 2023 - i.e. this workbook's existing FY2024 opening figure is that entity's own closing balance for its first, ~10-month accounting period, built mostly from a £179,405k share capital issuance (the mechanism for the ClearBank Limited acquisition) rather than organic trading profit. This bridging period is not added as its own column here since it doesn't align with this workbook's FY-year grid, but the £196,497k figure is now independently verified against its true source rather than only appearing as an unexplained opening balance. Balance Sheet and P&amp;L totals for each year are still internally consistent (assets = liabilities + equity; income - expenses = profit/loss) since each is a same-entity, same-year snapshot - only the cross-year equity roll-forward is affected. FY2023's own Statement of Financial Position/Comprehensive Income are Company-only (ClearBank Limited did not publish Consolidated statements that year - see the Company vs Consolidated presentation note below); FY2021/FY2022/FY2024/FY2025 are Consolidated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="380" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Per project convention, each year's own originally-published figures are used throughout (FY2022's own AR2022 Consolidated figures, not AR2023's restated comparative - see CASH_FLOW_SOURCES' existing ENTITY_NOTE for the same convention applied to Cash Flow).
 PRESENTATION NOTE: FY2021's own Statement of Comprehensive Income discloses only Net interest income and Net fee income (no separate Interest income/expense or Fee income/expense split) - per AR2022's own footnote, "In 2021, only net interest income and net fee income were presented without splitting for gross amounts." FY2023's own Statement of Comprehensive Income additionally has an "Expenses recharged" line (income, not cost) not present in any other year, resulting in a positive "Operating profit" that year rather than the "Operating loss" label used elsewhere - both reproduced as reported. Balance Sheet: "Loans and advances to banks" (an interbank placement, not a customer loan) appears as its own line FY2021-FY2023 only - dropped from FY2024/FY2025's presentation (folded into Cash and cash equivalents per the Group's own accounting policy note). "Due from UK tax authorities" (FY2022/FY2023) and "Current tax asset" (FY2024/FY2025) are the same concept under different labels; FY2021 has neither line. Equity: "Share-based payment reserve" (FY2021/FY2022) was replaced by "Capital contribution reserve" from FY2023 onward (see the entity-change note above); "Treasury shares" and "Translation reserve" are absent from FY2023's Company-only presentation, present in every other year's Consolidated presentation.
 FY2017-FY2020 presentation: "Amounts due to customers" (FY2017 label) and "Customer deposits" (FY2018-FY2020 label) are the same concept under different labels - ClearBank opened to customers in October 2017, so FY2017's figure (£1,601k) reflects barely two months of customer-facing activity. "Right-of-use assets"/"Lease obligations" first appear in FY2019 (adoption of IFRS 16, replacing IAS 17 - see the Group's own Note 3.1) - absent FY2017/FY2018. "Translation reserve" first appears in FY2019 (a small foreign currency translation difference of £33k) - absent FY2017/FY2018, which had no foreign operations giving rise to translation differences. "Deferred income" first appears in FY2019 - absent FY2017/FY2018. FY2017's Statement of Comprehensive Income shows no Interest expense line (Net interest income was not yet split into gross Interest income/expense until FY2019) and no Impairments line (first appears FY2019).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A57:I57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9310,7 +9412,7 @@
         <v>27062</v>
       </c>
     </row>
-    <row r="49" ht="280" customHeight="1">
+    <row r="49" ht="338" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are ClearBank Limited's own Consolidated Statement of Cash Flows:
@@ -9599,7 +9701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -10410,7 +10512,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="520" customHeight="1">
+    <row r="37" ht="409" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank's own published key-metrics table, reproduced as printed. Each column is transcribed from the edition in which that year is the reporting year, except FY2021 (see below).
@@ -10424,7 +10526,14 @@
 ENTITY CHANGES MID-SERIES, AND THE TABLE HEADER SAYS SO. The FY2022 edition heads its columns '31 Dec 2022 / 31 Dec 2021' and its narrative speaks of 'the Bank' - ClearBank Limited's own consolidation. The FY2023 edition heads its single column 'ClearBank Group / 31 Dec 2023', and FY2024/FY2025 continue on that basis: ClearBank Group Holdings Limited (company 14254435), which also consolidates ClearBank Europe N.V. FY2023-FY2025 are therefore group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2021/FY2022 columns. Same caveat as the other Pillar 3 sheets.
 TWO INCONSISTENCIES IN CLEARBANK'S OWN PRINTING, recorded and not reconciled:
 • FY2023 total risk-weighted exposure amount is 163 in the FY2023 edition and 162 in the FY2024 edition's FY2023 comparative. The 163 shown here is FY2023's own edition.
-• The FY2025 edition prints FY2024 total RWEA as 211 on its Key metrics table and 212 on its 'Overview of risk weighted exposure amounts' table, two pages apart in the same document. This sheet shows 211 (the key-metrics figure); the RWA Breakdown sheet shows 212, its own table's total. Both are as published.
+• The FY2025 edition prints FY2024 total RWEA as 211 on its Key metrics table and 212 on its 'Overview of risk weighted exposure amounts' table, two pages apart in the same document. This sheet shows 211 (the key-metrics figure); the RWA Breakdown sheet shows 212, its own table's total. Both are as published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="409" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FY2023 SREP ROWS LOOK WRONG IN THE SOURCE, AND ARE REPRODUCED ANYWAY. The FY2023 edition prints 'Additional CET1 SREP requirements 0.00%' and 'Total SREP own funds requirements 0.00%' - a total SREP own funds requirement of zero is not possible (the Pillar 1 minimum alone is 8%), and the same edition's own 'Overall capital requirements' row prints 22.11%. The FY2024 edition's FY2023 comparative instead prints 9.91% and 17.61% for those two rows, and 59.84% rather than 77.26% for 'CET1 available after meeting the total SREP own funds requirements'. Under this project's rule that each year comes from its own edition, the FY2023 column here carries the FY2023 edition's figures; the FY2024 edition's restated comparatives are recorded in this note so nothing is lost. The FY2022 edition prints 0.00% for those rows in both its columns, and a 0.00% capital conservation buffer, which is likewise as published.
 TWO PRINTED PRECISIONS FOR THE SAME FY2021 QUANTITY, ON THIS SHEET AND ON THE CET1/TIER 1/TOTAL CAPITAL SHEETS - not an error in either place. This sheet shows 37 for FY2021 because that is what the FY2022 edition's comparative column prints: ClearBank rounds the whole key-metrics table to whole £m. The CET1 Capital / Tier 1 Capital / Total Capital sheets show 36.7, because those sheets take FY2021 from FY2021's OWN Pillar 3 edition, whose 'Table 2: Own funds' gives the figure to the pound (£36,739k). Same quantity, two precisions, two documents. Both are left as published rather than re-rounded in either direction, because rounding 36,739 to '37' is ClearBank's act, not this workbook's, and re-deriving '36.7' onto a reproduction sheet would print a number the key-metrics table never contained.
 PRINTED PRECISION AND LABELS ARE AS EACH EDITION HAS THEM. The FY2023 edition prints the NSFR ratio with a thousands separator ('10,153.88%') where the others do not; the FY2025/FY2024 editions caption the LCR row 'Total net outflows (adjusted value)' where the FY2023/FY2022 editions caption it 'Total net cash outflows (adjusted value)', and capitalise 'Total Capital ratio' where the earlier ones write 'Total capital ratio'. The most recent edition's wording is used for the row label and the variants are recorded here.
@@ -10433,7 +10542,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A37:F37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10446,7 +10556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -10561,7 +10671,7 @@
         <v>23.681</v>
       </c>
     </row>
-    <row r="6" ht="190" customHeight="1">
+    <row r="6" ht="377" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
@@ -10580,7 +10690,14 @@
   FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
   FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
-Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="190" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
@@ -10588,8 +10705,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A8:J8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10601,7 +10719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -10734,7 +10852,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="190" customHeight="1">
+    <row r="6" ht="377" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
@@ -10753,7 +10871,14 @@
   FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
   FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
   FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
-Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="190" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
@@ -10761,8 +10886,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A8:J8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/CLEARBANK FINANCIALS.xlsx
+++ b/banks/CLEARBANK FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3368,14 +3369,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — Tier 1 Capital</t>
+          <t>ClearBank Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m (= CET1 capital; no AT1 instruments)</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -3434,35 +3435,53 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>132</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>141</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>126</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>29.952</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>17.461</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>23.681</v>
+          <t>Common Equity Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>49.75%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>67.02%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>77.45%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>87.66%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>139.70%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>114.20%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="377" customHeight="1">
@@ -3531,14 +3550,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — Tier 1 Ratio</t>
+          <t>ClearBank Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£m (= CET1 capital; no AT1 instruments)</t>
         </is>
       </c>
     </row>
@@ -3597,53 +3616,35 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>49.75%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>67.02%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>77.45%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>87.66%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>139.70%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>114.20%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>29.952</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>17.461</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>23.681</v>
       </c>
     </row>
     <row r="6" ht="377" customHeight="1">
@@ -3712,14 +3713,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — Total Capital</t>
+          <t>ClearBank Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m (= CET1 capital; no Tier 2 instruments)</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -3778,35 +3779,53 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>132</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>141</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>126</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>29.952</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>17.461</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>23.681</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>49.75%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>67.02%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>77.45%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>87.66%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>139.70%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>114.20%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="377" customHeight="1">
@@ -3875,14 +3894,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — Total Capital Ratio</t>
+          <t>ClearBank Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£m (= CET1 capital; no Tier 2 instruments)</t>
         </is>
       </c>
     </row>
@@ -3941,53 +3960,35 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>49.75%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>67.02%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>77.45%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>87.66%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>139.70%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>114.20%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>29.952</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>17.461</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>23.681</v>
       </c>
     </row>
     <row r="6" ht="377" customHeight="1">
@@ -4033,6 +4034,187 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank Limited — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>% of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>49.75%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>67.02%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>77.45%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>87.66%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>139.70%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>114.20%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="377" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
+FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
+FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="190" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A8:J8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4168,7 +4350,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4387,7 +4569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4579,7 +4761,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4760,7 +4942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4934,191 +5116,6 @@
         <is>
           <t>(continued)
 FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A9:J9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ClearBank Limited — MREL Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>MREL Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure; FY2024 Pillar 3 (PDF p.8) says only that the 2024 Resolution Communication left resolution strategy and MREL unchanged for 2025</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – FY2021 Pillar 3 MREL section (PDF p.11): 'Currently, ClearBank is not required to hold any additional capital in respect of MREL'</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no MREL figure; FY2017 Pillar 3 says only that MREL applied from 1 Jan 2016, fully phased in by 1 Jan 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: CORRECTED 2026-09-19 (GA-020). This note previously said no qualitative MREL statement appears in any Pillar 3 or Annual Report. That was wrong: the Pillar 3 documents carry an MREL section in FY2017 (phase-in dates only), FY2018 (PDF p.10), FY2019 (p.10), FY2020 (p.10) and FY2021 (p.11) - the last four stating that ClearBank has been informed by the PRA that it is not currently required to hold any additional capital in respect of MREL - and FY2024 (p.8) notes that the 2024 Resolution Communication left its resolution strategy and MREL unchanged for 2025. No MREL ratio or requirement figure is published in any year and none is derived. FY2022, FY2023 and FY2025 Pillar 3 documents and every Annual Report FY2016-FY2025 available return zero hits for 'MREL' (full-text search 2026-09-19).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="390" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
-REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
-FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
-FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
-FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
-FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
-FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
-  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
-  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
-  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
-  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
-  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
-Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
-FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="150" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>(continued)
 CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
 LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
         </is>
@@ -6061,6 +6058,191 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank Limited — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure; FY2024 Pillar 3 (PDF p.8) says only that the 2024 Resolution Communication left resolution strategy and MREL unchanged for 2025</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure or reference in this year's Pillar 3 or annual report (full-text search 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – FY2021 Pillar 3 MREL section (PDF p.11): 'Currently, ClearBank is not required to hold any additional capital in respect of MREL'</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – this year's Pillar 3 MREL section: ClearBank 'has been informed by the PRA that we are not currently required to hold any additional capital in respect of MREL'</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure; FY2017 Pillar 3 says only that MREL applied from 1 Jan 2016, fully phased in by 1 Jan 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: CORRECTED 2026-09-19 (GA-020). This note previously said no qualitative MREL statement appears in any Pillar 3 or Annual Report. That was wrong: the Pillar 3 documents carry an MREL section in FY2017 (phase-in dates only), FY2018 (PDF p.10), FY2019 (p.10), FY2020 (p.10) and FY2021 (p.11) - the last four stating that ClearBank has been informed by the PRA that it is not currently required to hold any additional capital in respect of MREL - and FY2024 (p.8) notes that the 2024 Resolution Communication left its resolution strategy and MREL unchanged for 2025. No MREL ratio or requirement figure is published in any year and none is derived. FY2022, FY2023 and FY2025 Pillar 3 documents and every Annual Report FY2016-FY2025 available return zero hits for 'MREL' (full-text search 2026-09-19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="390" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
+REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
+FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
+FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
+FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
+FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
+FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
+FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
+FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
+PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
+  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
+  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
+  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
+  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
+  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
+Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.
+FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
+LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A9:J9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9701,6 +9883,371 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClearBank Limited — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>-7.25%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>-5.87%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>20.66%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>8.55%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>-43.23%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>-60.51%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>-88.13%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>-70.03%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>-7.41%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>-4.64%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>17.29%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>7.81%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>-39.05%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>-51.15%</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>-84.48%</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>-67.31%</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>-40.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>-1.47%</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>-3.69%</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>-10.46%</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>-38.98%</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-1.02%</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>-2.83%</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>-6.04%</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>-28.41%</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>-34.73%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ClearBank Limited's own published return</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="156" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: COMPUTED, NOT PUBLISHED. ClearBank publishes NO ROE, RoTE or ROA. Full-text search of the ClearBank Annual Report and Accounts 2025 (born-digital, 102 pages, 275,426 text bytes) for 'returns? on', 'RoTE', 'ROE', 'ROA' returns three hits, none of them a return measure: two are 'Consolidated statement of comprehensive income' (substring match) and one is narrative - 'solvency while optimising the return on risk' (PDF p.89, treasury credit-risk commentary). The 'Key performance indicators (KPIs)' page, printed p.31 (PDF p.32), was confirmed on a 300 dpi render and holds six tiles: Fee income (pro forma) +37% GBP62.1m, Spread-based fee income +96% GBP25.9m, Payment volumes +57% 262m, Accounts +33% 17.1m, Customer deposits +65% GBP17.8bn, 2025 Group CET1 ratio 50%. No return on equity or assets, and the Alternative Performance Measures appendix (printed p.97) defines none. Every percentage above is therefore this project's own arithmetic on the figures printed on this workbook's statement sheets, and is labelled as such. That the bank publishes none is a POSITIVE FINDING, recorded in research/profitability/published_returns.jsonl, and not a failed search: for this bank the computed figure is the only figure there is.
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return. The two diverge most in FY2020, where return on equity is -60.51% on an average basis and -51.15% on a year-end basis.
+FY2017 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2017 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2017 because it needs only the closing balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “profit/(loss) for the year after taxation” and the Balance Sheet rows “total equity” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from ClearBank Limited's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The finding that ClearBank Limited publishes no return of its own is recorded in research/profitability/published_returns.jsonl under ‘CLEARBANK’, verified against the bank's own annual report rendered at 300 dpi.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A11:J11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10545,169 +11092,6 @@
   <mergeCells count="2">
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A37:F37"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ClearBank Limited — CET1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£m</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>132</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>141</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>126</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>29.952</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>17.461</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>23.681</v>
-      </c>
-    </row>
-    <row r="6" ht="377" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - ClearBank Group Pillar 3 Key Metrics table:
-REPORTING ENTITY (see the 'WHICH GROUP' note on the Cash Flow Statement sheet): FY2017-FY2022 these metrics are ClearBank Limited's own consolidation; FY2023-FY2025 they are ClearBank Group Holdings Limited's consolidation (company 14254435), which also includes ClearBank Europe N.V. There is no ClearBank-Limited-only Pillar 3 publication for FY2023 onward, so these are group-basis figures in an entity-level workbook and are NOT a like-for-like continuation of the FY2017-FY2022 series.
-FY2025: ClearBank Pillar 3 Disclosure 2025, 'Key metrics' table, p.15 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2025.pdf
-FY2024: ClearBank Pillar 3 Disclosure 2024, 'Key metrics' table, p.13 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Discolsure-2024.pdf (located 2026-09-16; the file is published under a misspelt name, 'ClearBank-Pillar-3-Discolsure-2024.pdf', which is why earlier passes cited the FY2025 edition's comparative column instead. Every FY2024 figure is identical in the two, so no value changed - but the citation now points at FY2024's own edition, as this project requires.)
-FY2023: ClearBank Pillar 3 Disclosure 2023, p.5-6 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-Disclosure-2023.pdf
-FY2022/FY2021: ClearBank Pillar 3 Disclosure 2022, p.4-5 (FY2021 as the FY2022 document's own comparative column, cross-checked against ClearBank Pillar 3 Disclosure 2021's own Table 1/Table 2 - CET1 140%/£36,739k there vs. 139.70%/£37m here, consistent to rounding) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-2022.pdf and https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-FY2020: mostly ClearBank Annual Report and Accounts 2020's own "Robust capital, liquidity and balance sheet" financial review narrative (CET1 ratio, LCR, NSFR) and Note 22 Capital management (CET1 capital £29,952k) - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2020.pdf; UK Leverage Ratio (30%) and Total RWA (£26.2m) are NOT disclosed anywhere in AR2020 itself and are instead taken from ClearBank Pillar 3 disclosure 2021's own FY2020 comparative column (Table 1 and the COREP own-funds template) - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2021.pdf
-FY2019: ClearBank Annual Report and Accounts 2019, financial review KPI table and Note 21 Capital management - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2019.pdf
-FY2018: ClearBank Limited 2018 Annual Report, financial review KPI table and capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2018.pdf
-FY2017: ClearBank Limited 2017 Annual Report, p.9 KPI table and p.19 capital/leverage notes - https://clear.bank/uploads/assets/ClearBank-Annual-Report-2017.pdf
-PRE-2021 DISCLOSURE FORMAT NOTE, CORRECTED 2026-09-16. This note previously read 'ClearBank did not publish a standalone Pillar 3 document for FY2017-FY2020'. That is FALSE and is retracted. ClearBank has published a standalone Pillar 3 disclosure every year since FY2016, and all of them are live on clear.bank today - they are listed in the site's own sitemap under /pillar-3-disclosure but are not all linked from the visible page, which is why earlier passes missed them:
-  FY2020 - https://clear.bank/uploads/assets/Clear.Bank-Pillar-3-disclosure-2020.pdf
-  FY2019 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2019.pdf
-  FY2018 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2018.pdf
-  FY2017 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2017.pdf
-  FY2016 - https://clear.bank/uploads/assets/ClearBank-Pillar-3-disclosure-2016.pdf
-Each was downloaded and read on 2026-09-16 (HTTP 200, application/pdf, %PDF magic bytes, real text layers). What IS true, and is the substantive point the old note was reaching for, is that none of those editions uses the KM1 template or anything like it: each has a bespoke 'Summary Analysis' section with 'Table 1: Capital and leverage ratios' and 'Table 2: Own funds'. The FY2020 edition's Table 1 gives CET1/Tier 1/Total 114%, CRD leverage 3%, UK leverage 30%, and its Table 2 gives CET1 capital of £29,952k - which is what this workbook already carries for FY2020, so no figure changes. The FY2019 edition prints CET1 capital of £17,460k where this workbook carries £17,461k from AR2019; the £1k difference is left as each source printed it. Re-sourcing FY2016-FY2019 from these documents rather than from the Annual Reports is a real improvement left for a later pass - it is logged here rather than done, because the KM1 rollout ticket that found them covers the KM1 sheet and the latest edition, not a re-sourcing of nine-year-old columns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="190" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>(continued)
-FY2017-FY2019's CET1/leverage ratios are disclosed only to whole-percent precision in the source (e.g. "53%", "88%"); FY2020's are disclosed to 1 decimal place via the FY2021 Pillar 3 document's comparative column. No Basel II/CET1-terminology issue arises for any of these years (all post-date the 2014 CRD IV/CET1 introduction).
-CET1 = Tier 1 = Total Capital every year (no AT1/Tier 2 instruments). No MREL ratio is disclosed in any Pillar 3 document or Annual Report reviewed (FY2017-FY2025); the FY2018-FY2021 Pillar 3 documents state the Bank is not required to hold additional capital for MREL - see the MREL Ratio sheet (corrected 2026-09-19, GA-020).
-LEVERAGE RATIO BASIS NOTE: FY2021's own Pillar 3 document (Table 1) discloses two different leverage figures with materially different values - a "CRD leverage ratio" of 1% and a "UK leverage ratio" of 39%, reflecting genuinely different exposure-measure definitions, not a typo. The 38.79% figure used here for FY2021 (from the FY2022 document's comparative, "excluding claims on central banks" basis) matches the UK leverage ratio figure, consistent with the basis used FY2022 onward. FY2017-FY2020's leverage ratios are each year's own disclosed "UK Leverage Ratio" (84%/74%/21%/30%), which pre-date the "excluding claims on central banks" wording introduced later - shown as originally disclosed each year, not adjusted for comparability.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A8:J8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10737,14 +11121,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClearBank Limited — CET1 Ratio</t>
+          <t>ClearBank Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -10803,53 +11187,35 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>49.75%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>67.02%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>77.45%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>87.66%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>139.70%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>114.20%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>29.952</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>17.461</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>23.681</v>
       </c>
     </row>
     <row r="6" ht="377" customHeight="1">
